--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Pizza builder" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Hours" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Shop details" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Lists" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -112,6 +113,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -491,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104" customWidth="1" min="1" max="1"/>
@@ -520,7 +524,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HOW TO PUBLISH</t>
+          <t>HOW TO PUBLISH — from any computer, nothing to install</t>
         </is>
       </c>
     </row>
@@ -534,21 +538,21 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2.  Close Excel. It has to be closed or the file stays locked.</t>
+          <t>2.  Go to github.com/Tejas7727/tastypizza-site and click  Add file  -&gt;  Upload files.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>3.  Double-click "Publish website" in the same folder as this file.</t>
+          <t>3.  Drop this file in, and click  Commit changes.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>4.  A black window opens and tells you what it is doing. When it says DONE, the site is live in about a minute.</t>
+          <t>4.  The site updates in about two minutes. If something in the sheet is wrong, nothing changes and the Actions tab says which cell.</t>
         </is>
       </c>
     </row>
@@ -556,83 +560,93 @@
       <c r="A10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Or, on the computer that has the website folder: close Excel and double-click "Publish website". It also picks up new photos dropped in assets\photos-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>WHAT EACH SHEET IS FOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Home page      the big slogan, the sentence under it, the three little facts</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Deals          your offers: turn them on and off, change the price or the wording</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Menu           every dish, its description and its prices</t>
+          <t>Home page      the big slogan, the sentence under it, the three little facts</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Pizza builder  what a build-your-own pizza costs, and extra toppings</t>
+          <t>Deals          your offers: on and off, price, wording, and which ones go on the front page</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hours          opening and closing times</t>
+          <t>Menu           every dish, its description, its prices and its photo</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Pizza builder  what a build-your-own pizza costs, and extra toppings</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hours          opening and closing times</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Shop details   phone, email, delivery fee, tax, DoorDash and Uber Eats links</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="8" customHeight="1">
-      <c r="A18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="8" customHeight="1">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>THE GREY COLUMNS</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Grey columns are how each row finds its way back to the website. Do not edit them, do not delete rows, do not sort the sheet. Everything else is yours.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="8" customHeight="1">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23" ht="8" customHeight="1">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>IF SOMETHING LOOKS WRONG</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Nothing goes live if a price is not a number or a required box is empty — the window will say which row and nothing will be published. Fix it and run it again.</t>
         </is>
@@ -658,188 +672,188 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Home page</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>The words on the front of the website. The LAST line of each slogan is the one printed in red. The phone slogan is shown on phones, where three lines take up too much of the screen — keep it to two short lines.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>home.sloganWide</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Fresh daily.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>home.sloganWide</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Hot nightly.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>home.sloganWide</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Always tasty.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>home.sloganPhone</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Fresh. Hot.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>home.sloganPhone</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Always tasty.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>home.eyebrow</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>760 Main Street · Dartmouth</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>home.lede</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Fresh dough every morning, hand-stretched, out of a deck oven. Owned and operated by the Patel family.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>home.facts</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>20–30 min | pickup</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>home.facts</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>$2.00 | delivery</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>home.facts</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Free | parking</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Facts are written as  bold part | the rest  — e.g.  Free | parking</t>
         </is>
@@ -859,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -868,279 +882,308 @@
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Deals</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Your offers. "Showing" turns one on or off on the website — no need to delete it. "Was price" is the crossed-out price; leave it empty for no saving. Prices are numbers only, no dollar sign.</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Your offers. "Showing" turns one on or off on the website — no need to delete it. "Was price" is the crossed-out price; leave it empty for no saving. Prices are numbers only, no dollar sign. Pick a "Home page pizza" to put the deal on the front page; leave it empty to keep it off.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Showing</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Was price</t>
         </is>
       </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Home page pizza</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>large-4-topping</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Large 16" Pizza, 4 Toppings</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Any four toppings you like.</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>20.95</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>22.95</v>
       </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>pepperoni</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>pizza-and-fingers</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Medium Pizza + Medium Garlic Fingers</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>12" pizza with four toppings, plus 12" garlic fingers with donair sauce.</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>28.95</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>31.4</v>
       </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>meat-lovers</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>two-mediums</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Two Medium Pizzas</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Four toppings on each.</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>32.95</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>34.9</v>
       </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>greek</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>party-box</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Tasty Party Box</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Onion rings, deep fried pepperoni, 9 mozza sticks, 12 chicken fries and 6 donair egg rolls. Honey mustard, sour cream and donair sauce. 2L pop included.</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>47.99</v>
       </c>
-      <c r="F8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>egg-rolls-6</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>6 Donair Egg Rolls</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>With donair sauce.</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>15</v>
       </c>
+      <c r="G9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>pogos-6</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>6 Donair Pogos</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>With donair sauce.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>19.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>20.7</v>
       </c>
+      <c r="G10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>two-large-subs</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Two Large Subs</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Cold cut, pizza or real turkey.</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>22.45</v>
       </c>
-      <c r="F11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>two-can-dine</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Two Can Dine</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Two medium burritos, two small chips &amp; salsa, two cans of pop.</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>24.99</v>
       </c>
-      <c r="F12" s="9" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="B5:B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
+      <formula1>=Lists!$A$1:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1153,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1165,4378 +1208,4692 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Menu</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Every dish on the site. Change a name, a description or any price. Prices are numbers only. Leave a price empty if that size is not sold. Items priced by a shared tier show their tier's prices — changing one changes every dish on that tier, which is how the printed menu works.</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Every dish on the site. Change a name, a description or any price. Prices are numbers only. Leave a price empty if that size is not sold. Items priced by a shared tier show their tier's prices — changing one changes every dish on that tier, which is how the printed menu works. "Photo" picks the picture; the shop's own photos show big on the site.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Dish</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Price 1</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Price 2</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Price 3</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Price 4</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Sizes</t>
         </is>
       </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>build-your-own/Build Your Own Pizza</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Build Your Own</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Build Your Own Pizza</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Pick your size, then tap toppings. Five toppings makes it a Tasty Pizza Special.</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>cheese-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>gourmet/All Dressed</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>All Dressed</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Pepperoni, salami, mushrooms, green peppers, onions, bacon, hamburger.</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>all-dressed-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>gourmet/Donair Pizza</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Donair Pizza</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Donair meat, onions, tomatoes, donair sauce.</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="10" t="n">
         <v>27.45</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="10" t="n">
         <v>32.95</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>donair-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>gourmet/Bubba</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Bubba</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Garlic spread, donair meat, onions, tomatoes, donair sauce.</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="10" t="n">
         <v>27.45</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="10" t="n">
         <v>32.95</v>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>gourmet/Meat Lovers</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Meat Lovers</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Pepperoni, salami, bacon, hamburger, ham, donair meat, Italian sausage.</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>meat-lovers-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>gourmet/Hawaiian</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Hawaiian</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Ham, pineapple, mozzarella.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>hawaiian-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>gourmet/Greek</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Greek</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Tomatoes, red onions, black olives, feta and mozzarella, oregano and olive oil.</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>greek-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>gourmet/Cheese Lovers</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Cheese Lovers</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Feta, cheddar, mozzarella and parmesan.</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>gourmet/BBQ Chicken</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>BBQ Chicken</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Chicken, zesty sauce, tomatoes, green peppers, red onions, mushrooms, mozzarella and cheddar.</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>bbq-chicken-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>gourmet/Vegetarian</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Vegetarian</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Mushrooms, green peppers, onions, tomatoes, hot peppers, olives, pineapple.</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>veggie-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>gourmet/Canadian Classic</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Canadian Classic</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Pepperoni, mushrooms, bacon, mozzarella and cheddar on a garlic crust.</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>gourmet/Cheeseburger</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Cheeseburger</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Hamburger, cheddar and mozzarella, your choice of four vegetables.</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="10" t="n">
         <v>25.45</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="10" t="n">
         <v>30.95</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>cheeseburger-pizza</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>gourmet/Philly Cheese Steak</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Gourmet Specialty Pizza</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Philly Cheese Steak</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Zesty sauce, sliced steak, red onions, tomatoes, green peppers, mushrooms, mozzarella and cheddar.</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="10" t="n">
         <v>27.45</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="10" t="n">
         <v>32.95</v>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>garlic-fingers/Garlic Fingers</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Garlic Fingers</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Garlic Fingers</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Garlic butter, mozzarella, pulled apart by hand.</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="10" t="n">
         <v>10.25</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="10" t="n">
         <v>17.95</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="10" t="n">
         <v>22.45</v>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>garlic-fingers</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>garlic-fingers/With Bacon</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Garlic Fingers</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>With Bacon</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Same, with bacon through it.</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <v>11.25</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="10" t="n">
         <v>19.95</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="10" t="n">
         <v>24.45</v>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>garlic-fingers/With Donair</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Garlic Fingers</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>With Donair</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Same, loaded with donair meat.</t>
         </is>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <v>17.95</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="10" t="n">
         <v>21.95</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="10" t="n">
         <v>26.95</v>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>garlic-fingers/Honey Garlic Fingers</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Garlic Fingers</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Honey Garlic Fingers</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>PLACEHOLDER — on the old menu with no price. Confirm price before launch.</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>pizza-extras/Special Topping</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Pizza Extras</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Special Topping</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Zesty chicken, sliced steak, parmesan, cheddar or feta.</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="10" t="n">
         <v>1.95</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="10" t="n">
         <v>2.85</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="10" t="n">
         <v>3.95</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="10" t="n">
         <v>4.95</v>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>pizza-extras/Gluten Free Crust</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Pizza Extras</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Gluten Free Crust</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Any size.</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
         </is>
       </c>
+      <c r="J23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>donair/Donair</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Donair</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Donair</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Spiced beef off the spit, sweet sauce, warm pita. The one we're known for.</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>9.25</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="10" t="n">
         <v>11.35</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="10" t="n">
         <v>13.45</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="10" t="n">
         <v>15.55</v>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large / Super</t>
         </is>
       </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>donair</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>donair/Add Cheese</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Donair</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Add Cheese</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Melted through the meat.</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="10" t="n">
         <v>2.85</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="10" t="n">
         <v>3.35</v>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large / Super</t>
         </is>
       </c>
+      <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>donair/Add Extra Meat</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Donair</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Add Extra Meat</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>For when a large isn't a large.</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="10" t="n">
         <v>3.35</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>4.35</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="10" t="n">
         <v>5.35</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="H26" s="10" t="n">
         <v>6.35</v>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large / Super</t>
         </is>
       </c>
+      <c r="J26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>donair-plates/Small Donair Plate</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Donair Plates</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Small Donair Plate</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="9" t="n">
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="n">
         <v>11.95</v>
       </c>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="inlineStr"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>donair-plate</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>donair-plates/Large Donair Plate</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Donair Plates</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Large Donair Plate</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="9" t="n">
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="n">
         <v>15.95</v>
       </c>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="inlineStr"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>donair-fried/Donair Egg Roll</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Donair, Deep Fried</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Donair Egg Roll</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Donair, rolled and fried. Order more than one.</t>
         </is>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="inlineStr"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>donair-egg-roll</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>donair-fried/Donair Egg Rolls — Dozen</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Donair, Deep Fried</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Donair Egg Rolls — Dozen</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="9" t="n">
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="inlineStr"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>donair-fried/Donair Pogo</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Donair, Deep Fried</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Donair Pogo</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Donair on a stick in batter. Yes, really.</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="10" t="n">
         <v>3.45</v>
       </c>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="inlineStr"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>donair-pogo</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>donair-fried/Donair Pogos — Dozen</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Donair, Deep Fried</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Donair Pogos — Dozen</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="9" t="n">
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="n">
         <v>38.95</v>
       </c>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="inlineStr"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>donair-sauce/Small Donair Sauce</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Donair Sauce</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Small Donair Sauce</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="9" t="n">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="n">
         <v>2.25</v>
       </c>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="inlineStr"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>donair-sauce/Large Donair Sauce</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Donair Sauce</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Large Donair Sauce</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="9" t="n">
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="n">
         <v>3.25</v>
       </c>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="inlineStr"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>donair-sauce/Extra Large Donair Sauce</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Donair Sauce</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Extra Large Donair Sauce</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="n">
         <v>4.95</v>
       </c>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="inlineStr"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>poutine/Classic Poutine</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Poutine</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Classic Poutine</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Curds, gravy, fries. Done right.</t>
         </is>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="10" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="10" t="n">
         <v>12.25</v>
       </c>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>poutine</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>poutine/Donair Poutine</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Poutine</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Donair Poutine</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>With donair meat and a line of donair sauce.</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n">
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n">
         <v>14.25</v>
       </c>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>poutine/Chicken Poutine</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Poutine</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Chicken Poutine</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n">
+      <c r="D38" s="10" t="inlineStr"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>poutine/Hamburger Poutine</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Poutine</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Hamburger Poutine</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n">
+      <c r="D39" s="10" t="inlineStr"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>poutine/Greek Poutine</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Poutine</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Greek Poutine</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Feta, tomato, red onion, olives.</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n">
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>poutine/Extra Cheese</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Poutine</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Extra Cheese</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="n">
+      <c r="D41" s="10" t="inlineStr"/>
+      <c r="E41" s="10" t="n">
         <v>2.25</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>2.95</v>
       </c>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>poutine/Extra Gravy</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Poutine</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Extra Gravy</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="9" t="n">
+      <c r="D42" s="10" t="inlineStr"/>
+      <c r="E42" s="10" t="n">
         <v>1.75</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>wings/10 Wings</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Chicken Wings</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>10 Wings</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="n">
+      <c r="D43" s="10" t="inlineStr"/>
+      <c r="E43" s="10" t="n">
         <v>12.99</v>
       </c>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="inlineStr"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>chicken-wings</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>wings/15 Wings</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Chicken Wings</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>15 Wings</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="n">
+      <c r="D44" s="10" t="inlineStr"/>
+      <c r="E44" s="10" t="n">
         <v>18.95</v>
       </c>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="inlineStr"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>wings/20 Wings</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Chicken Wings</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>20 Wings</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr"/>
-      <c r="E45" s="9" t="n">
+      <c r="D45" s="10" t="inlineStr"/>
+      <c r="E45" s="10" t="n">
         <v>24.95</v>
       </c>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="inlineStr"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>wings/30 Wings</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Chicken Wings</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>30 Wings</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>For the room.</t>
         </is>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="10" t="n">
         <v>36.95</v>
       </c>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="inlineStr"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="inlineStr"/>
+      <c r="J46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>nachos/Nachos</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Nachos</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>Nachos</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>Green onion, tomato, black olives, jalapeño, mozzarella and cheddar. Salsa and sour cream on the side.</t>
         </is>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="10" t="n">
         <v>15.45</v>
       </c>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="inlineStr"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>nachos</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>nachos/Add Chicken, Hamburger or Bacon</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Nachos</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Add Chicken, Hamburger or Bacon</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr"/>
-      <c r="E48" s="9" t="n">
+      <c r="D48" s="10" t="inlineStr"/>
+      <c r="E48" s="10" t="n">
         <v>3.65</v>
       </c>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="9" t="n"/>
-      <c r="I48" s="9" t="inlineStr"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>nachos/Extra Cheese</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Nachos</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>Extra Cheese</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr"/>
-      <c r="E49" s="9" t="n">
+      <c r="D49" s="10" t="inlineStr"/>
+      <c r="E49" s="10" t="n">
         <v>3.95</v>
       </c>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="9" t="n"/>
-      <c r="I49" s="9" t="inlineStr"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>burgers/Hamburger</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Burgers</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>Hamburger</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr"/>
-      <c r="E50" s="9" t="n">
+      <c r="D50" s="10" t="inlineStr"/>
+      <c r="E50" s="10" t="n">
         <v>6.45</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="10" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Burger / Platter</t>
         </is>
       </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>hamburger</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>burgers/Cheeseburger</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Burgers</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>Cheeseburger</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr"/>
-      <c r="E51" s="9" t="n">
+      <c r="D51" s="10" t="inlineStr"/>
+      <c r="E51" s="10" t="n">
         <v>6.95</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="10" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Burger / Platter</t>
         </is>
       </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>cheeseburger</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>burgers/Chicken Burger</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Burgers</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>Chicken Burger</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr"/>
-      <c r="E52" s="9" t="n">
+      <c r="D52" s="10" t="inlineStr"/>
+      <c r="E52" s="10" t="n">
         <v>6.95</v>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="10" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-      <c r="I52" s="9" t="inlineStr">
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Burger / Platter</t>
         </is>
       </c>
+      <c r="J52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>burgers/Donair Burger</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Burgers</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Donair Burger</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>Donair meat and sauce on a burger. A Dartmouth idea.</t>
         </is>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="E53" s="10" t="n">
         <v>7.25</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="10" t="n">
         <v>10.45</v>
       </c>
-      <c r="G53" s="9" t="n"/>
-      <c r="H53" s="9" t="n"/>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Burger / Platter</t>
         </is>
       </c>
+      <c r="J53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>burgers/Pizza Burger</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Burgers</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>Pizza Burger</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr"/>
-      <c r="E54" s="9" t="n">
+      <c r="D54" s="10" t="inlineStr"/>
+      <c r="E54" s="10" t="n">
         <v>6.95</v>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" s="10" t="n">
         <v>10.45</v>
       </c>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-      <c r="I54" s="9" t="inlineStr">
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Burger / Platter</t>
         </is>
       </c>
+      <c r="J54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>burgers/Add Bacon</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Burgers</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>Add Bacon</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr"/>
-      <c r="E55" s="9" t="n">
+      <c r="D55" s="10" t="inlineStr"/>
+      <c r="E55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Burger / Platter</t>
         </is>
       </c>
+      <c r="J55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>sides/Club House Sandwich with Fries</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>Club House Sandwich with Fries</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>Real turkey.</t>
         </is>
       </c>
-      <c r="E56" s="9" t="n">
+      <c r="E56" s="10" t="n">
         <v>14.45</v>
       </c>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="inlineStr"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="inlineStr"/>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>club-sandwich</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>sides/Hot Hamburger with Gravy &amp; Fries</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Hot Hamburger with Gravy &amp; Fries</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr"/>
-      <c r="E57" s="9" t="n">
+      <c r="D57" s="10" t="inlineStr"/>
+      <c r="E57" s="10" t="n">
         <v>12.3</v>
       </c>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="9" t="n"/>
-      <c r="H57" s="9" t="n"/>
-      <c r="I57" s="9" t="inlineStr"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>sides/Hot Turkey with Gravy &amp; Fries</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Hot Turkey with Gravy &amp; Fries</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr"/>
-      <c r="E58" s="9" t="n">
+      <c r="D58" s="10" t="inlineStr"/>
+      <c r="E58" s="10" t="n">
         <v>12.3</v>
       </c>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
-      <c r="H58" s="9" t="n"/>
-      <c r="I58" s="9" t="inlineStr"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="inlineStr"/>
+      <c r="J58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>sides/Large Fries</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Large Fries</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr"/>
-      <c r="E59" s="9" t="n">
+      <c r="D59" s="10" t="inlineStr"/>
+      <c r="E59" s="10" t="n">
         <v>5.45</v>
       </c>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="9" t="inlineStr"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>fries</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>sides/Large Onion Rings</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>Large Onion Rings</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="9" t="n">
+      <c r="D60" s="10" t="inlineStr"/>
+      <c r="E60" s="10" t="n">
         <v>5.45</v>
       </c>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="9" t="n"/>
-      <c r="I60" s="9" t="inlineStr"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="inlineStr"/>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>onion-rings</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>sides/12 Chicken Fries</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>12 Chicken Fries</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr"/>
-      <c r="E61" s="9" t="n">
+      <c r="D61" s="10" t="inlineStr"/>
+      <c r="E61" s="10" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-      <c r="H61" s="9" t="n"/>
-      <c r="I61" s="9" t="inlineStr"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="inlineStr"/>
+      <c r="J61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>sides/9 Mozza Sticks</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>9 Mozza Sticks</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr"/>
-      <c r="E62" s="9" t="n">
+      <c r="D62" s="10" t="inlineStr"/>
+      <c r="E62" s="10" t="n">
         <v>10.95</v>
       </c>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
-      <c r="H62" s="9" t="n"/>
-      <c r="I62" s="9" t="inlineStr"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="inlineStr"/>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>mozza-sticks</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>sides/Cup of Gravy — Small</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>Cup of Gravy — Small</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="n">
+      <c r="D63" s="10" t="inlineStr"/>
+      <c r="E63" s="10" t="n">
         <v>1.65</v>
       </c>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="9" t="n"/>
-      <c r="H63" s="9" t="n"/>
-      <c r="I63" s="9" t="inlineStr"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>sides/Cup of Gravy — Large</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>Sides &amp; Plates</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>Cup of Gravy — Large</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr"/>
-      <c r="E64" s="9" t="n">
+      <c r="D64" s="10" t="inlineStr"/>
+      <c r="E64" s="10" t="n">
         <v>2.85</v>
       </c>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
-      <c r="H64" s="9" t="n"/>
-      <c r="I64" s="9" t="inlineStr"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="inlineStr"/>
+      <c r="J64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>bread-sticks/Small Yum Yums</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>Bread Sticks ("Yum Yums")</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>Small Yum Yums</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr"/>
-      <c r="E65" s="9" t="n">
+      <c r="D65" s="10" t="inlineStr"/>
+      <c r="E65" s="10" t="n">
         <v>12.95</v>
       </c>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="inlineStr"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="inlineStr"/>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>bread-sticks</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>bread-sticks/Large Yum Yums</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>Bread Sticks ("Yum Yums")</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>Large Yum Yums</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="n">
+      <c r="D66" s="10" t="inlineStr"/>
+      <c r="E66" s="10" t="n">
         <v>16.45</v>
       </c>
-      <c r="F66" s="9" t="n"/>
-      <c r="G66" s="9" t="n"/>
-      <c r="H66" s="9" t="n"/>
-      <c r="I66" s="9" t="inlineStr"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="inlineStr"/>
+      <c r="J66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>wraps-pockets/Pita Wrap</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>Wraps &amp; Pockets</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Pita Wrap</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>Pizza, donair, cold cut, club, vegetarian, chicken, turkey or chicken Caesar.</t>
         </is>
       </c>
-      <c r="E67" s="9" t="n">
+      <c r="E67" s="10" t="n">
         <v>10.45</v>
       </c>
-      <c r="F67" s="9" t="n"/>
-      <c r="G67" s="9" t="n"/>
-      <c r="H67" s="9" t="n"/>
-      <c r="I67" s="9" t="inlineStr"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="inlineStr"/>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>pita-wrap</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>wraps-pockets/Pocket — Pizza, Chicken, Meats or Vegetarian</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Wraps &amp; Pockets</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Pocket — Pizza, Chicken, Meats or Vegetarian</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Oven baked or deep fried.</t>
         </is>
       </c>
-      <c r="E68" s="9" t="n">
+      <c r="E68" s="10" t="n">
         <v>15.95</v>
       </c>
-      <c r="F68" s="9" t="n"/>
-      <c r="G68" s="9" t="n"/>
-      <c r="H68" s="9" t="n"/>
-      <c r="I68" s="9" t="inlineStr"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="inlineStr"/>
+      <c r="J68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>wraps-pockets/Pocket — Donair or Steak</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>Wraps &amp; Pockets</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>Pocket — Donair or Steak</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>Oven baked or deep fried.</t>
         </is>
       </c>
-      <c r="E69" s="9" t="n">
+      <c r="E69" s="10" t="n">
         <v>16.45</v>
       </c>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
-      <c r="I69" s="9" t="inlineStr"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>pocket</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>chicken/Chicken &amp; Chips — 1 pc</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>Chicken &amp; Chips — 1 pc</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="9" t="n">
+      <c r="D70" s="10" t="inlineStr"/>
+      <c r="E70" s="10" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="9" t="n"/>
-      <c r="I70" s="9" t="inlineStr"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="inlineStr"/>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>fried-chicken</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>chicken/Chicken &amp; Chips — 2 pc</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>Chicken &amp; Chips — 2 pc</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr"/>
-      <c r="E71" s="9" t="n">
+      <c r="D71" s="10" t="inlineStr"/>
+      <c r="E71" s="10" t="n">
         <v>12.45</v>
       </c>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
-      <c r="H71" s="9" t="n"/>
-      <c r="I71" s="9" t="inlineStr"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="inlineStr"/>
+      <c r="J71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>chicken/Chicken &amp; Chips — 3 pc</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>Chicken &amp; Chips — 3 pc</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="n">
+      <c r="D72" s="10" t="inlineStr"/>
+      <c r="E72" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="F72" s="9" t="n"/>
-      <c r="G72" s="9" t="n"/>
-      <c r="H72" s="9" t="n"/>
-      <c r="I72" s="9" t="inlineStr"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="inlineStr"/>
+      <c r="J72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>chicken/Extra Piece of Chicken</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>Extra Piece of Chicken</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr"/>
-      <c r="E73" s="9" t="n">
+      <c r="D73" s="10" t="inlineStr"/>
+      <c r="E73" s="10" t="n">
         <v>3.75</v>
       </c>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="inlineStr"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="inlineStr"/>
+      <c r="J73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>chicken/2 Chicken Legs &amp; Chips</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>2 Chicken Legs &amp; Chips</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>Everyday special.</t>
         </is>
       </c>
-      <c r="E74" s="9" t="n">
+      <c r="E74" s="10" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
-      <c r="H74" s="9" t="n"/>
-      <c r="I74" s="9" t="inlineStr"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="10" t="inlineStr"/>
+      <c r="J74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>chicken/Chicken Family Pack</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>Chicken Family Pack</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>10 pieces, 2 large fries, gravy and coleslaw.</t>
         </is>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="E75" s="10" t="n">
         <v>39.95</v>
       </c>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="inlineStr"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="inlineStr"/>
+      <c r="J75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>chicken/6 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>6 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr"/>
-      <c r="E76" s="9" t="n">
+      <c r="D76" s="10" t="inlineStr"/>
+      <c r="E76" s="10" t="n">
         <v>7.95</v>
       </c>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
-      <c r="H76" s="9" t="n"/>
-      <c r="I76" s="9" t="inlineStr"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="inlineStr"/>
+      <c r="J76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>chicken/12 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>12 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="n">
+      <c r="D77" s="10" t="inlineStr"/>
+      <c r="E77" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="9" t="n"/>
-      <c r="H77" s="9" t="n"/>
-      <c r="I77" s="9" t="inlineStr"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="inlineStr"/>
+      <c r="J77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>chicken/5 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>5 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr"/>
-      <c r="E78" s="9" t="n">
+      <c r="D78" s="10" t="inlineStr"/>
+      <c r="E78" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="F78" s="9" t="n"/>
-      <c r="G78" s="9" t="n"/>
-      <c r="H78" s="9" t="n"/>
-      <c r="I78" s="9" t="inlineStr"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="inlineStr"/>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>chicken-fingers</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>chicken/10 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>Chicken</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>10 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="n">
+      <c r="D79" s="10" t="inlineStr"/>
+      <c r="E79" s="10" t="n">
         <v>26.45</v>
       </c>
-      <c r="F79" s="9" t="n"/>
-      <c r="G79" s="9" t="n"/>
-      <c r="H79" s="9" t="n"/>
-      <c r="I79" s="9" t="inlineStr"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="inlineStr"/>
+      <c r="J79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>salads-pasta/Caesar or Garden Salad</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>Salads &amp; Pasta</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>Caesar or Garden Salad</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="n">
+      <c r="D80" s="10" t="inlineStr"/>
+      <c r="E80" s="10" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="9" t="n"/>
-      <c r="I80" s="9" t="inlineStr"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="inlineStr"/>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>salad</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>salads-pasta/Greek Salad</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>Salads &amp; Pasta</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>Greek Salad</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="n">
+      <c r="D81" s="10" t="inlineStr"/>
+      <c r="E81" s="10" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="F81" s="9" t="n"/>
-      <c r="G81" s="9" t="n"/>
-      <c r="H81" s="9" t="n"/>
-      <c r="I81" s="9" t="inlineStr"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="inlineStr"/>
+      <c r="J81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>salads-pasta/Add Chicken — Crispy or Grilled</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>Salads &amp; Pasta</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>Add Chicken — Crispy or Grilled</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr"/>
-      <c r="E82" s="9" t="n">
+      <c r="D82" s="10" t="inlineStr"/>
+      <c r="E82" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="F82" s="9" t="n"/>
-      <c r="G82" s="9" t="n"/>
-      <c r="H82" s="9" t="n"/>
-      <c r="I82" s="9" t="inlineStr"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="10" t="inlineStr"/>
+      <c r="J82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>salads-pasta/Lasagna with Garlic Bread</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>Salads &amp; Pasta</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>Lasagna with Garlic Bread</t>
         </is>
       </c>
-      <c r="D83" s="9" t="inlineStr"/>
-      <c r="E83" s="9" t="n">
+      <c r="D83" s="10" t="inlineStr"/>
+      <c r="E83" s="10" t="n">
         <v>10.45</v>
       </c>
-      <c r="F83" s="9" t="n"/>
-      <c r="G83" s="9" t="n"/>
-      <c r="H83" s="9" t="n"/>
-      <c r="I83" s="9" t="inlineStr"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="inlineStr"/>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>lasagna</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>salads-pasta/Ravioli with Garlic Bread</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>Salads &amp; Pasta</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>Ravioli with Garlic Bread</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="n">
+      <c r="D84" s="10" t="inlineStr"/>
+      <c r="E84" s="10" t="n">
         <v>10.45</v>
       </c>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
-      <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9" t="inlineStr"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="inlineStr"/>
+      <c r="J84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>fish/Fish &amp; Chips — 1 pc</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips — 1 pc</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr"/>
-      <c r="E85" s="9" t="n">
+      <c r="D85" s="10" t="inlineStr"/>
+      <c r="E85" s="10" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
-      <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9" t="inlineStr"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>fish-and-chips</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>fish/Fish &amp; Chips — 2 pc</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips — 2 pc</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="n">
+      <c r="D86" s="10" t="inlineStr"/>
+      <c r="E86" s="10" t="n">
         <v>12.95</v>
       </c>
-      <c r="F86" s="9" t="n"/>
-      <c r="G86" s="9" t="n"/>
-      <c r="H86" s="9" t="n"/>
-      <c r="I86" s="9" t="inlineStr"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="10" t="n"/>
+      <c r="I86" s="10" t="inlineStr"/>
+      <c r="J86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>fish/Fish &amp; Chips — 3 pc</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips — 3 pc</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr"/>
-      <c r="E87" s="9" t="n">
+      <c r="D87" s="10" t="inlineStr"/>
+      <c r="E87" s="10" t="n">
         <v>14.95</v>
       </c>
-      <c r="F87" s="9" t="n"/>
-      <c r="G87" s="9" t="n"/>
-      <c r="H87" s="9" t="n"/>
-      <c r="I87" s="9" t="inlineStr"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>fish/Extra Piece of Fish</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>Extra Piece of Fish</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr"/>
-      <c r="E88" s="9" t="n">
+      <c r="D88" s="10" t="inlineStr"/>
+      <c r="E88" s="10" t="n">
         <v>3.95</v>
       </c>
-      <c r="F88" s="9" t="n"/>
-      <c r="G88" s="9" t="n"/>
-      <c r="H88" s="9" t="n"/>
-      <c r="I88" s="9" t="inlineStr"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="10" t="inlineStr"/>
+      <c r="J88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>fish/Fish Family Pack</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>Fish &amp; Chips</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>Fish Family Pack</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
         </is>
       </c>
-      <c r="E89" s="9" t="n">
+      <c r="E89" s="10" t="n">
         <v>39.95</v>
       </c>
-      <c r="F89" s="9" t="n"/>
-      <c r="G89" s="9" t="n"/>
-      <c r="H89" s="9" t="n"/>
-      <c r="I89" s="9" t="inlineStr"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="10" t="inlineStr"/>
+      <c r="J89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>seafood/Scallops &amp; Chips</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>More Seafood</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>Scallops &amp; Chips</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>10 scallops.</t>
         </is>
       </c>
-      <c r="E90" s="9" t="n">
+      <c r="E90" s="10" t="n">
         <v>13.45</v>
       </c>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-      <c r="I90" s="9" t="inlineStr"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="inlineStr"/>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>scallops</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>seafood/Clams &amp; Chips</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>More Seafood</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>Clams &amp; Chips</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D91" s="10" t="inlineStr">
         <is>
           <t>Two cups of clams.</t>
         </is>
       </c>
-      <c r="E91" s="9" t="n">
+      <c r="E91" s="10" t="n">
         <v>13.45</v>
       </c>
-      <c r="F91" s="9" t="n"/>
-      <c r="G91" s="9" t="n"/>
-      <c r="H91" s="9" t="n"/>
-      <c r="I91" s="9" t="inlineStr"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="inlineStr"/>
+      <c r="J91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>seafood/Shrimp &amp; Chips</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>More Seafood</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>Shrimp &amp; Chips</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>12 shrimp.</t>
         </is>
       </c>
-      <c r="E92" s="9" t="n">
+      <c r="E92" s="10" t="n">
         <v>13.45</v>
       </c>
-      <c r="F92" s="9" t="n"/>
-      <c r="G92" s="9" t="n"/>
-      <c r="H92" s="9" t="n"/>
-      <c r="I92" s="9" t="inlineStr"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="10" t="n"/>
+      <c r="I92" s="10" t="inlineStr"/>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>shrimp</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>seafood/Seafood Platter</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>More Seafood</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>Seafood Platter</t>
         </is>
       </c>
-      <c r="D93" s="9" t="inlineStr">
+      <c r="D93" s="10" t="inlineStr">
         <is>
           <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
         </is>
       </c>
-      <c r="E93" s="9" t="n">
+      <c r="E93" s="10" t="n">
         <v>17.45</v>
       </c>
-      <c r="F93" s="9" t="n"/>
-      <c r="G93" s="9" t="n"/>
-      <c r="H93" s="9" t="n"/>
-      <c r="I93" s="9" t="inlineStr"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="inlineStr"/>
+      <c r="J93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>seafood/Extra Coleslaw — Small</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>More Seafood</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>Extra Coleslaw — Small</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr"/>
-      <c r="E94" s="9" t="n">
+      <c r="D94" s="10" t="inlineStr"/>
+      <c r="E94" s="10" t="n">
         <v>1.75</v>
       </c>
-      <c r="F94" s="9" t="n"/>
-      <c r="G94" s="9" t="n"/>
-      <c r="H94" s="9" t="n"/>
-      <c r="I94" s="9" t="inlineStr"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="inlineStr"/>
+      <c r="J94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>seafood/Extra Coleslaw — Large</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>More Seafood</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C95" s="10" t="inlineStr">
         <is>
           <t>Extra Coleslaw — Large</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr"/>
-      <c r="E95" s="9" t="n">
+      <c r="D95" s="10" t="inlineStr"/>
+      <c r="E95" s="10" t="n">
         <v>2.95</v>
       </c>
-      <c r="F95" s="9" t="n"/>
-      <c r="G95" s="9" t="n"/>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="9" t="inlineStr"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="inlineStr"/>
+      <c r="J95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>subs/Cold Cut</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>Cold Cut</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr"/>
-      <c r="E96" s="9" t="n">
+      <c r="D96" s="10" t="inlineStr"/>
+      <c r="E96" s="10" t="n">
         <v>9.25</v>
       </c>
-      <c r="F96" s="9" t="n">
+      <c r="F96" s="10" t="n">
         <v>11.45</v>
       </c>
-      <c r="G96" s="9" t="n"/>
-      <c r="H96" s="9" t="n"/>
-      <c r="I96" s="9" t="inlineStr">
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>cold-cut-sub</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>subs/Salami &amp; Ham</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>Salami &amp; Ham</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr"/>
-      <c r="E97" s="9" t="n">
+      <c r="D97" s="10" t="inlineStr"/>
+      <c r="E97" s="10" t="n">
         <v>9.25</v>
       </c>
-      <c r="F97" s="9" t="n">
+      <c r="F97" s="10" t="n">
         <v>11.45</v>
       </c>
-      <c r="G97" s="9" t="n"/>
-      <c r="H97" s="9" t="n"/>
-      <c r="I97" s="9" t="inlineStr">
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>subs/Pizza Sub</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>Pizza Sub</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr"/>
-      <c r="E98" s="9" t="n">
+      <c r="D98" s="10" t="inlineStr"/>
+      <c r="E98" s="10" t="n">
         <v>9.25</v>
       </c>
-      <c r="F98" s="9" t="n">
+      <c r="F98" s="10" t="n">
         <v>11.45</v>
       </c>
-      <c r="G98" s="9" t="n"/>
-      <c r="H98" s="9" t="n"/>
-      <c r="I98" s="9" t="inlineStr">
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>subs/Vegetarian</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>Vegetarian</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr"/>
-      <c r="E99" s="9" t="n">
+      <c r="D99" s="10" t="inlineStr"/>
+      <c r="E99" s="10" t="n">
         <v>9.25</v>
       </c>
-      <c r="F99" s="9" t="n">
+      <c r="F99" s="10" t="n">
         <v>11.45</v>
       </c>
-      <c r="G99" s="9" t="n"/>
-      <c r="H99" s="9" t="n"/>
-      <c r="I99" s="9" t="inlineStr">
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>subs/Real Turkey</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>Real Turkey</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr"/>
-      <c r="E100" s="9" t="n">
+      <c r="D100" s="10" t="inlineStr"/>
+      <c r="E100" s="10" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="F100" s="9" t="n">
+      <c r="F100" s="10" t="n">
         <v>11.45</v>
       </c>
-      <c r="G100" s="9" t="n"/>
-      <c r="H100" s="9" t="n"/>
-      <c r="I100" s="9" t="inlineStr">
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>subs/Bubba</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>Bubba</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>The one people ask for by name.</t>
         </is>
       </c>
-      <c r="E101" s="9" t="n">
+      <c r="E101" s="10" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="F101" s="9" t="n">
+      <c r="F101" s="10" t="n">
         <v>12.75</v>
       </c>
-      <c r="G101" s="9" t="n"/>
-      <c r="H101" s="9" t="n"/>
-      <c r="I101" s="9" t="inlineStr">
+      <c r="G101" s="10" t="n"/>
+      <c r="H101" s="10" t="n"/>
+      <c r="I101" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>subs/Club</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>Club</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr"/>
-      <c r="E102" s="9" t="n">
+      <c r="D102" s="10" t="inlineStr"/>
+      <c r="E102" s="10" t="n">
         <v>10.25</v>
       </c>
-      <c r="F102" s="9" t="n">
+      <c r="F102" s="10" t="n">
         <v>12.75</v>
       </c>
-      <c r="G102" s="9" t="n"/>
-      <c r="H102" s="9" t="n"/>
-      <c r="I102" s="9" t="inlineStr">
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>subs/Steak</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>Steak</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr"/>
-      <c r="E103" s="9" t="n">
+      <c r="D103" s="10" t="inlineStr"/>
+      <c r="E103" s="10" t="n">
         <v>10.25</v>
       </c>
-      <c r="F103" s="9" t="n">
+      <c r="F103" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="G103" s="9" t="n"/>
-      <c r="H103" s="9" t="n"/>
-      <c r="I103" s="9" t="inlineStr">
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>steak-sub</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>subs/Donair Sub</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>Donair Sub</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="9" t="n">
+      <c r="D104" s="10" t="inlineStr"/>
+      <c r="E104" s="10" t="n">
         <v>10.25</v>
       </c>
-      <c r="F104" s="9" t="n">
+      <c r="F104" s="10" t="n">
         <v>13.25</v>
       </c>
-      <c r="G104" s="9" t="n"/>
-      <c r="H104" s="9" t="n"/>
-      <c r="I104" s="9" t="inlineStr">
+      <c r="G104" s="10" t="n"/>
+      <c r="H104" s="10" t="n"/>
+      <c r="I104" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>subs/Super Sub</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>Super Sub</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="9" t="n">
+      <c r="D105" s="10" t="inlineStr"/>
+      <c r="E105" s="10" t="n">
         <v>10.95</v>
       </c>
-      <c r="F105" s="9" t="n">
+      <c r="F105" s="10" t="n">
         <v>14.75</v>
       </c>
-      <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="inlineStr">
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>subs/Garlic Bread</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>Garlic Bread</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr"/>
-      <c r="E106" s="9" t="n">
+      <c r="D106" s="10" t="inlineStr"/>
+      <c r="E106" s="10" t="n">
         <v>4.95</v>
       </c>
-      <c r="F106" s="9" t="n">
+      <c r="F106" s="10" t="n">
         <v>5.95</v>
       </c>
-      <c r="G106" s="9" t="n"/>
-      <c r="H106" s="9" t="n"/>
-      <c r="I106" s="9" t="inlineStr">
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>subs/Extra Cheese</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>Extra Cheese</t>
         </is>
       </c>
-      <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="n">
+      <c r="D107" s="10" t="inlineStr"/>
+      <c r="E107" s="10" t="n">
         <v>2.45</v>
       </c>
-      <c r="F107" s="9" t="n">
+      <c r="F107" s="10" t="n">
         <v>3.45</v>
       </c>
-      <c r="G107" s="9" t="n"/>
-      <c r="H107" s="9" t="n"/>
-      <c r="I107" s="9" t="inlineStr">
+      <c r="G107" s="10" t="n"/>
+      <c r="H107" s="10" t="n"/>
+      <c r="I107" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>subs/Extra Meat</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>Subs</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>Extra Meat</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr"/>
-      <c r="E108" s="9" t="n">
+      <c r="D108" s="10" t="inlineStr"/>
+      <c r="E108" s="10" t="n">
         <v>3.45</v>
       </c>
-      <c r="F108" s="9" t="n">
+      <c r="F108" s="10" t="n">
         <v>4.45</v>
       </c>
-      <c r="G108" s="9" t="n"/>
-      <c r="H108" s="9" t="n"/>
-      <c r="I108" s="9" t="inlineStr">
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>burritos/Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="n">
+      <c r="D109" s="10" t="inlineStr"/>
+      <c r="E109" s="10" t="n">
         <v>7.99</v>
       </c>
-      <c r="F109" s="9" t="n">
+      <c r="F109" s="10" t="n">
         <v>8.99</v>
       </c>
-      <c r="G109" s="9" t="n">
+      <c r="G109" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="H109" s="9" t="n"/>
-      <c r="I109" s="9" t="inlineStr">
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>burritos/Spicy Chicken</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>Spicy Chicken</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr"/>
-      <c r="E110" s="9" t="n">
+      <c r="D110" s="10" t="inlineStr"/>
+      <c r="E110" s="10" t="n">
         <v>9.99</v>
       </c>
-      <c r="F110" s="9" t="n">
+      <c r="F110" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="G110" s="9" t="n">
+      <c r="G110" s="10" t="n">
         <v>12.99</v>
       </c>
-      <c r="H110" s="9" t="n"/>
-      <c r="I110" s="9" t="inlineStr">
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J110" s="10" t="inlineStr">
+        <is>
+          <t>burrito</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="inlineStr">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>burritos/Ground Beef</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>Ground Beef</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr"/>
-      <c r="E111" s="9" t="n">
+      <c r="D111" s="10" t="inlineStr"/>
+      <c r="E111" s="10" t="n">
         <v>9.99</v>
       </c>
-      <c r="F111" s="9" t="n">
+      <c r="F111" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="G111" s="9" t="n">
+      <c r="G111" s="10" t="n">
         <v>12.99</v>
       </c>
-      <c r="H111" s="9" t="n"/>
-      <c r="I111" s="9" t="inlineStr">
+      <c r="H111" s="10" t="n"/>
+      <c r="I111" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>burritos/Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr"/>
-      <c r="E112" s="9" t="n">
+      <c r="D112" s="10" t="inlineStr"/>
+      <c r="E112" s="10" t="n">
         <v>9.99</v>
       </c>
-      <c r="F112" s="9" t="n">
+      <c r="F112" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="G112" s="9" t="n">
+      <c r="G112" s="10" t="n">
         <v>12.99</v>
       </c>
-      <c r="H112" s="9" t="n"/>
-      <c r="I112" s="9" t="inlineStr">
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>burritos/Fish</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>Fish</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr"/>
-      <c r="E113" s="9" t="n">
+      <c r="D113" s="10" t="inlineStr"/>
+      <c r="E113" s="10" t="n">
         <v>9.99</v>
       </c>
-      <c r="F113" s="9" t="n">
+      <c r="F113" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="G113" s="9" t="n">
+      <c r="G113" s="10" t="n">
         <v>12.99</v>
       </c>
-      <c r="H113" s="9" t="n"/>
-      <c r="I113" s="9" t="inlineStr">
+      <c r="H113" s="10" t="n"/>
+      <c r="I113" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>burritos/Shawarma Chicken</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>Shawarma Chicken</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr"/>
-      <c r="E114" s="9" t="n">
+      <c r="D114" s="10" t="inlineStr"/>
+      <c r="E114" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F114" s="9" t="n">
+      <c r="F114" s="10" t="n">
         <v>11.99</v>
       </c>
-      <c r="G114" s="9" t="n">
+      <c r="G114" s="10" t="n">
         <v>13.99</v>
       </c>
-      <c r="H114" s="9" t="n"/>
-      <c r="I114" s="9" t="inlineStr">
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>burritos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="B115" s="9" t="inlineStr">
+      <c r="B115" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C115" s="9" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="D115" s="9" t="inlineStr"/>
-      <c r="E115" s="9" t="n">
+      <c r="D115" s="10" t="inlineStr"/>
+      <c r="E115" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F115" s="9" t="n">
+      <c r="F115" s="10" t="n">
         <v>11.99</v>
       </c>
-      <c r="G115" s="9" t="n">
+      <c r="G115" s="10" t="n">
         <v>13.99</v>
       </c>
-      <c r="H115" s="9" t="n"/>
-      <c r="I115" s="9" t="inlineStr">
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>burritos/Steak</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" s="10" t="inlineStr">
         <is>
           <t>Burritos</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>Steak</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr"/>
-      <c r="E116" s="9" t="n">
+      <c r="D116" s="10" t="inlineStr"/>
+      <c r="E116" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F116" s="9" t="n">
+      <c r="F116" s="10" t="n">
         <v>11.99</v>
       </c>
-      <c r="G116" s="9" t="n">
+      <c r="G116" s="10" t="n">
         <v>13.99</v>
       </c>
-      <c r="H116" s="9" t="n"/>
-      <c r="I116" s="9" t="inlineStr">
+      <c r="H116" s="10" t="n"/>
+      <c r="I116" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large</t>
         </is>
       </c>
+      <c r="J116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr"/>
-      <c r="E117" s="9" t="n">
+      <c r="D117" s="10" t="inlineStr"/>
+      <c r="E117" s="10" t="n">
         <v>10.49</v>
       </c>
-      <c r="F117" s="9" t="n">
+      <c r="F117" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="G117" s="9" t="n"/>
-      <c r="H117" s="9" t="n"/>
-      <c r="I117" s="9" t="inlineStr">
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>rice-bowl</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Spicy Chicken</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>Spicy Chicken</t>
         </is>
       </c>
-      <c r="D118" s="9" t="inlineStr"/>
-      <c r="E118" s="9" t="n">
+      <c r="D118" s="10" t="inlineStr"/>
+      <c r="E118" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F118" s="9" t="n">
+      <c r="F118" s="10" t="n">
         <v>13.49</v>
       </c>
-      <c r="G118" s="9" t="n"/>
-      <c r="H118" s="9" t="n"/>
-      <c r="I118" s="9" t="inlineStr">
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Ground Beef</t>
         </is>
       </c>
-      <c r="B119" s="9" t="inlineStr">
+      <c r="B119" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>Ground Beef</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr"/>
-      <c r="E119" s="9" t="n">
+      <c r="D119" s="10" t="inlineStr"/>
+      <c r="E119" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F119" s="9" t="n">
+      <c r="F119" s="10" t="n">
         <v>13.49</v>
       </c>
-      <c r="G119" s="9" t="n"/>
-      <c r="H119" s="9" t="n"/>
-      <c r="I119" s="9" t="inlineStr">
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr"/>
-      <c r="E120" s="9" t="n">
+      <c r="D120" s="10" t="inlineStr"/>
+      <c r="E120" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F120" s="9" t="n">
+      <c r="F120" s="10" t="n">
         <v>13.49</v>
       </c>
-      <c r="G120" s="9" t="n"/>
-      <c r="H120" s="9" t="n"/>
-      <c r="I120" s="9" t="inlineStr">
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="inlineStr">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Fish</t>
         </is>
       </c>
-      <c r="B121" s="9" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C121" s="9" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>Fish</t>
         </is>
       </c>
-      <c r="D121" s="9" t="inlineStr"/>
-      <c r="E121" s="9" t="n">
+      <c r="D121" s="10" t="inlineStr"/>
+      <c r="E121" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F121" s="9" t="n">
+      <c r="F121" s="10" t="n">
         <v>13.49</v>
       </c>
-      <c r="G121" s="9" t="n"/>
-      <c r="H121" s="9" t="n"/>
-      <c r="I121" s="9" t="inlineStr">
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Shawarma Chicken</t>
         </is>
       </c>
-      <c r="B122" s="9" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C122" s="9" t="inlineStr">
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>Shawarma Chicken</t>
         </is>
       </c>
-      <c r="D122" s="9" t="inlineStr"/>
-      <c r="E122" s="9" t="n">
+      <c r="D122" s="10" t="inlineStr"/>
+      <c r="E122" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="F122" s="9" t="n">
+      <c r="F122" s="10" t="n">
         <v>14.49</v>
       </c>
-      <c r="G122" s="9" t="n"/>
-      <c r="H122" s="9" t="n"/>
-      <c r="I122" s="9" t="inlineStr">
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="10" t="n"/>
+      <c r="I122" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="B123" s="9" t="inlineStr">
+      <c r="B123" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C123" s="9" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="D123" s="9" t="inlineStr"/>
-      <c r="E123" s="9" t="n">
+      <c r="D123" s="10" t="inlineStr"/>
+      <c r="E123" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="F123" s="9" t="n">
+      <c r="F123" s="10" t="n">
         <v>14.49</v>
       </c>
-      <c r="G123" s="9" t="n"/>
-      <c r="H123" s="9" t="n"/>
-      <c r="I123" s="9" t="inlineStr">
+      <c r="G123" s="10" t="n"/>
+      <c r="H123" s="10" t="n"/>
+      <c r="I123" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>rice-bowls/Steak</t>
         </is>
       </c>
-      <c r="B124" s="9" t="inlineStr">
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>Rice Bowls</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>Steak</t>
         </is>
       </c>
-      <c r="D124" s="9" t="inlineStr"/>
-      <c r="E124" s="9" t="n">
+      <c r="D124" s="10" t="inlineStr"/>
+      <c r="E124" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="F124" s="9" t="n">
+      <c r="F124" s="10" t="n">
         <v>14.49</v>
       </c>
-      <c r="G124" s="9" t="n"/>
-      <c r="H124" s="9" t="n"/>
-      <c r="I124" s="9" t="inlineStr">
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="10" t="n"/>
+      <c r="I124" s="10" t="inlineStr">
         <is>
           <t>Small / Large</t>
         </is>
       </c>
+      <c r="J124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="D125" s="9" t="inlineStr"/>
-      <c r="E125" s="9" t="n">
+      <c r="D125" s="10" t="inlineStr"/>
+      <c r="E125" s="10" t="n">
         <v>10.49</v>
       </c>
-      <c r="F125" s="9" t="n"/>
-      <c r="G125" s="9" t="n"/>
-      <c r="H125" s="9" t="n"/>
-      <c r="I125" s="9" t="inlineStr"/>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
+      <c r="H125" s="10" t="n"/>
+      <c r="I125" s="10" t="inlineStr"/>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>quesadilla</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Spicy Chicken</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>Spicy Chicken</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr"/>
-      <c r="E126" s="9" t="n">
+      <c r="D126" s="10" t="inlineStr"/>
+      <c r="E126" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F126" s="9" t="n"/>
-      <c r="G126" s="9" t="n"/>
-      <c r="H126" s="9" t="n"/>
-      <c r="I126" s="9" t="inlineStr"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="10" t="n"/>
+      <c r="I126" s="10" t="inlineStr"/>
+      <c r="J126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Ground Beef</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>Ground Beef</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr"/>
-      <c r="E127" s="9" t="n">
+      <c r="D127" s="10" t="inlineStr"/>
+      <c r="E127" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F127" s="9" t="n"/>
-      <c r="G127" s="9" t="n"/>
-      <c r="H127" s="9" t="n"/>
-      <c r="I127" s="9" t="inlineStr"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
+      <c r="H127" s="10" t="n"/>
+      <c r="I127" s="10" t="inlineStr"/>
+      <c r="J127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr"/>
-      <c r="E128" s="9" t="n">
+      <c r="D128" s="10" t="inlineStr"/>
+      <c r="E128" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F128" s="9" t="n"/>
-      <c r="G128" s="9" t="n"/>
-      <c r="H128" s="9" t="n"/>
-      <c r="I128" s="9" t="inlineStr"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="10" t="n"/>
+      <c r="I128" s="10" t="inlineStr"/>
+      <c r="J128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Fish</t>
         </is>
       </c>
-      <c r="B129" s="9" t="inlineStr">
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C129" s="9" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>Fish</t>
         </is>
       </c>
-      <c r="D129" s="9" t="inlineStr"/>
-      <c r="E129" s="9" t="n">
+      <c r="D129" s="10" t="inlineStr"/>
+      <c r="E129" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F129" s="9" t="n"/>
-      <c r="G129" s="9" t="n"/>
-      <c r="H129" s="9" t="n"/>
-      <c r="I129" s="9" t="inlineStr"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
+      <c r="H129" s="10" t="n"/>
+      <c r="I129" s="10" t="inlineStr"/>
+      <c r="J129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="inlineStr">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Shawarma Chicken</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>Shawarma Chicken</t>
         </is>
       </c>
-      <c r="D130" s="9" t="inlineStr"/>
-      <c r="E130" s="9" t="n">
+      <c r="D130" s="10" t="inlineStr"/>
+      <c r="E130" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="F130" s="9" t="n"/>
-      <c r="G130" s="9" t="n"/>
-      <c r="H130" s="9" t="n"/>
-      <c r="I130" s="9" t="inlineStr"/>
+      <c r="F130" s="10" t="n"/>
+      <c r="G130" s="10" t="n"/>
+      <c r="H130" s="10" t="n"/>
+      <c r="I130" s="10" t="inlineStr"/>
+      <c r="J130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="B131" s="9" t="inlineStr">
+      <c r="B131" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C131" s="9" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="D131" s="9" t="inlineStr"/>
-      <c r="E131" s="9" t="n">
+      <c r="D131" s="10" t="inlineStr"/>
+      <c r="E131" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="F131" s="9" t="n"/>
-      <c r="G131" s="9" t="n"/>
-      <c r="H131" s="9" t="n"/>
-      <c r="I131" s="9" t="inlineStr"/>
+      <c r="F131" s="10" t="n"/>
+      <c r="G131" s="10" t="n"/>
+      <c r="H131" s="10" t="n"/>
+      <c r="I131" s="10" t="inlineStr"/>
+      <c r="J131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="inlineStr">
+      <c r="A132" s="9" t="inlineStr">
         <is>
           <t>quesadillas/Steak</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>Quesadillas</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>Steak</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr"/>
-      <c r="E132" s="9" t="n">
+      <c r="D132" s="10" t="inlineStr"/>
+      <c r="E132" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="F132" s="9" t="n"/>
-      <c r="G132" s="9" t="n"/>
-      <c r="H132" s="9" t="n"/>
-      <c r="I132" s="9" t="inlineStr"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="10" t="inlineStr"/>
+      <c r="J132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>tacos/Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="B133" s="9" t="inlineStr">
+      <c r="B133" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>Beans &amp; Veggie</t>
         </is>
       </c>
-      <c r="D133" s="9" t="inlineStr"/>
-      <c r="E133" s="9" t="n">
+      <c r="D133" s="10" t="inlineStr"/>
+      <c r="E133" s="10" t="n">
         <v>9.99</v>
       </c>
-      <c r="F133" s="9" t="n"/>
-      <c r="G133" s="9" t="n"/>
-      <c r="H133" s="9" t="n"/>
-      <c r="I133" s="9" t="inlineStr"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="10" t="inlineStr"/>
+      <c r="J133" s="10" t="inlineStr">
+        <is>
+          <t>tacos</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>tacos/Spicy Chicken</t>
         </is>
       </c>
-      <c r="B134" s="9" t="inlineStr">
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>Spicy Chicken</t>
         </is>
       </c>
-      <c r="D134" s="9" t="inlineStr"/>
-      <c r="E134" s="9" t="n">
+      <c r="D134" s="10" t="inlineStr"/>
+      <c r="E134" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F134" s="9" t="n"/>
-      <c r="G134" s="9" t="n"/>
-      <c r="H134" s="9" t="n"/>
-      <c r="I134" s="9" t="inlineStr"/>
+      <c r="F134" s="10" t="n"/>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="10" t="n"/>
+      <c r="I134" s="10" t="inlineStr"/>
+      <c r="J134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>tacos/Ground Beef</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="B135" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="C135" s="10" t="inlineStr">
         <is>
           <t>Ground Beef</t>
         </is>
       </c>
-      <c r="D135" s="9" t="inlineStr"/>
-      <c r="E135" s="9" t="n">
+      <c r="D135" s="10" t="inlineStr"/>
+      <c r="E135" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F135" s="9" t="n"/>
-      <c r="G135" s="9" t="n"/>
-      <c r="H135" s="9" t="n"/>
-      <c r="I135" s="9" t="inlineStr"/>
+      <c r="F135" s="10" t="n"/>
+      <c r="G135" s="10" t="n"/>
+      <c r="H135" s="10" t="n"/>
+      <c r="I135" s="10" t="inlineStr"/>
+      <c r="J135" s="10" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="A136" s="9" t="inlineStr">
         <is>
           <t>tacos/Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="B136" s="9" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="C136" s="10" t="inlineStr">
         <is>
           <t>Zesty Grilled Chicken</t>
         </is>
       </c>
-      <c r="D136" s="9" t="inlineStr"/>
-      <c r="E136" s="9" t="n">
+      <c r="D136" s="10" t="inlineStr"/>
+      <c r="E136" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F136" s="9" t="n"/>
-      <c r="G136" s="9" t="n"/>
-      <c r="H136" s="9" t="n"/>
-      <c r="I136" s="9" t="inlineStr"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="10" t="n"/>
+      <c r="I136" s="10" t="inlineStr"/>
+      <c r="J136" s="10" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>tacos/Fish</t>
         </is>
       </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>Fish</t>
         </is>
       </c>
-      <c r="D137" s="9" t="inlineStr"/>
-      <c r="E137" s="9" t="n">
+      <c r="D137" s="10" t="inlineStr"/>
+      <c r="E137" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F137" s="9" t="n"/>
-      <c r="G137" s="9" t="n"/>
-      <c r="H137" s="9" t="n"/>
-      <c r="I137" s="9" t="inlineStr"/>
+      <c r="F137" s="10" t="n"/>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="10" t="n"/>
+      <c r="I137" s="10" t="inlineStr"/>
+      <c r="J137" s="10" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="inlineStr">
+      <c r="A138" s="9" t="inlineStr">
         <is>
           <t>tacos/Shawarma Chicken</t>
         </is>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>Shawarma Chicken</t>
         </is>
       </c>
-      <c r="D138" s="9" t="inlineStr"/>
-      <c r="E138" s="9" t="n">
+      <c r="D138" s="10" t="inlineStr"/>
+      <c r="E138" s="10" t="n">
         <v>11.99</v>
       </c>
-      <c r="F138" s="9" t="n"/>
-      <c r="G138" s="9" t="n"/>
-      <c r="H138" s="9" t="n"/>
-      <c r="I138" s="9" t="inlineStr"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="n"/>
+      <c r="I138" s="10" t="inlineStr"/>
+      <c r="J138" s="10" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="inlineStr">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>tacos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="B139" s="9" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C139" s="9" t="inlineStr">
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
-      <c r="D139" s="9" t="inlineStr"/>
-      <c r="E139" s="9" t="n">
+      <c r="D139" s="10" t="inlineStr"/>
+      <c r="E139" s="10" t="n">
         <v>11.99</v>
       </c>
-      <c r="F139" s="9" t="n"/>
-      <c r="G139" s="9" t="n"/>
-      <c r="H139" s="9" t="n"/>
-      <c r="I139" s="9" t="inlineStr"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="n"/>
+      <c r="I139" s="10" t="inlineStr"/>
+      <c r="J139" s="10" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>tacos/Steak</t>
         </is>
       </c>
-      <c r="B140" s="9" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>Tacos</t>
         </is>
       </c>
-      <c r="C140" s="9" t="inlineStr">
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>Steak</t>
         </is>
       </c>
-      <c r="D140" s="9" t="inlineStr"/>
-      <c r="E140" s="9" t="n">
+      <c r="D140" s="10" t="inlineStr"/>
+      <c r="E140" s="10" t="n">
         <v>11.99</v>
       </c>
-      <c r="F140" s="9" t="n"/>
-      <c r="G140" s="9" t="n"/>
-      <c r="H140" s="9" t="n"/>
-      <c r="I140" s="9" t="inlineStr"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="10" t="n"/>
+      <c r="I140" s="10" t="inlineStr"/>
+      <c r="J140" s="10" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="A141" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Chips &amp; Salsa — Small</t>
         </is>
       </c>
-      <c r="B141" s="9" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C141" s="9" t="inlineStr">
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>Chips &amp; Salsa — Small</t>
         </is>
       </c>
-      <c r="D141" s="9" t="inlineStr"/>
-      <c r="E141" s="9" t="n">
+      <c r="D141" s="10" t="inlineStr"/>
+      <c r="E141" s="10" t="n">
         <v>2.49</v>
       </c>
-      <c r="F141" s="9" t="n"/>
-      <c r="G141" s="9" t="n"/>
-      <c r="H141" s="9" t="n"/>
-      <c r="I141" s="9" t="inlineStr"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="n"/>
+      <c r="I141" s="10" t="inlineStr"/>
+      <c r="J141" s="10" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="inlineStr">
+      <c r="A142" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Chips &amp; Salsa — Large</t>
         </is>
       </c>
-      <c r="B142" s="9" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C142" s="9" t="inlineStr">
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>Chips &amp; Salsa — Large</t>
         </is>
       </c>
-      <c r="D142" s="9" t="inlineStr"/>
-      <c r="E142" s="9" t="n">
+      <c r="D142" s="10" t="inlineStr"/>
+      <c r="E142" s="10" t="n">
         <v>4.49</v>
       </c>
-      <c r="F142" s="9" t="n"/>
-      <c r="G142" s="9" t="n"/>
-      <c r="H142" s="9" t="n"/>
-      <c r="I142" s="9" t="inlineStr"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="n"/>
+      <c r="I142" s="10" t="inlineStr"/>
+      <c r="J142" s="10" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="A143" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Chips &amp; Queso — Small</t>
         </is>
       </c>
-      <c r="B143" s="9" t="inlineStr">
+      <c r="B143" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C143" s="10" t="inlineStr">
         <is>
           <t>Chips &amp; Queso — Small</t>
         </is>
       </c>
-      <c r="D143" s="9" t="inlineStr"/>
-      <c r="E143" s="9" t="n">
+      <c r="D143" s="10" t="inlineStr"/>
+      <c r="E143" s="10" t="n">
         <v>3.49</v>
       </c>
-      <c r="F143" s="9" t="n"/>
-      <c r="G143" s="9" t="n"/>
-      <c r="H143" s="9" t="n"/>
-      <c r="I143" s="9" t="inlineStr"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="n"/>
+      <c r="I143" s="10" t="inlineStr"/>
+      <c r="J143" s="10" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Chips &amp; Queso — Large</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr">
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C144" s="10" t="inlineStr">
         <is>
           <t>Chips &amp; Queso — Large</t>
         </is>
       </c>
-      <c r="D144" s="9" t="inlineStr"/>
-      <c r="E144" s="9" t="n">
+      <c r="D144" s="10" t="inlineStr"/>
+      <c r="E144" s="10" t="n">
         <v>6.49</v>
       </c>
-      <c r="F144" s="9" t="n"/>
-      <c r="G144" s="9" t="n"/>
-      <c r="H144" s="9" t="n"/>
-      <c r="I144" s="9" t="inlineStr"/>
+      <c r="F144" s="10" t="n"/>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="10" t="n"/>
+      <c r="I144" s="10" t="inlineStr"/>
+      <c r="J144" s="10" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Chips &amp; Guac — Small</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C145" s="10" t="inlineStr">
         <is>
           <t>Chips &amp; Guac — Small</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr"/>
-      <c r="E145" s="9" t="n">
+      <c r="D145" s="10" t="inlineStr"/>
+      <c r="E145" s="10" t="n">
         <v>3.99</v>
       </c>
-      <c r="F145" s="9" t="n"/>
-      <c r="G145" s="9" t="n"/>
-      <c r="H145" s="9" t="n"/>
-      <c r="I145" s="9" t="inlineStr"/>
+      <c r="F145" s="10" t="n"/>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="10" t="inlineStr"/>
+      <c r="J145" s="10" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="A146" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Chips &amp; Guac — Large</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>Chips &amp; Guac — Large</t>
         </is>
       </c>
-      <c r="D146" s="9" t="inlineStr"/>
-      <c r="E146" s="9" t="n">
+      <c r="D146" s="10" t="inlineStr"/>
+      <c r="E146" s="10" t="n">
         <v>6.99</v>
       </c>
-      <c r="F146" s="9" t="n"/>
-      <c r="G146" s="9" t="n"/>
-      <c r="H146" s="9" t="n"/>
-      <c r="I146" s="9" t="inlineStr"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+      <c r="I146" s="10" t="inlineStr"/>
+      <c r="J146" s="10" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="A147" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Fries Supreme</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>Fries Supreme</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr"/>
-      <c r="E147" s="9" t="n">
+      <c r="D147" s="10" t="inlineStr"/>
+      <c r="E147" s="10" t="n">
         <v>9.99</v>
       </c>
-      <c r="F147" s="9" t="n"/>
-      <c r="G147" s="9" t="n"/>
-      <c r="H147" s="9" t="n"/>
-      <c r="I147" s="9" t="inlineStr"/>
+      <c r="F147" s="10" t="n"/>
+      <c r="G147" s="10" t="n"/>
+      <c r="H147" s="10" t="n"/>
+      <c r="I147" s="10" t="inlineStr"/>
+      <c r="J147" s="10" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="A148" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Spicy Fries</t>
         </is>
       </c>
-      <c r="B148" s="9" t="inlineStr">
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C148" s="9" t="inlineStr">
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>Spicy Fries</t>
         </is>
       </c>
-      <c r="D148" s="9" t="inlineStr"/>
-      <c r="E148" s="9" t="n">
+      <c r="D148" s="10" t="inlineStr"/>
+      <c r="E148" s="10" t="n">
         <v>8.99</v>
       </c>
-      <c r="F148" s="9" t="n"/>
-      <c r="G148" s="9" t="n"/>
-      <c r="H148" s="9" t="n"/>
-      <c r="I148" s="9" t="inlineStr"/>
+      <c r="F148" s="10" t="n"/>
+      <c r="G148" s="10" t="n"/>
+      <c r="H148" s="10" t="n"/>
+      <c r="I148" s="10" t="inlineStr"/>
+      <c r="J148" s="10" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="inlineStr">
+      <c r="A149" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Deep Fried Pepperoni</t>
         </is>
       </c>
-      <c r="B149" s="9" t="inlineStr">
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C149" s="9" t="inlineStr">
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>Deep Fried Pepperoni</t>
         </is>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D149" s="10" t="inlineStr">
         <is>
           <t>With honey mustard sauce.</t>
         </is>
       </c>
-      <c r="E149" s="9" t="n">
+      <c r="E149" s="10" t="n">
         <v>12.99</v>
       </c>
-      <c r="F149" s="9" t="n"/>
-      <c r="G149" s="9" t="n"/>
-      <c r="H149" s="9" t="n"/>
-      <c r="I149" s="9" t="inlineStr"/>
+      <c r="F149" s="10" t="n"/>
+      <c r="G149" s="10" t="n"/>
+      <c r="H149" s="10" t="n"/>
+      <c r="I149" s="10" t="inlineStr"/>
+      <c r="J149" s="10" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="inlineStr">
+      <c r="A150" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
         </is>
       </c>
-      <c r="B150" s="9" t="inlineStr">
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>Add Chips &amp; Salsa + a Can of Pop</t>
         </is>
       </c>
-      <c r="D150" s="9" t="inlineStr"/>
-      <c r="E150" s="9" t="n">
+      <c r="D150" s="10" t="inlineStr"/>
+      <c r="E150" s="10" t="n">
         <v>3.49</v>
       </c>
-      <c r="F150" s="9" t="n"/>
-      <c r="G150" s="9" t="n"/>
-      <c r="H150" s="9" t="n"/>
-      <c r="I150" s="9" t="inlineStr"/>
+      <c r="F150" s="10" t="n"/>
+      <c r="G150" s="10" t="n"/>
+      <c r="H150" s="10" t="n"/>
+      <c r="I150" s="10" t="inlineStr"/>
+      <c r="J150" s="10" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="8" t="inlineStr">
+      <c r="A151" s="9" t="inlineStr">
         <is>
           <t>burrito-sides/Brownie</t>
         </is>
       </c>
-      <c r="B151" s="9" t="inlineStr">
+      <c r="B151" s="10" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="C151" s="9" t="inlineStr">
+      <c r="C151" s="10" t="inlineStr">
         <is>
           <t>Brownie</t>
         </is>
       </c>
-      <c r="D151" s="9" t="inlineStr"/>
-      <c r="E151" s="9" t="n">
+      <c r="D151" s="10" t="inlineStr"/>
+      <c r="E151" s="10" t="n">
         <v>2.99</v>
       </c>
-      <c r="F151" s="9" t="n"/>
-      <c r="G151" s="9" t="n"/>
-      <c r="H151" s="9" t="n"/>
-      <c r="I151" s="9" t="inlineStr"/>
+      <c r="F151" s="10" t="n"/>
+      <c r="G151" s="10" t="n"/>
+      <c r="H151" s="10" t="n"/>
+      <c r="I151" s="10" t="inlineStr"/>
+      <c r="J151" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="J5:J151" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
+      <formula1>=Lists!$B$1:$B$41</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5559,221 +5916,221 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Pizza builder</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>What a build-your-own pizza costs. One row per number of toppings, one column per size. The last row is what each EXTRA topping costs once the included ones are used up.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Toppings</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>9" Small</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>12" Medium</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>16" Large</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>18" X-Large</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>builder.count.0</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>0 toppings</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>9.5</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <v>12.9</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>16.9</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>20.95</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>builder.count.1</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>1 topping</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <v>13.8</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>22.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>builder.count.2</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>2 toppings</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>11.2</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>15.75</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>19.75</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>23.95</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>builder.count.3</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>3 toppings</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>11.95</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>16.45</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>20.45</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>25.35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>builder.count.4</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>4 toppings</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>12.8</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>17.45</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>22.95</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>27.45</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>builder.count.5</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>5 toppings</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>13.5</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>18.75</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>24.45</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>28.45</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>builder.extra</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Each extra</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>The extra-topping prices were worked out from the steps between the rows above. Confirm them with the shop before trusting them.</t>
         </is>
@@ -5804,202 +6161,202 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Opening times on a 24-hour clock. Use 25 for 1am the next morning, 26 for 2am. Put "yes" in Closed for a day off.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Opens</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Closes</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>hours.Sunday</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>hours.Monday</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>hours.Tuesday</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>hours.Wednesday</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>hours.Thursday</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>hours.Friday</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>hours.Saturday</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6033,225 +6390,225 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Shop details</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Phone, email, delivery and the ordering links. Tax is a decimal — 0.14 is 14%.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Phone number (as shown)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>902-435-5700</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>phoneLink</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Phone number (for the call button)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>+19024355700</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Email address</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>tastypizzadm@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>tagline</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Tagline</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Dartmouth's pizza shop for over 20 years</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Owner line</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Owned and operated by the Patel family</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>delivery.fee</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Delivery fee</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>delivery.minimum</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Minimum order for delivery</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>taxRate</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Tax rate (0.14 = 14%)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>ordering.doordash</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>DoorDash link</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>https://www.doordash.com/en-CA/store/tasty-pizza-dartmouth-32990155/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>ordering.ubereats</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Uber Eats link</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>https://www.ubereats.com/ca/store/tasty-pizza/IST5GL8wVniy8hh0oilx9w</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>ordering.skipthedishes</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Skip The Dishes link</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>seo.description</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Google description (70-165 characters)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Dartmouth's donair and pizza shop on Main Street. Fresh dough daily, garlic fingers, subs and seafood. Open 7 days, Friday till 1am. Call 902-435-5700.</t>
         </is>
@@ -6263,4 +6620,330 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>build-your-own</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>all-dressed-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>greek</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bbq-chicken-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>meat-lovers</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>bread-sticks</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pepperoni</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>burrito</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>veggie</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cheese-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cheeseburger</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cheeseburger-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>chicken-fingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>chicken-wings</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>club-sandwich</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cold-cut-sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>custom-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>donair</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>donair-egg-roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>donair-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>donair-plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>donair-pogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fish-and-chips</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fried-chicken</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fries</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>garlic-fingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>greek-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>hamburger</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>hawaiian-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>lasagna</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>meat-lovers-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mozza-sticks</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nachos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>onion-rings</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pita-wrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pocket</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>poutine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>quesadilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rice-bowl</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>salad</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>scallops</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>shrimp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>steak-sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>tacos</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>two-topping-pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>veggie-pizza</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Pizza builder" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Hours" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Shop details" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Lists" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="Questions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Lists" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6628,6 +6629,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Extra questions for the FAQ page. Hours, delivery areas, crusts and vegetarian pizzas are answered automatically from the other sheets. Fill a blank row to add one; clear a row to remove it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -955,14 +955,14 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Any four toppings you like.</t>
+          <t>Any four toppings you like. Add medium garlic fingers for $13.45.</t>
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>20.95</v>
+        <v>22.95</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>22.95</v>
+        <v>23.95</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>pizza-and-fingers</t>
+          <t>large-4-topping-fingers</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -983,30 +983,26 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Medium Pizza + Medium Garlic Fingers</t>
+          <t>Medium Garlic Fingers with the 16" Deal</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>12" pizza with four toppings, plus 12" garlic fingers with donair sauce.</t>
+          <t>12" garlic fingers with dipping sauce, added to a 16" four-topping pizza deal.</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>28.95</v>
+        <v>13.45</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>meat-lovers</t>
-        </is>
-      </c>
+        <v>15.45</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>two-mediums</t>
+          <t>pizza-and-fingers</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1016,30 +1012,30 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Two Medium Pizzas</t>
+          <t>Medium Pizza + Medium Garlic Fingers</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Four toppings on each.</t>
+          <t>12" pizza with four toppings, plus 12" garlic fingers with donair sauce.</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
         <v>32.95</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>34.9</v>
+        <v>34.4</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>greek</t>
+          <t>meat-lovers</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>party-box</t>
+          <t>two-mediums</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1049,53 +1045,57 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Tasty Party Box</t>
+          <t>Two Medium Pizzas</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Onion rings, deep fried pepperoni, 9 mozza sticks, 12 chicken fries and 6 donair egg rolls. Honey mustard, sour cream and donair sauce. 2L pop included.</t>
+          <t>Four toppings on each.</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="inlineStr"/>
+        <v>36.95</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>greek</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>egg-rolls-6</t>
+          <t>party-box</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>6 Donair Egg Rolls</t>
+          <t>Tasty Party Box</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>With donair sauce.</t>
+          <t>Onion rings, deep fried pepperoni, 9 mozza sticks, 12 chicken fries and 6 donair egg rolls. Honey mustard, sour cream and donair sauce. 2L pop included.</t>
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>47.99</v>
+      </c>
+      <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>pogos-6</t>
+          <t>egg-rolls-6</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>6 Donair Pogos</t>
+          <t>6 Donair Egg Rolls</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1114,17 +1114,17 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>19.5</v>
+        <v>16.95</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>20.7</v>
+        <v>17.7</v>
       </c>
       <c r="G10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>two-large-subs</t>
+          <t>pogos-6</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1134,56 +1134,87 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Two Large Subs</t>
+          <t>6 Donair Pogos</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Cold cut, pizza or real turkey.</t>
+          <t>With donair sauce.</t>
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="F11" s="10" t="n"/>
+        <v>22.95</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
+          <t>two-large-subs</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Two Large Subs</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Cold cut, pizza or real turkey.</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
           <t>two-can-dine</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Two Can Dine</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Two medium burritos, two small chips &amp; salsa, two cans of pop.</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E13" s="10" t="n">
         <v>24.99</v>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B5:B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B5:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
+    <dataValidation sqref="G5:G13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
       <formula1>=Lists!$A$1:$A$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -1197,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1336,16 +1367,16 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
@@ -1380,16 +1411,16 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>14.95</v>
+        <v>17.45</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>21.5</v>
+        <v>24.25</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>27.45</v>
+        <v>29.45</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>32.95</v>
+        <v>34.95</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
@@ -1424,16 +1455,16 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>14.95</v>
+        <v>17.45</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>21.5</v>
+        <v>24.25</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>27.45</v>
+        <v>29.45</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>32.95</v>
+        <v>34.95</v>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
@@ -1464,16 +1495,16 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
@@ -1508,16 +1539,16 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
@@ -1552,16 +1583,16 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
@@ -1596,16 +1627,16 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
@@ -1636,16 +1667,16 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
@@ -1680,16 +1711,16 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
@@ -1724,16 +1755,16 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
@@ -1764,16 +1795,16 @@
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>13.25</v>
+        <v>15.95</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>19.75</v>
+        <v>22.45</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>30.95</v>
+        <v>32.95</v>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
@@ -1808,16 +1839,16 @@
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>14.95</v>
+        <v>17.45</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>21.5</v>
+        <v>24.25</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>27.45</v>
+        <v>29.45</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>32.95</v>
+        <v>34.95</v>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
@@ -1844,20 +1875,20 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Garlic butter, mozzarella, pulled apart by hand.</t>
+          <t>Served with donair sauce.</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>10.25</v>
+        <v>11.95</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>13.95</v>
+        <v>15.45</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>17.95</v>
+        <v>19.45</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>22.45</v>
+        <v>23.95</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
@@ -1892,16 +1923,16 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>11.25</v>
+        <v>13.25</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>14.95</v>
+        <v>16.95</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>19.95</v>
+        <v>21.95</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>24.45</v>
+        <v>26.45</v>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
@@ -1932,16 +1963,16 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>14.95</v>
+        <v>16.95</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>17.95</v>
+        <v>19.95</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>21.95</v>
+        <v>24.95</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>26.95</v>
+        <v>28.45</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
@@ -2004,16 +2035,16 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
@@ -2025,7 +2056,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>pizza-extras/Gluten Free Crust</t>
+          <t>pizza-extras/Extra Cheese</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -2035,20 +2066,22 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Gluten Free Crust</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Any size.</t>
-        </is>
-      </c>
+          <t>Extra Cheese</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
+        <v>2.85</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>6.45</v>
+      </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
           <t>9" S / 12" M / 16" L / 18" XL</t>
@@ -2059,51 +2092,41 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>donair/Donair</t>
+          <t>pizza-extras/Gluten Free Crust</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Donair</t>
+          <t>Pizza Extras</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Donair</t>
+          <t>Gluten Free Crust</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Spiced beef off the spit, sweet sauce, warm pita. The one we're known for.</t>
+          <t>Any size.</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>11.35</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>15.55</v>
-      </c>
+        <v>4.99</v>
+      </c>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large / Super</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>donair</t>
-        </is>
-      </c>
+          <t>9" S / 12" M / 16" L / 18" XL</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>donair/Add Cheese</t>
+          <t>donair/Donair</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -2113,37 +2136,41 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Add Cheese</t>
+          <t>Donair</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Melted through the meat.</t>
+          <t>Spiced beef off the spit, sweet sauce, warm pita. The one we're known for.</t>
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>2</v>
+        <v>10.95</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>2.3</v>
+        <v>13.45</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>2.85</v>
+        <v>15.75</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>3.35</v>
+        <v>16.95</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Small / Medium / Large / Super</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>donair</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>donair/Add Extra Meat</t>
+          <t>donair/Add Cheese</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -2153,25 +2180,25 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Add Extra Meat</t>
+          <t>Add Cheese</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>For when a large isn't a large.</t>
+          <t>Melted through the meat.</t>
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>3.35</v>
+        <v>2.25</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>4.35</v>
+        <v>2.65</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>5.35</v>
+        <v>3.15</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>6.35</v>
+        <v>3.65</v>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
@@ -2183,37 +2210,47 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>donair-plates/Small Donair Plate</t>
+          <t>donair/Add Extra Meat</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Donair Plates</t>
+          <t>Donair</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Small Donair Plate</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
+          <t>Add Extra Meat</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>For when a large isn't a large.</t>
+        </is>
+      </c>
       <c r="E27" s="10" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>donair-plate</t>
-        </is>
-      </c>
+        <v>3.75</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Small / Medium / Large / Super</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>donair-plates/Large Donair Plate</t>
+          <t>donair-plates/Small Donair Plate</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2223,57 +2260,61 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Large Donair Plate</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr"/>
+          <t>Small Donair Plate</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Fries and donair meat, topped with mozzarella, onions, tomatoes and donair sauce.</t>
+        </is>
+      </c>
       <c r="E28" s="10" t="n">
-        <v>15.95</v>
+        <v>13.95</v>
       </c>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>donair-plate</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Egg Roll</t>
+          <t>donair-plates/Large Donair Plate</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Donair, Deep Fried</t>
+          <t>Donair Plates</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Donair Egg Roll</t>
+          <t>Large Donair Plate</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Donair, rolled and fried. Order more than one.</t>
+          <t>Fries and donair meat, topped with mozzarella, onions, tomatoes and donair sauce.</t>
         </is>
       </c>
       <c r="E29" s="10" t="n">
-        <v>2.5</v>
+        <v>17.45</v>
       </c>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>donair-egg-roll</t>
-        </is>
-      </c>
+      <c r="J29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Egg Rolls — Dozen</t>
+          <t>donair-fried/Donair Egg Roll</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -2283,23 +2324,31 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Donair Egg Rolls — Dozen</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+          <t>Donair Egg Roll</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Donair, rolled and fried. Order more than one.</t>
+        </is>
+      </c>
       <c r="E30" s="10" t="n">
-        <v>28</v>
+        <v>2.95</v>
       </c>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>donair-egg-roll</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Pogo</t>
+          <t>donair-fried/Donair Egg Rolls — Dozen</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -2309,31 +2358,23 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Donair Pogo</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Donair on a stick in batter. Yes, really.</t>
-        </is>
-      </c>
+          <t>Donair Egg Rolls — Dozen</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="10" t="n">
-        <v>3.45</v>
+        <v>32.95</v>
       </c>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>donair-pogo</t>
-        </is>
-      </c>
+      <c r="J31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Pogos — Dozen</t>
+          <t>donair-fried/Donair Pogo</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -2343,38 +2384,46 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Donair Pogos — Dozen</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr"/>
+          <t>Donair Pogo</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Donair on a stick in batter. Yes, really.</t>
+        </is>
+      </c>
       <c r="E32" s="10" t="n">
-        <v>38.95</v>
+        <v>3.95</v>
       </c>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>donair-pogo</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>donair-sauce/Small Donair Sauce</t>
+          <t>donair-fried/Donair Pogos — Dozen</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Donair Sauce</t>
+          <t>Donair, Deep Fried</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Small Donair Sauce</t>
+          <t>Donair Pogos — Dozen</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="n">
-        <v>2.25</v>
+        <v>43.95</v>
       </c>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
@@ -2385,7 +2434,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>donair-sauce/Large Donair Sauce</t>
+          <t>donair-sauce/Small Donair Sauce</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -2395,12 +2444,12 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Large Donair Sauce</t>
+          <t>Small Donair Sauce</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="10" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
@@ -2411,7 +2460,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>donair-sauce/Extra Large Donair Sauce</t>
+          <t>donair-sauce/Large Donair Sauce</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -2421,12 +2470,12 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Extra Large Donair Sauce</t>
+          <t>Large Donair Sauce</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
       <c r="E35" s="10" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
@@ -2437,47 +2486,33 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>poutine/Classic Poutine</t>
+          <t>donair-sauce/Extra Large Donair Sauce</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Poutine</t>
+          <t>Donair Sauce</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Classic Poutine</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Curds, gravy, fries. Done right.</t>
-        </is>
-      </c>
+          <t>Extra Large Donair Sauce</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr"/>
       <c r="E36" s="10" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>12.25</v>
-      </c>
+        <v>5.25</v>
+      </c>
+      <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>poutine</t>
-        </is>
-      </c>
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>poutine/Donair Poutine</t>
+          <t>poutine/Classic Poutine</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -2487,17 +2522,19 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Donair Poutine</t>
+          <t>Classic Poutine</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>With donair meat and a line of donair sauce.</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n"/>
+          <t>Curds, gravy, fries. Done right.</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>9.449999999999999</v>
+      </c>
       <c r="F37" s="10" t="n">
-        <v>14.25</v>
+        <v>13.25</v>
       </c>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
@@ -2506,12 +2543,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>poutine</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>poutine/Chicken Poutine</t>
+          <t>poutine/Donair Poutine</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -2521,13 +2562,17 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Chicken Poutine</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr"/>
+          <t>Donair Poutine</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>With donair meat and a line of donair sauce.</t>
+        </is>
+      </c>
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n">
-        <v>13.95</v>
+        <v>15.25</v>
       </c>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="10" t="n"/>
@@ -2541,7 +2586,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>poutine/Hamburger Poutine</t>
+          <t>poutine/Chicken Poutine</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -2551,13 +2596,13 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Hamburger Poutine</t>
+          <t>Chicken Poutine</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr"/>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n">
-        <v>13.95</v>
+        <v>14.95</v>
       </c>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
@@ -2571,7 +2616,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>poutine/Greek Poutine</t>
+          <t>poutine/Hamburger Poutine</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -2581,17 +2626,13 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Greek Poutine</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Feta, tomato, red onion, olives.</t>
-        </is>
-      </c>
+          <t>Hamburger Poutine</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="10" t="n">
-        <v>13.95</v>
+        <v>14.95</v>
       </c>
       <c r="G40" s="10" t="n"/>
       <c r="H40" s="10" t="n"/>
@@ -2605,7 +2646,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>poutine/Extra Cheese</t>
+          <t>poutine/Greek Poutine</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -2615,15 +2656,17 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr"/>
-      <c r="E41" s="10" t="n">
-        <v>2.25</v>
-      </c>
+          <t>Greek Poutine</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Feta, tomato, red onion, olives.</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n"/>
       <c r="F41" s="10" t="n">
-        <v>2.95</v>
+        <v>14.95</v>
       </c>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n"/>
@@ -2637,7 +2680,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>poutine/Extra Gravy</t>
+          <t>poutine/Extra Cheese</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -2647,15 +2690,15 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Extra Gravy</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr"/>
       <c r="E42" s="10" t="n">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
@@ -2669,37 +2712,39 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>wings/10 Wings</t>
+          <t>poutine/Extra Gravy</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Chicken Wings</t>
+          <t>Poutine</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>10 Wings</t>
+          <t>Extra Gravy</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr"/>
       <c r="E43" s="10" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="F43" s="10" t="n"/>
+        <v>2.25</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>3.45</v>
+      </c>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>chicken-wings</t>
-        </is>
-      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>wings/15 Wings</t>
+          <t>wings/10 Wings</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -2709,23 +2754,27 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>15 Wings</t>
+          <t>10 Wings</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr"/>
       <c r="E44" s="10" t="n">
-        <v>18.95</v>
+        <v>13.95</v>
       </c>
       <c r="F44" s="10" t="n"/>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n"/>
       <c r="I44" s="10" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>chicken-wings</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>wings/20 Wings</t>
+          <t>wings/15 Wings</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2735,12 +2784,12 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>20 Wings</t>
+          <t>15 Wings</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr"/>
       <c r="E45" s="10" t="n">
-        <v>24.95</v>
+        <v>20.95</v>
       </c>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
@@ -2751,7 +2800,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>wings/30 Wings</t>
+          <t>wings/20 Wings</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2761,16 +2810,12 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>30 Wings</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>For the room.</t>
-        </is>
-      </c>
+          <t>20 Wings</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr"/>
       <c r="E46" s="10" t="n">
-        <v>36.95</v>
+        <v>26.95</v>
       </c>
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
@@ -2781,41 +2826,37 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>nachos/Nachos</t>
+          <t>wings/30 Wings</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Nachos</t>
+          <t>Chicken Wings</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Nachos</t>
+          <t>30 Wings</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Green onion, tomato, black olives, jalapeño, mozzarella and cheddar. Salsa and sour cream on the side.</t>
+          <t>For the room.</t>
         </is>
       </c>
       <c r="E47" s="10" t="n">
-        <v>15.45</v>
+        <v>39.95</v>
       </c>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
       <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>nachos</t>
-        </is>
-      </c>
+      <c r="J47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>nachos/Add Chicken, Hamburger or Bacon</t>
+          <t>nachos/Nachos</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2825,23 +2866,37 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Add Chicken, Hamburger or Bacon</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr"/>
+          <t>Nachos</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Green onion, tomato, black olives, jalapeño, mozzarella and cheddar. Salsa and sour cream on the side.</t>
+        </is>
+      </c>
       <c r="E48" s="10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="F48" s="10" t="n"/>
+        <v>12.95</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>16.95</v>
+      </c>
       <c r="G48" s="10" t="n"/>
       <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="inlineStr"/>
-      <c r="J48" s="10" t="inlineStr"/>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>nachos</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>nachos/Extra Cheese</t>
+          <t>nachos/Add Chicken, Hamburger or Bacon</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2851,7 +2906,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
+          <t>Add Chicken, Hamburger or Bacon</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr"/>
@@ -2861,49 +2916,47 @@
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="inlineStr"/>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>burgers/Hamburger</t>
+          <t>nachos/Extra Cheese</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Nachos</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Hamburger</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr"/>
       <c r="E50" s="10" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="F50" s="10" t="n">
-        <v>9.949999999999999</v>
-      </c>
+        <v>4.25</v>
+      </c>
+      <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
       <c r="H50" s="10" t="n"/>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>Burger / Platter</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>hamburger</t>
-        </is>
-      </c>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>burgers/Cheeseburger</t>
+          <t>burgers/Hamburger</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -2913,15 +2966,15 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Cheeseburger</t>
+          <t>Hamburger</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr"/>
       <c r="E51" s="10" t="n">
-        <v>6.95</v>
+        <v>7.75</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>12.95</v>
       </c>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
@@ -2932,14 +2985,14 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>cheeseburger</t>
+          <t>hamburger</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>burgers/Chicken Burger</t>
+          <t>burgers/Cheeseburger</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -2949,15 +3002,15 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Chicken Burger</t>
+          <t>Cheeseburger</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr"/>
       <c r="E52" s="10" t="n">
-        <v>6.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>13.25</v>
       </c>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
@@ -2966,12 +3019,16 @@
           <t>Burger / Platter</t>
         </is>
       </c>
-      <c r="J52" s="10" t="inlineStr"/>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>cheeseburger</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>burgers/Donair Burger</t>
+          <t>burgers/Chicken Burger</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -2981,19 +3038,15 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Donair Burger</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>Donair meat and sauce on a burger. A Dartmouth idea.</t>
-        </is>
-      </c>
+          <t>Chicken Burger</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr"/>
       <c r="E53" s="10" t="n">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>10.45</v>
+        <v>12.95</v>
       </c>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
@@ -3007,7 +3060,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>burgers/Pizza Burger</t>
+          <t>burgers/Donair Burger</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -3017,15 +3070,19 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Pizza Burger</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr"/>
+          <t>Donair Burger</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Donair meat and sauce on a burger. A Dartmouth idea.</t>
+        </is>
+      </c>
       <c r="E54" s="10" t="n">
-        <v>6.95</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>10.45</v>
+        <v>13.95</v>
       </c>
       <c r="G54" s="10" t="n"/>
       <c r="H54" s="10" t="n"/>
@@ -3039,7 +3096,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>burgers/Add Bacon</t>
+          <t>burgers/Pizza Burger</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -3049,15 +3106,15 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Add Bacon</t>
+          <t>Pizza Burger</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr"/>
       <c r="E55" s="10" t="n">
-        <v>1</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1</v>
+        <v>13.45</v>
       </c>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
@@ -3071,41 +3128,39 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>sides/Club House Sandwich with Fries</t>
+          <t>burgers/Add Bacon</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Club House Sandwich with Fries</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>Real turkey.</t>
-        </is>
-      </c>
+          <t>Add Bacon</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr"/>
       <c r="E56" s="10" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="F56" s="10" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G56" s="10" t="n"/>
       <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="inlineStr"/>
-      <c r="J56" s="10" t="inlineStr">
-        <is>
-          <t>club-sandwich</t>
-        </is>
-      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Burger / Platter</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>sides/Hot Hamburger with Gravy &amp; Fries</t>
+          <t>sides/Club House Sandwich with Fries</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -3115,23 +3170,35 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Hot Hamburger with Gravy &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr"/>
+          <t>Club House Sandwich with Fries</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Real turkey.</t>
+        </is>
+      </c>
       <c r="E57" s="10" t="n">
-        <v>12.3</v>
+        <v>15.95</v>
       </c>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr"/>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>club-sandwich</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>sides/Hot Turkey with Gravy &amp; Fries</t>
+          <t>sides/Hot Hamburger with Gravy &amp; Fries</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -3141,23 +3208,27 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Hot Turkey with Gravy &amp; Fries</t>
+          <t>Hot Hamburger with Gravy &amp; Fries</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr"/>
       <c r="E58" s="10" t="n">
-        <v>12.3</v>
+        <v>13.95</v>
       </c>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
       <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="inlineStr"/>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>sides/Large Fries</t>
+          <t>sides/Hot Turkey with Gravy &amp; Fries</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -3167,27 +3238,27 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Large Fries</t>
+          <t>Hot Turkey with Gravy &amp; Fries</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr"/>
       <c r="E59" s="10" t="n">
-        <v>5.45</v>
+        <v>13.95</v>
       </c>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>fries</t>
-        </is>
-      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>sides/Large Onion Rings</t>
+          <t>sides/Fries</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -3197,27 +3268,33 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Large Onion Rings</t>
+          <t>Fries</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr"/>
       <c r="E60" s="10" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="F60" s="10" t="n"/>
+        <v>4.95</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>6.95</v>
+      </c>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="inlineStr"/>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>onion-rings</t>
+          <t>fries</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>sides/12 Chicken Fries</t>
+          <t>sides/Large Onion Rings</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -3227,23 +3304,31 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>12 Chicken Fries</t>
+          <t>Large Onion Rings</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr"/>
       <c r="E61" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="inlineStr"/>
-      <c r="J61" s="10" t="inlineStr"/>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>onion-rings</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>sides/9 Mozza Sticks</t>
+          <t>sides/9 Chicken Fries</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3253,27 +3338,27 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>9 Mozza Sticks</t>
+          <t>9 Chicken Fries</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr"/>
       <c r="E62" s="10" t="n">
-        <v>10.95</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="10" t="n"/>
       <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="inlineStr"/>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>mozza-sticks</t>
-        </is>
-      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>sides/Cup of Gravy — Small</t>
+          <t>sides/9 Mozza Sticks</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -3283,23 +3368,31 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Cup of Gravy — Small</t>
+          <t>9 Mozza Sticks</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr"/>
       <c r="E63" s="10" t="n">
-        <v>1.65</v>
+        <v>12.95</v>
       </c>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>mozza-sticks</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>sides/Cup of Gravy — Large</t>
+          <t>sides/Cup of Gravy — Small</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -3309,162 +3402,166 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Cup of Gravy — Large</t>
+          <t>Cup of Gravy — Small</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr"/>
       <c r="E64" s="10" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="F64" s="10" t="n"/>
       <c r="G64" s="10" t="n"/>
       <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="inlineStr"/>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>bread-sticks/Small Yum Yums</t>
+          <t>sides/Cup of Gravy — Large</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Bread Sticks ("Yum Yums")</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Small Yum Yums</t>
+          <t>Cup of Gravy — Large</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr"/>
       <c r="E65" s="10" t="n">
-        <v>12.95</v>
+        <v>3.15</v>
       </c>
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="inlineStr"/>
-      <c r="J65" s="10" t="inlineStr">
-        <is>
-          <t>bread-sticks</t>
-        </is>
-      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>bread-sticks/Large Yum Yums</t>
+          <t>sides/Spicy Fries</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Bread Sticks ("Yum Yums")</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Large Yum Yums</t>
+          <t>Spicy Fries</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr"/>
       <c r="E66" s="10" t="n">
-        <v>16.45</v>
+        <v>8.99</v>
       </c>
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
       <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="inlineStr"/>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>wraps-pockets/Pita Wrap</t>
+          <t>sides/Brownie</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Wraps &amp; Pockets</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Pita Wrap</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>Pizza, donair, cold cut, club, vegetarian, chicken, turkey or chicken Caesar.</t>
-        </is>
-      </c>
+          <t>Brownie</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr"/>
       <c r="E67" s="10" t="n">
-        <v>10.45</v>
+        <v>2.99</v>
       </c>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="inlineStr"/>
-      <c r="J67" s="10" t="inlineStr">
-        <is>
-          <t>pita-wrap</t>
-        </is>
-      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>wraps-pockets/Pocket — Pizza, Chicken, Meats or Vegetarian</t>
+          <t>sides/Chips &amp; Salsa</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Wraps &amp; Pockets</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Pocket — Pizza, Chicken, Meats or Vegetarian</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Oven baked or deep fried.</t>
-        </is>
-      </c>
+          <t>Chips &amp; Salsa</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr"/>
       <c r="E68" s="10" t="n">
-        <v>15.95</v>
+        <v>2.95</v>
       </c>
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="inlineStr"/>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>wraps-pockets/Pocket — Donair or Steak</t>
+          <t>bread-sticks/Small Yum Yums</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Wraps &amp; Pockets</t>
+          <t>Bread Sticks ("Yum Yums")</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Pocket — Donair or Steak</t>
+          <t>Small Yum Yums</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Oven baked or deep fried.</t>
+          <t>Tossed in parmesan, with donair dipping sauce.</t>
         </is>
       </c>
       <c r="E69" s="10" t="n">
-        <v>16.45</v>
+        <v>14.45</v>
       </c>
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
@@ -3472,85 +3569,97 @@
       <c r="I69" s="10" t="inlineStr"/>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>pocket</t>
+          <t>bread-sticks</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken &amp; Chips — 1 pc</t>
+          <t>bread-sticks/Large Yum Yums</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Bread Sticks ("Yum Yums")</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Chicken &amp; Chips — 1 pc</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr"/>
+          <t>Large Yum Yums</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Tossed in parmesan, with donair dipping sauce.</t>
+        </is>
+      </c>
       <c r="E70" s="10" t="n">
-        <v>8.449999999999999</v>
+        <v>18.95</v>
       </c>
       <c r="F70" s="10" t="n"/>
       <c r="G70" s="10" t="n"/>
       <c r="H70" s="10" t="n"/>
       <c r="I70" s="10" t="inlineStr"/>
-      <c r="J70" s="10" t="inlineStr">
-        <is>
-          <t>fried-chicken</t>
-        </is>
-      </c>
+      <c r="J70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken &amp; Chips — 2 pc</t>
+          <t>wraps-pockets/Pita Wrap</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Wraps &amp; Pockets</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Chicken &amp; Chips — 2 pc</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr"/>
+          <t>Pita Wrap</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Pizza, donair, cold cut, club, vegetarian, chicken, turkey or chicken Caesar.</t>
+        </is>
+      </c>
       <c r="E71" s="10" t="n">
-        <v>12.45</v>
+        <v>11.95</v>
       </c>
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="inlineStr"/>
-      <c r="J71" s="10" t="inlineStr"/>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>pita-wrap</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken &amp; Chips — 3 pc</t>
+          <t>wraps-pockets/Pocket — Pizza, Chicken, Meats or Vegetarian</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Wraps &amp; Pockets</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Chicken &amp; Chips — 3 pc</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr"/>
+          <t>Pocket — Pizza, Chicken, Meats or Vegetarian</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Oven baked or deep fried.</t>
+        </is>
+      </c>
       <c r="E72" s="10" t="n">
-        <v>14.95</v>
+        <v>17.45</v>
       </c>
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="10" t="n"/>
@@ -3561,33 +3670,41 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>chicken/Extra Piece of Chicken</t>
+          <t>wraps-pockets/Pocket — Donair or Steak</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Wraps &amp; Pockets</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Extra Piece of Chicken</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr"/>
+          <t>Pocket — Donair or Steak</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Oven baked or deep fried.</t>
+        </is>
+      </c>
       <c r="E73" s="10" t="n">
-        <v>3.75</v>
+        <v>18.45</v>
       </c>
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="inlineStr"/>
-      <c r="J73" s="10" t="inlineStr"/>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>pocket</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>chicken/2 Chicken Legs &amp; Chips</t>
+          <t>chicken/Chicken &amp; Chips — 1 pc</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -3597,27 +3714,27 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>2 Chicken Legs &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>Everyday special.</t>
-        </is>
-      </c>
+          <t>Chicken &amp; Chips — 1 pc</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr"/>
       <c r="E74" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>10.95</v>
       </c>
       <c r="F74" s="10" t="n"/>
       <c r="G74" s="10" t="n"/>
       <c r="H74" s="10" t="n"/>
       <c r="I74" s="10" t="inlineStr"/>
-      <c r="J74" s="10" t="inlineStr"/>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>fried-chicken</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken Family Pack</t>
+          <t>chicken/Chicken &amp; Chips — 2 pc</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -3627,16 +3744,12 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Chicken Family Pack</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>10 pieces, 2 large fries, gravy and coleslaw.</t>
-        </is>
-      </c>
+          <t>Chicken &amp; Chips — 2 pc</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr"/>
       <c r="E75" s="10" t="n">
-        <v>39.95</v>
+        <v>13.95</v>
       </c>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
@@ -3647,7 +3760,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>chicken/6 Chicken Nuggets &amp; Fries</t>
+          <t>chicken/Chicken &amp; Chips — 3 pc</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -3657,12 +3770,12 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>6 Chicken Nuggets &amp; Fries</t>
+          <t>Chicken &amp; Chips — 3 pc</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr"/>
       <c r="E76" s="10" t="n">
-        <v>7.95</v>
+        <v>16.95</v>
       </c>
       <c r="F76" s="10" t="n"/>
       <c r="G76" s="10" t="n"/>
@@ -3673,7 +3786,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>chicken/12 Chicken Nuggets &amp; Fries</t>
+          <t>chicken/Extra Piece of Chicken</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -3683,12 +3796,12 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>12 Chicken Nuggets &amp; Fries</t>
+          <t>Extra Piece of Chicken</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr"/>
       <c r="E77" s="10" t="n">
-        <v>13.95</v>
+        <v>4.25</v>
       </c>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
@@ -3699,7 +3812,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>chicken/5 Chicken Fingers &amp; Fries</t>
+          <t>chicken/2 Chicken Legs &amp; Chips</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -3709,27 +3822,27 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>5 Chicken Fingers &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr"/>
+          <t>2 Chicken Legs &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Everyday special.</t>
+        </is>
+      </c>
       <c r="E78" s="10" t="n">
-        <v>14.95</v>
+        <v>11.95</v>
       </c>
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="10" t="n"/>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="10" t="inlineStr"/>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>chicken-fingers</t>
-        </is>
-      </c>
+      <c r="J78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>chicken/10 Chicken Fingers &amp; Fries</t>
+          <t>chicken/Chicken Family Pack</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -3739,12 +3852,16 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>10 Chicken Fingers &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr"/>
+          <t>Chicken Family Pack</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>10 pieces, 2 large fries, gravy and coleslaw.</t>
+        </is>
+      </c>
       <c r="E79" s="10" t="n">
-        <v>26.45</v>
+        <v>45.95</v>
       </c>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
@@ -3755,52 +3872,48 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Caesar or Garden Salad</t>
+          <t>chicken/6 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Caesar or Garden Salad</t>
+          <t>6 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr"/>
       <c r="E80" s="10" t="n">
-        <v>8.949999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F80" s="10" t="n"/>
       <c r="G80" s="10" t="n"/>
       <c r="H80" s="10" t="n"/>
       <c r="I80" s="10" t="inlineStr"/>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>salad</t>
-        </is>
-      </c>
+      <c r="J80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Greek Salad</t>
+          <t>chicken/12 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Greek Salad</t>
+          <t>12 Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr"/>
       <c r="E81" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
@@ -3811,63 +3924,63 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Add Chicken — Crispy or Grilled</t>
+          <t>chicken/5 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Add Chicken — Crispy or Grilled</t>
+          <t>5 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr"/>
       <c r="E82" s="10" t="n">
-        <v>2.3</v>
+        <v>16.95</v>
       </c>
       <c r="F82" s="10" t="n"/>
       <c r="G82" s="10" t="n"/>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="inlineStr"/>
-      <c r="J82" s="10" t="inlineStr"/>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>chicken-fingers</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Lasagna with Garlic Bread</t>
+          <t>chicken/10 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Lasagna with Garlic Bread</t>
+          <t>10 Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr"/>
       <c r="E83" s="10" t="n">
-        <v>10.45</v>
+        <v>29.95</v>
       </c>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="inlineStr"/>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>lasagna</t>
-        </is>
-      </c>
+      <c r="J83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Ravioli with Garlic Bread</t>
+          <t>salads-pasta/Caesar or Garden Salad</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -3877,68 +3990,68 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Ravioli with Garlic Bread</t>
+          <t>Caesar or Garden Salad</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr"/>
       <c r="E84" s="10" t="n">
-        <v>10.45</v>
+        <v>11.45</v>
       </c>
       <c r="F84" s="10" t="n"/>
       <c r="G84" s="10" t="n"/>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="inlineStr"/>
-      <c r="J84" s="10" t="inlineStr"/>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>salad</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 1 pc</t>
+          <t>salads-pasta/Greek Salad</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 1 pc</t>
+          <t>Greek Salad</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr"/>
       <c r="E85" s="10" t="n">
-        <v>8.949999999999999</v>
+        <v>12.45</v>
       </c>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="inlineStr"/>
-      <c r="J85" s="10" t="inlineStr">
-        <is>
-          <t>fish-and-chips</t>
-        </is>
-      </c>
+      <c r="J85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 2 pc</t>
+          <t>salads-pasta/Add Chicken — Crispy or Grilled</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 2 pc</t>
+          <t>Add Chicken — Crispy or Grilled</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr"/>
       <c r="E86" s="10" t="n">
-        <v>12.95</v>
+        <v>2.95</v>
       </c>
       <c r="F86" s="10" t="n"/>
       <c r="G86" s="10" t="n"/>
@@ -3949,48 +4062,52 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 3 pc</t>
+          <t>salads-pasta/Lasagna with Garlic Bread</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 3 pc</t>
+          <t>Lasagna with Garlic Bread</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr"/>
       <c r="E87" s="10" t="n">
-        <v>14.95</v>
+        <v>13.45</v>
       </c>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="inlineStr"/>
-      <c r="J87" s="10" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>lasagna</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>fish/Extra Piece of Fish</t>
+          <t>salads-pasta/Ravioli with Garlic Bread</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Extra Piece of Fish</t>
+          <t>Ravioli with Garlic Bread</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr"/>
       <c r="E88" s="10" t="n">
-        <v>3.95</v>
+        <v>13.45</v>
       </c>
       <c r="F88" s="10" t="n"/>
       <c r="G88" s="10" t="n"/>
@@ -4001,7 +4118,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish Family Pack</t>
+          <t>fish/Fish &amp; Chips — 1 pc</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -4011,80 +4128,68 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Fish Family Pack</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
-        </is>
-      </c>
+          <t>Fish &amp; Chips — 1 pc</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr"/>
       <c r="E89" s="10" t="n">
-        <v>39.95</v>
+        <v>11.95</v>
       </c>
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="inlineStr"/>
-      <c r="J89" s="10" t="inlineStr"/>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>fish-and-chips</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>seafood/Scallops &amp; Chips</t>
+          <t>fish/Fish &amp; Chips — 2 pc</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Scallops &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="inlineStr">
-        <is>
-          <t>10 scallops.</t>
-        </is>
-      </c>
+          <t>Fish &amp; Chips — 2 pc</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr"/>
       <c r="E90" s="10" t="n">
-        <v>13.45</v>
+        <v>15.95</v>
       </c>
       <c r="F90" s="10" t="n"/>
       <c r="G90" s="10" t="n"/>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="inlineStr"/>
-      <c r="J90" s="10" t="inlineStr">
-        <is>
-          <t>scallops</t>
-        </is>
-      </c>
+      <c r="J90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>seafood/Clams &amp; Chips</t>
+          <t>fish/Fish &amp; Chips — 3 pc</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Clams &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>Two cups of clams.</t>
-        </is>
-      </c>
+          <t>Fish &amp; Chips — 3 pc</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr"/>
       <c r="E91" s="10" t="n">
-        <v>13.45</v>
+        <v>17.95</v>
       </c>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
@@ -4095,60 +4200,52 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>seafood/Shrimp &amp; Chips</t>
+          <t>fish/Extra Piece of Fish</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Shrimp &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D92" s="10" t="inlineStr">
-        <is>
-          <t>12 shrimp.</t>
-        </is>
-      </c>
+          <t>Extra Piece of Fish</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr"/>
       <c r="E92" s="10" t="n">
-        <v>13.45</v>
+        <v>4.95</v>
       </c>
       <c r="F92" s="10" t="n"/>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="10" t="inlineStr"/>
-      <c r="J92" s="10" t="inlineStr">
-        <is>
-          <t>shrimp</t>
-        </is>
-      </c>
+      <c r="J92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>seafood/Seafood Platter</t>
+          <t>fish/Fish Family Pack</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Seafood Platter</t>
+          <t>Fish Family Pack</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
+          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
         </is>
       </c>
       <c r="E93" s="10" t="n">
-        <v>17.45</v>
+        <v>46.95</v>
       </c>
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
@@ -4159,7 +4256,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>seafood/Extra Coleslaw — Small</t>
+          <t>seafood/Scallops &amp; Chips</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -4169,23 +4266,31 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Extra Coleslaw — Small</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr"/>
+          <t>Scallops &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>10 scallops.</t>
+        </is>
+      </c>
       <c r="E94" s="10" t="n">
-        <v>1.75</v>
+        <v>14.95</v>
       </c>
       <c r="F94" s="10" t="n"/>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="inlineStr"/>
-      <c r="J94" s="10" t="inlineStr"/>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>scallops</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>seafood/Extra Coleslaw — Large</t>
+          <t>seafood/Clams &amp; Chips</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -4195,12 +4300,16 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Extra Coleslaw — Large</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr"/>
+          <t>Clams &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Two cups of clams.</t>
+        </is>
+      </c>
       <c r="E95" s="10" t="n">
-        <v>2.95</v>
+        <v>14.95</v>
       </c>
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
@@ -4211,139 +4320,123 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>subs/Cold Cut</t>
+          <t>seafood/Shrimp &amp; Chips</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Cold Cut</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr"/>
+          <t>Shrimp &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>12 shrimp.</t>
+        </is>
+      </c>
       <c r="E96" s="10" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>11.45</v>
-      </c>
+        <v>14.95</v>
+      </c>
+      <c r="F96" s="10" t="n"/>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I96" s="10" t="inlineStr"/>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>cold-cut-sub</t>
+          <t>shrimp</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>subs/Salami &amp; Ham</t>
+          <t>seafood/Seafood Platter</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Salami &amp; Ham</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr"/>
+          <t>Seafood Platter</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
+        </is>
+      </c>
       <c r="E97" s="10" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="F97" s="10" t="n">
-        <v>11.45</v>
-      </c>
+        <v>23.95</v>
+      </c>
+      <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I97" s="10" t="inlineStr"/>
       <c r="J97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>subs/Pizza Sub</t>
+          <t>seafood/Extra Coleslaw — Small</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Pizza Sub</t>
+          <t>Extra Coleslaw — Small</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr"/>
       <c r="E98" s="10" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="F98" s="10" t="n">
-        <v>11.45</v>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="F98" s="10" t="n"/>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I98" s="10" t="inlineStr"/>
       <c r="J98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>subs/Vegetarian</t>
+          <t>seafood/Extra Coleslaw — Large</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Extra Coleslaw — Large</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr"/>
       <c r="E99" s="10" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="F99" s="10" t="n">
-        <v>11.45</v>
-      </c>
+        <v>3.45</v>
+      </c>
+      <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I99" s="10" t="inlineStr"/>
       <c r="J99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>subs/Real Turkey</t>
+          <t>subs/Cold Cut</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -4353,15 +4446,15 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Real Turkey</t>
+          <t>Cold Cut</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr"/>
       <c r="E100" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>10.95</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>11.45</v>
+        <v>13.25</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -4370,12 +4463,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J100" s="10" t="inlineStr"/>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>cold-cut-sub</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>subs/Bubba</t>
+          <t>subs/Salami &amp; Ham</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -4385,19 +4482,15 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Bubba</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t>The one people ask for by name.</t>
-        </is>
-      </c>
+          <t>Salami &amp; Ham</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr"/>
       <c r="E101" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>10.95</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -4411,7 +4504,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>subs/Club</t>
+          <t>subs/Pizza Sub</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -4421,15 +4514,15 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Pizza Sub</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr"/>
       <c r="E102" s="10" t="n">
-        <v>10.25</v>
+        <v>10.95</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
@@ -4443,7 +4536,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>subs/Steak</t>
+          <t>subs/Vegetarian</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -4453,12 +4546,12 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Vegetarian</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr"/>
       <c r="E103" s="10" t="n">
-        <v>10.25</v>
+        <v>10.95</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>13.25</v>
@@ -4470,16 +4563,12 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J103" s="10" t="inlineStr">
-        <is>
-          <t>steak-sub</t>
-        </is>
-      </c>
+      <c r="J103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>subs/Donair Sub</t>
+          <t>subs/Real Turkey</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -4489,12 +4578,12 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Donair Sub</t>
+          <t>Real Turkey</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr"/>
       <c r="E104" s="10" t="n">
-        <v>10.25</v>
+        <v>11.45</v>
       </c>
       <c r="F104" s="10" t="n">
         <v>13.25</v>
@@ -4511,7 +4600,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>subs/Super Sub</t>
+          <t>subs/Bubba</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -4521,15 +4610,19 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Super Sub</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr"/>
+          <t>Bubba</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>The one people ask for by name.</t>
+        </is>
+      </c>
       <c r="E105" s="10" t="n">
-        <v>10.95</v>
+        <v>11.95</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>14.75</v>
+        <v>14.25</v>
       </c>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
@@ -4543,7 +4636,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>subs/Garlic Bread</t>
+          <t>subs/Club</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -4553,15 +4646,15 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Garlic Bread</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr"/>
       <c r="E106" s="10" t="n">
-        <v>4.95</v>
+        <v>11.95</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>5.95</v>
+        <v>14.25</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
@@ -4575,7 +4668,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Cheese</t>
+          <t>subs/Steak</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -4585,15 +4678,15 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr"/>
       <c r="E107" s="10" t="n">
-        <v>2.45</v>
+        <v>11.95</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>3.45</v>
+        <v>14.95</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
@@ -4602,12 +4695,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J107" s="10" t="inlineStr"/>
+      <c r="J107" s="10" t="inlineStr">
+        <is>
+          <t>steak-sub</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Meat</t>
+          <t>subs/Donair Sub</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -4617,15 +4714,15 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Extra Meat</t>
+          <t>Donair Sub</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr"/>
       <c r="E108" s="10" t="n">
-        <v>3.45</v>
+        <v>11.95</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>4.45</v>
+        <v>14.95</v>
       </c>
       <c r="G108" s="10" t="n"/>
       <c r="H108" s="10" t="n"/>
@@ -4639,33 +4736,31 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>burritos/Beans &amp; Veggie</t>
+          <t>subs/Super Sub</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Super Sub</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr"/>
       <c r="E109" s="10" t="n">
-        <v>7.99</v>
+        <v>12.45</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="G109" s="10" t="n">
-        <v>10.99</v>
-      </c>
+        <v>16.25</v>
+      </c>
+      <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr"/>
@@ -4673,71 +4768,63 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>burritos/Spicy Chicken</t>
+          <t>subs/Garlic Bread</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Garlic Bread</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr"/>
       <c r="E110" s="10" t="n">
-        <v>9.99</v>
+        <v>6.25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G110" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>7.45</v>
+      </c>
+      <c r="G110" s="10" t="n"/>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
-      <c r="J110" s="10" t="inlineStr">
-        <is>
-          <t>burrito</t>
-        </is>
-      </c>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>burritos/Ground Beef</t>
+          <t>subs/Extra Cheese</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr"/>
       <c r="E111" s="10" t="n">
-        <v>9.99</v>
+        <v>2.75</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G111" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>3.95</v>
+      </c>
+      <c r="G111" s="10" t="n"/>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J111" s="10" t="inlineStr"/>
@@ -4745,33 +4832,31 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>burritos/Zesty Grilled Chicken</t>
+          <t>subs/Extra Meat</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Extra Meat</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr"/>
       <c r="E112" s="10" t="n">
-        <v>9.99</v>
+        <v>3.95</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G112" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="G112" s="10" t="n"/>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J112" s="10" t="inlineStr"/>
@@ -4779,7 +4864,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>burritos/Fish</t>
+          <t>burritos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -4789,18 +4874,18 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr"/>
       <c r="E113" s="10" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="F113" s="10" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="G113" s="10" t="n">
         <v>10.99</v>
-      </c>
-      <c r="G113" s="10" t="n">
-        <v>12.99</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="inlineStr">
@@ -4813,7 +4898,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>burritos/Shawarma Chicken</t>
+          <t>burritos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -4823,18 +4908,18 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr"/>
       <c r="E114" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F114" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F114" s="10" t="n">
-        <v>11.99</v>
-      </c>
       <c r="G114" s="10" t="n">
-        <v>13.99</v>
+        <v>12.99</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="inlineStr">
@@ -4842,12 +4927,16 @@
           <t>Small / Medium / Large</t>
         </is>
       </c>
-      <c r="J114" s="10" t="inlineStr"/>
+      <c r="J114" s="10" t="inlineStr">
+        <is>
+          <t>burrito</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>burritos/Tequila-Lime Glazed Chicken</t>
+          <t>burritos/Ground Beef</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -4857,18 +4946,18 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr"/>
       <c r="E115" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F115" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F115" s="10" t="n">
-        <v>11.99</v>
-      </c>
       <c r="G115" s="10" t="n">
-        <v>13.99</v>
+        <v>12.99</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="inlineStr">
@@ -4881,7 +4970,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>burritos/Steak</t>
+          <t>burritos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -4891,18 +4980,18 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr"/>
       <c r="E116" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F116" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F116" s="10" t="n">
-        <v>11.99</v>
-      </c>
       <c r="G116" s="10" t="n">
-        <v>13.99</v>
+        <v>12.99</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="inlineStr">
@@ -4915,67 +5004,67 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Beans &amp; Veggie</t>
+          <t>burritos/Fish</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr"/>
       <c r="E117" s="10" t="n">
-        <v>10.49</v>
+        <v>9.99</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="G117" s="10" t="n"/>
+        <v>10.99</v>
+      </c>
+      <c r="G117" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J117" s="10" t="inlineStr">
-        <is>
-          <t>rice-bowl</t>
-        </is>
-      </c>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
+      <c r="J117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Spicy Chicken</t>
+          <t>burritos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr"/>
       <c r="E118" s="10" t="n">
-        <v>11.49</v>
+        <v>10.99</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="G118" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J118" s="10" t="inlineStr"/>
@@ -4983,31 +5072,33 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Ground Beef</t>
+          <t>burritos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr"/>
       <c r="E119" s="10" t="n">
-        <v>11.49</v>
+        <v>10.99</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="G119" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J119" s="10" t="inlineStr"/>
@@ -5015,31 +5106,33 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Zesty Grilled Chicken</t>
+          <t>burritos/Steak</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr"/>
       <c r="E120" s="10" t="n">
-        <v>11.49</v>
+        <v>10.99</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="G120" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J120" s="10" t="inlineStr"/>
@@ -5047,7 +5140,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Fish</t>
+          <t>rice-bowls/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -5057,15 +5150,15 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr"/>
       <c r="E121" s="10" t="n">
-        <v>11.49</v>
+        <v>10.49</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>13.49</v>
+        <v>12.49</v>
       </c>
       <c r="G121" s="10" t="n"/>
       <c r="H121" s="10" t="n"/>
@@ -5074,12 +5167,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J121" s="10" t="inlineStr"/>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>rice-bowl</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Shawarma Chicken</t>
+          <t>rice-bowls/Spicy Chicken</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -5089,15 +5186,15 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr"/>
       <c r="E122" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>14.49</v>
+        <v>13.49</v>
       </c>
       <c r="G122" s="10" t="n"/>
       <c r="H122" s="10" t="n"/>
@@ -5111,7 +5208,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
+          <t>rice-bowls/Ground Beef</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -5121,15 +5218,15 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr"/>
       <c r="E123" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>14.49</v>
+        <v>13.49</v>
       </c>
       <c r="G123" s="10" t="n"/>
       <c r="H123" s="10" t="n"/>
@@ -5143,7 +5240,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Steak</t>
+          <t>rice-bowls/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -5153,15 +5250,15 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr"/>
       <c r="E124" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>14.49</v>
+        <v>13.49</v>
       </c>
       <c r="G124" s="10" t="n"/>
       <c r="H124" s="10" t="n"/>
@@ -5175,115 +5272,135 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Beans &amp; Veggie</t>
+          <t>rice-bowls/Fish</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr"/>
       <c r="E125" s="10" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="F125" s="10" t="n"/>
+        <v>11.49</v>
+      </c>
+      <c r="F125" s="10" t="n">
+        <v>13.49</v>
+      </c>
       <c r="G125" s="10" t="n"/>
       <c r="H125" s="10" t="n"/>
-      <c r="I125" s="10" t="inlineStr"/>
-      <c r="J125" s="10" t="inlineStr">
-        <is>
-          <t>quesadilla</t>
-        </is>
-      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Spicy Chicken</t>
+          <t>rice-bowls/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr"/>
       <c r="E126" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F126" s="10" t="n"/>
+        <v>12.49</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>14.49</v>
+      </c>
       <c r="G126" s="10" t="n"/>
       <c r="H126" s="10" t="n"/>
-      <c r="I126" s="10" t="inlineStr"/>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Ground Beef</t>
+          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr"/>
       <c r="E127" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F127" s="10" t="n"/>
+        <v>12.49</v>
+      </c>
+      <c r="F127" s="10" t="n">
+        <v>14.49</v>
+      </c>
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="n"/>
-      <c r="I127" s="10" t="inlineStr"/>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Zesty Grilled Chicken</t>
+          <t>rice-bowls/Steak</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr"/>
       <c r="E128" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F128" s="10" t="n"/>
+        <v>12.49</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>14.49</v>
+      </c>
       <c r="G128" s="10" t="n"/>
       <c r="H128" s="10" t="n"/>
-      <c r="I128" s="10" t="inlineStr"/>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Fish</t>
+          <t>quesadillas/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -5293,23 +5410,27 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr"/>
       <c r="E129" s="10" t="n">
-        <v>11.49</v>
+        <v>10.49</v>
       </c>
       <c r="F129" s="10" t="n"/>
       <c r="G129" s="10" t="n"/>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="inlineStr"/>
-      <c r="J129" s="10" t="inlineStr"/>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>quesadilla</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Shawarma Chicken</t>
+          <t>quesadillas/Spicy Chicken</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -5319,12 +5440,12 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr"/>
       <c r="E130" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F130" s="10" t="n"/>
       <c r="G130" s="10" t="n"/>
@@ -5335,7 +5456,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
+          <t>quesadillas/Ground Beef</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -5345,12 +5466,12 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr"/>
       <c r="E131" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F131" s="10" t="n"/>
       <c r="G131" s="10" t="n"/>
@@ -5361,7 +5482,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Steak</t>
+          <t>quesadillas/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -5371,12 +5492,12 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr"/>
       <c r="E132" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F132" s="10" t="n"/>
       <c r="G132" s="10" t="n"/>
@@ -5387,52 +5508,48 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>tacos/Beans &amp; Veggie</t>
+          <t>quesadillas/Fish</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr"/>
       <c r="E133" s="10" t="n">
-        <v>9.99</v>
+        <v>11.49</v>
       </c>
       <c r="F133" s="10" t="n"/>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="inlineStr"/>
-      <c r="J133" s="10" t="inlineStr">
-        <is>
-          <t>tacos</t>
-        </is>
-      </c>
+      <c r="J133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>tacos/Spicy Chicken</t>
+          <t>quesadillas/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr"/>
       <c r="E134" s="10" t="n">
-        <v>10.99</v>
+        <v>12.49</v>
       </c>
       <c r="F134" s="10" t="n"/>
       <c r="G134" s="10" t="n"/>
@@ -5443,22 +5560,22 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>tacos/Ground Beef</t>
+          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr"/>
       <c r="E135" s="10" t="n">
-        <v>10.99</v>
+        <v>12.49</v>
       </c>
       <c r="F135" s="10" t="n"/>
       <c r="G135" s="10" t="n"/>
@@ -5469,22 +5586,22 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>tacos/Zesty Grilled Chicken</t>
+          <t>quesadillas/Steak</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr"/>
       <c r="E136" s="10" t="n">
-        <v>10.99</v>
+        <v>12.49</v>
       </c>
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="10" t="n"/>
@@ -5495,7 +5612,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>tacos/Fish</t>
+          <t>tacos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -5505,23 +5622,27 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr"/>
       <c r="E137" s="10" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="F137" s="10" t="n"/>
       <c r="G137" s="10" t="n"/>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="inlineStr"/>
-      <c r="J137" s="10" t="inlineStr"/>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>tacos</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>tacos/Shawarma Chicken</t>
+          <t>tacos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -5531,12 +5652,12 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr"/>
       <c r="E138" s="10" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="10" t="n"/>
@@ -5547,7 +5668,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>tacos/Tequila-Lime Glazed Chicken</t>
+          <t>tacos/Ground Beef</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -5557,12 +5678,12 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr"/>
       <c r="E139" s="10" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="F139" s="10" t="n"/>
       <c r="G139" s="10" t="n"/>
@@ -5573,7 +5694,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>tacos/Steak</t>
+          <t>tacos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -5583,12 +5704,12 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr"/>
       <c r="E140" s="10" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
@@ -5599,22 +5720,22 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Salsa — Small</t>
+          <t>tacos/Fish</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Salsa — Small</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr"/>
       <c r="E141" s="10" t="n">
-        <v>2.49</v>
+        <v>10.99</v>
       </c>
       <c r="F141" s="10" t="n"/>
       <c r="G141" s="10" t="n"/>
@@ -5625,22 +5746,22 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Salsa — Large</t>
+          <t>tacos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Salsa — Large</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr"/>
       <c r="E142" s="10" t="n">
-        <v>4.49</v>
+        <v>11.99</v>
       </c>
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="10" t="n"/>
@@ -5651,22 +5772,22 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Queso — Small</t>
+          <t>tacos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Queso — Small</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr"/>
       <c r="E143" s="10" t="n">
-        <v>3.49</v>
+        <v>11.99</v>
       </c>
       <c r="F143" s="10" t="n"/>
       <c r="G143" s="10" t="n"/>
@@ -5677,22 +5798,22 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Queso — Large</t>
+          <t>tacos/Steak</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Queso — Large</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr"/>
       <c r="E144" s="10" t="n">
-        <v>6.49</v>
+        <v>11.99</v>
       </c>
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
@@ -5703,7 +5824,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Guac — Small</t>
+          <t>burrito-sides/Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -5713,12 +5834,12 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Guac — Small</t>
+          <t>Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr"/>
       <c r="E145" s="10" t="n">
-        <v>3.99</v>
+        <v>2.49</v>
       </c>
       <c r="F145" s="10" t="n"/>
       <c r="G145" s="10" t="n"/>
@@ -5729,7 +5850,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Guac — Large</t>
+          <t>burrito-sides/Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -5739,12 +5860,12 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Guac — Large</t>
+          <t>Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr"/>
       <c r="E146" s="10" t="n">
-        <v>6.99</v>
+        <v>4.49</v>
       </c>
       <c r="F146" s="10" t="n"/>
       <c r="G146" s="10" t="n"/>
@@ -5755,7 +5876,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Fries Supreme</t>
+          <t>burrito-sides/Chips &amp; Queso — Small</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -5765,12 +5886,12 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Fries Supreme</t>
+          <t>Chips &amp; Queso — Small</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr"/>
       <c r="E147" s="10" t="n">
-        <v>9.99</v>
+        <v>3.49</v>
       </c>
       <c r="F147" s="10" t="n"/>
       <c r="G147" s="10" t="n"/>
@@ -5781,7 +5902,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Spicy Fries</t>
+          <t>burrito-sides/Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -5791,12 +5912,12 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Spicy Fries</t>
+          <t>Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr"/>
       <c r="E148" s="10" t="n">
-        <v>8.99</v>
+        <v>6.49</v>
       </c>
       <c r="F148" s="10" t="n"/>
       <c r="G148" s="10" t="n"/>
@@ -5807,7 +5928,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Deep Fried Pepperoni</t>
+          <t>burrito-sides/Chips &amp; Guac — Small</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -5817,16 +5938,12 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Deep Fried Pepperoni</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="inlineStr">
-        <is>
-          <t>With honey mustard sauce.</t>
-        </is>
-      </c>
+          <t>Chips &amp; Guac — Small</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr"/>
       <c r="E149" s="10" t="n">
-        <v>12.99</v>
+        <v>3.99</v>
       </c>
       <c r="F149" s="10" t="n"/>
       <c r="G149" s="10" t="n"/>
@@ -5837,7 +5954,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
+          <t>burrito-sides/Chips &amp; Guac — Large</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -5847,12 +5964,12 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Add Chips &amp; Salsa + a Can of Pop</t>
+          <t>Chips &amp; Guac — Large</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr"/>
       <c r="E150" s="10" t="n">
-        <v>3.49</v>
+        <v>6.99</v>
       </c>
       <c r="F150" s="10" t="n"/>
       <c r="G150" s="10" t="n"/>
@@ -5863,7 +5980,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Brownie</t>
+          <t>burrito-sides/Fries Supreme</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -5873,12 +5990,12 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Fries Supreme</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr"/>
       <c r="E151" s="10" t="n">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
       <c r="F151" s="10" t="n"/>
       <c r="G151" s="10" t="n"/>
@@ -5886,12 +6003,120 @@
       <c r="I151" s="10" t="inlineStr"/>
       <c r="J151" s="10" t="inlineStr"/>
     </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Spicy Fries</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Spicy Fries</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr"/>
+      <c r="E152" s="10" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F152" s="10" t="n"/>
+      <c r="G152" s="10" t="n"/>
+      <c r="H152" s="10" t="n"/>
+      <c r="I152" s="10" t="inlineStr"/>
+      <c r="J152" s="10" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Deep Fried Pepperoni</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>Deep Fried Pepperoni</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>With honey mustard sauce.</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="F153" s="10" t="n"/>
+      <c r="G153" s="10" t="n"/>
+      <c r="H153" s="10" t="n"/>
+      <c r="I153" s="10" t="inlineStr"/>
+      <c r="J153" s="10" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Add Chips &amp; Salsa + a Can of Pop</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr"/>
+      <c r="E154" s="10" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F154" s="10" t="n"/>
+      <c r="G154" s="10" t="n"/>
+      <c r="H154" s="10" t="n"/>
+      <c r="I154" s="10" t="inlineStr"/>
+      <c r="J154" s="10" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Brownie</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>Brownie</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr"/>
+      <c r="E155" s="10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="F155" s="10" t="n"/>
+      <c r="G155" s="10" t="n"/>
+      <c r="H155" s="10" t="n"/>
+      <c r="I155" s="10" t="inlineStr"/>
+      <c r="J155" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J151" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
+    <dataValidation sqref="J5:J155" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
       <formula1>=Lists!$B$1:$B$41</formula1>
     </dataValidation>
   </dataValidations>
@@ -5974,16 +6199,16 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>9.5</v>
+        <v>10.45</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>12.9</v>
+        <v>13.95</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>16.9</v>
+        <v>17.95</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>20.95</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="6">
@@ -5998,16 +6223,16 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>10.7</v>
+        <v>11.75</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>13.8</v>
+        <v>14.45</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>17.9</v>
+        <v>18.45</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>22.25</v>
+        <v>23.95</v>
       </c>
     </row>
     <row r="7">
@@ -6022,16 +6247,16 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>11.2</v>
+        <v>12.25</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>15.75</v>
+        <v>16.35</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>19.75</v>
+        <v>20.45</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>23.95</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="8">
@@ -6046,16 +6271,16 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>11.95</v>
+        <v>13.25</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>16.45</v>
+        <v>17.05</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>20.45</v>
+        <v>21.95</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>25.35</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="9">
@@ -6070,16 +6295,16 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>12.8</v>
+        <v>14.05</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>17.45</v>
+        <v>18.95</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>22.95</v>
+        <v>23.95</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>27.45</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="10">
@@ -6094,16 +6319,16 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>13.5</v>
+        <v>14.75</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>18.75</v>
+        <v>20.45</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>24.45</v>
+        <v>25.95</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>28.45</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="11">
@@ -6118,16 +6343,16 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -6629,7 +6854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6663,8 +6888,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n"/>
-      <c r="B5" s="10" t="n"/>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>How can I pay?</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Visa and Mastercard, and debit at the door on request. Prices do not include HST.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n"/>
@@ -6701,6 +6934,10 @@
     <row r="14">
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -1228,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>4.99</v>
+        <v>6.45</v>
       </c>
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
@@ -4118,52 +4118,48 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 1 pc</t>
+          <t>beverages/Any 519ml Pop</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 1 pc</t>
+          <t>Any 519ml Pop</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr"/>
       <c r="E89" s="10" t="n">
-        <v>11.95</v>
+        <v>2.59</v>
       </c>
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="inlineStr"/>
-      <c r="J89" s="10" t="inlineStr">
-        <is>
-          <t>fish-and-chips</t>
-        </is>
-      </c>
+      <c r="J89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 2 pc</t>
+          <t>beverages/Any Juice, Gatorade, G2 or Energy Drink</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 2 pc</t>
+          <t>Any Juice, Gatorade, G2 or Energy Drink</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr"/>
       <c r="E90" s="10" t="n">
-        <v>15.95</v>
+        <v>3.39</v>
       </c>
       <c r="F90" s="10" t="n"/>
       <c r="G90" s="10" t="n"/>
@@ -4174,22 +4170,22 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 3 pc</t>
+          <t>beverages/Chocolate Milk</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 3 pc</t>
+          <t>Chocolate Milk</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr"/>
       <c r="E91" s="10" t="n">
-        <v>17.95</v>
+        <v>2.79</v>
       </c>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
@@ -4200,22 +4196,22 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>fish/Extra Piece of Fish</t>
+          <t>beverages/Any 355ml Pop</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Extra Piece of Fish</t>
+          <t>Any 355ml Pop</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr"/>
       <c r="E92" s="10" t="n">
-        <v>4.95</v>
+        <v>1.59</v>
       </c>
       <c r="F92" s="10" t="n"/>
       <c r="G92" s="10" t="n"/>
@@ -4226,26 +4222,22 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish Family Pack</t>
+          <t>beverages/Any 2L Pop</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Fish Family Pack</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
-        </is>
-      </c>
+          <t>Any 2L Pop</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr"/>
       <c r="E93" s="10" t="n">
-        <v>46.95</v>
+        <v>4.19</v>
       </c>
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
@@ -4256,124 +4248,104 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>seafood/Scallops &amp; Chips</t>
+          <t>beverages/Aquafina Water 591ml</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Scallops &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>10 scallops.</t>
-        </is>
-      </c>
+          <t>Aquafina Water 591ml</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr"/>
       <c r="E94" s="10" t="n">
-        <v>14.95</v>
+        <v>1.69</v>
       </c>
       <c r="F94" s="10" t="n"/>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="inlineStr"/>
-      <c r="J94" s="10" t="inlineStr">
-        <is>
-          <t>scallops</t>
-        </is>
-      </c>
+      <c r="J94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>seafood/Clams &amp; Chips</t>
+          <t>fish/Fish &amp; Chips — 1 pc</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Clams &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>Two cups of clams.</t>
-        </is>
-      </c>
+          <t>Fish &amp; Chips — 1 pc</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr"/>
       <c r="E95" s="10" t="n">
-        <v>14.95</v>
+        <v>11.95</v>
       </c>
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="inlineStr"/>
-      <c r="J95" s="10" t="inlineStr"/>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>fish-and-chips</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>seafood/Shrimp &amp; Chips</t>
+          <t>fish/Fish &amp; Chips — 2 pc</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Shrimp &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>12 shrimp.</t>
-        </is>
-      </c>
+          <t>Fish &amp; Chips — 2 pc</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr"/>
       <c r="E96" s="10" t="n">
-        <v>14.95</v>
+        <v>15.95</v>
       </c>
       <c r="F96" s="10" t="n"/>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="inlineStr"/>
-      <c r="J96" s="10" t="inlineStr">
-        <is>
-          <t>shrimp</t>
-        </is>
-      </c>
+      <c r="J96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>seafood/Seafood Platter</t>
+          <t>fish/Fish &amp; Chips — 3 pc</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Seafood Platter</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
-        </is>
-      </c>
+          <t>Fish &amp; Chips — 3 pc</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr"/>
       <c r="E97" s="10" t="n">
-        <v>23.95</v>
+        <v>17.95</v>
       </c>
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
@@ -4384,22 +4356,22 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>seafood/Extra Coleslaw — Small</t>
+          <t>fish/Extra Piece of Fish</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Extra Coleslaw — Small</t>
+          <t>Extra Piece of Fish</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr"/>
       <c r="E98" s="10" t="n">
-        <v>2.25</v>
+        <v>4.95</v>
       </c>
       <c r="F98" s="10" t="n"/>
       <c r="G98" s="10" t="n"/>
@@ -4410,22 +4382,26 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>seafood/Extra Coleslaw — Large</t>
+          <t>fish/Fish Family Pack</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Extra Coleslaw — Large</t>
-        </is>
-      </c>
-      <c r="D99" s="10" t="inlineStr"/>
+          <t>Fish Family Pack</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
+        </is>
+      </c>
       <c r="E99" s="10" t="n">
-        <v>3.45</v>
+        <v>46.95</v>
       </c>
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
@@ -4436,207 +4412,187 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>subs/Cold Cut</t>
+          <t>seafood/Scallops &amp; Chips</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Cold Cut</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr"/>
+          <t>Scallops &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>10 scallops.</t>
+        </is>
+      </c>
       <c r="E100" s="10" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="F100" s="10" t="n">
-        <v>13.25</v>
-      </c>
+        <v>14.95</v>
+      </c>
+      <c r="F100" s="10" t="n"/>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I100" s="10" t="inlineStr"/>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>cold-cut-sub</t>
+          <t>scallops</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>subs/Salami &amp; Ham</t>
+          <t>seafood/Clams &amp; Chips</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Salami &amp; Ham</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr"/>
+          <t>Clams &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Two cups of clams.</t>
+        </is>
+      </c>
       <c r="E101" s="10" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="F101" s="10" t="n">
-        <v>13.25</v>
-      </c>
+        <v>14.95</v>
+      </c>
+      <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I101" s="10" t="inlineStr"/>
       <c r="J101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>subs/Pizza Sub</t>
+          <t>seafood/Shrimp &amp; Chips</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Pizza Sub</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="inlineStr"/>
+          <t>Shrimp &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>12 shrimp.</t>
+        </is>
+      </c>
       <c r="E102" s="10" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="F102" s="10" t="n">
-        <v>13.25</v>
-      </c>
+        <v>14.95</v>
+      </c>
+      <c r="F102" s="10" t="n"/>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J102" s="10" t="inlineStr"/>
+      <c r="I102" s="10" t="inlineStr"/>
+      <c r="J102" s="10" t="inlineStr">
+        <is>
+          <t>shrimp</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>subs/Vegetarian</t>
+          <t>seafood/Seafood Platter</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr"/>
+          <t>Seafood Platter</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
+        </is>
+      </c>
       <c r="E103" s="10" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="F103" s="10" t="n">
-        <v>13.25</v>
-      </c>
+        <v>23.95</v>
+      </c>
+      <c r="F103" s="10" t="n"/>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I103" s="10" t="inlineStr"/>
       <c r="J103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>subs/Real Turkey</t>
+          <t>seafood/Extra Coleslaw — Small</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Real Turkey</t>
+          <t>Extra Coleslaw — Small</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr"/>
       <c r="E104" s="10" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="F104" s="10" t="n">
-        <v>13.25</v>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="F104" s="10" t="n"/>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I104" s="10" t="inlineStr"/>
       <c r="J104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>subs/Bubba</t>
+          <t>seafood/Extra Coleslaw — Large</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Bubba</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>The one people ask for by name.</t>
-        </is>
-      </c>
+          <t>Extra Coleslaw — Large</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr"/>
       <c r="E105" s="10" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="F105" s="10" t="n">
-        <v>14.25</v>
-      </c>
+        <v>3.45</v>
+      </c>
+      <c r="F105" s="10" t="n"/>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I105" s="10" t="inlineStr"/>
       <c r="J105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>subs/Club</t>
+          <t>subs/Cold Cut</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -4646,15 +4602,15 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Cold Cut</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr"/>
       <c r="E106" s="10" t="n">
-        <v>11.95</v>
+        <v>10.95</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>14.25</v>
+        <v>13.25</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
@@ -4663,12 +4619,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J106" s="10" t="inlineStr"/>
+      <c r="J106" s="10" t="inlineStr">
+        <is>
+          <t>cold-cut-sub</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>subs/Steak</t>
+          <t>subs/Salami &amp; Ham</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -4678,15 +4638,15 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Salami &amp; Ham</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr"/>
       <c r="E107" s="10" t="n">
-        <v>11.95</v>
+        <v>10.95</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>14.95</v>
+        <v>13.25</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
@@ -4695,16 +4655,12 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J107" s="10" t="inlineStr">
-        <is>
-          <t>steak-sub</t>
-        </is>
-      </c>
+      <c r="J107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>subs/Donair Sub</t>
+          <t>subs/Pizza Sub</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -4714,15 +4670,15 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Donair Sub</t>
+          <t>Pizza Sub</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr"/>
       <c r="E108" s="10" t="n">
-        <v>11.95</v>
+        <v>10.95</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>14.95</v>
+        <v>13.25</v>
       </c>
       <c r="G108" s="10" t="n"/>
       <c r="H108" s="10" t="n"/>
@@ -4736,7 +4692,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>subs/Super Sub</t>
+          <t>subs/Vegetarian</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -4746,15 +4702,15 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Super Sub</t>
+          <t>Vegetarian</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr"/>
       <c r="E109" s="10" t="n">
-        <v>12.45</v>
+        <v>10.95</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>16.25</v>
+        <v>13.25</v>
       </c>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
@@ -4768,7 +4724,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>subs/Garlic Bread</t>
+          <t>subs/Real Turkey</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -4778,15 +4734,15 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Garlic Bread</t>
+          <t>Real Turkey</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr"/>
       <c r="E110" s="10" t="n">
-        <v>6.25</v>
+        <v>11.45</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>7.45</v>
+        <v>13.25</v>
       </c>
       <c r="G110" s="10" t="n"/>
       <c r="H110" s="10" t="n"/>
@@ -4800,7 +4756,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Cheese</t>
+          <t>subs/Bubba</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -4810,15 +4766,19 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr"/>
+          <t>Bubba</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>The one people ask for by name.</t>
+        </is>
+      </c>
       <c r="E111" s="10" t="n">
-        <v>2.75</v>
+        <v>11.95</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>3.95</v>
+        <v>14.25</v>
       </c>
       <c r="G111" s="10" t="n"/>
       <c r="H111" s="10" t="n"/>
@@ -4832,7 +4792,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Meat</t>
+          <t>subs/Club</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -4842,15 +4802,15 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Extra Meat</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr"/>
       <c r="E112" s="10" t="n">
-        <v>3.95</v>
+        <v>11.95</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>4.75</v>
+        <v>14.25</v>
       </c>
       <c r="G112" s="10" t="n"/>
       <c r="H112" s="10" t="n"/>
@@ -4864,105 +4824,99 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>burritos/Beans &amp; Veggie</t>
+          <t>subs/Steak</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr"/>
       <c r="E113" s="10" t="n">
-        <v>7.99</v>
+        <v>11.95</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="G113" s="10" t="n">
-        <v>10.99</v>
-      </c>
+        <v>14.95</v>
+      </c>
+      <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
-      <c r="J113" s="10" t="inlineStr"/>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>steak-sub</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>burritos/Spicy Chicken</t>
+          <t>subs/Donair Sub</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Donair Sub</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr"/>
       <c r="E114" s="10" t="n">
-        <v>9.99</v>
+        <v>11.95</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G114" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>14.95</v>
+      </c>
+      <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
-      <c r="J114" s="10" t="inlineStr">
-        <is>
-          <t>burrito</t>
-        </is>
-      </c>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>burritos/Ground Beef</t>
+          <t>subs/Super Sub</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Super Sub</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr"/>
       <c r="E115" s="10" t="n">
-        <v>9.99</v>
+        <v>12.45</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G115" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>16.25</v>
+      </c>
+      <c r="G115" s="10" t="n"/>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr"/>
@@ -4970,33 +4924,31 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>burritos/Zesty Grilled Chicken</t>
+          <t>subs/Garlic Bread</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Garlic Bread</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr"/>
       <c r="E116" s="10" t="n">
-        <v>9.99</v>
+        <v>6.25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G116" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>7.45</v>
+      </c>
+      <c r="G116" s="10" t="n"/>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J116" s="10" t="inlineStr"/>
@@ -5004,33 +4956,31 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>burritos/Fish</t>
+          <t>subs/Extra Cheese</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr"/>
       <c r="E117" s="10" t="n">
-        <v>9.99</v>
+        <v>2.75</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G117" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>3.95</v>
+      </c>
+      <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J117" s="10" t="inlineStr"/>
@@ -5038,33 +4988,31 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>burritos/Shawarma Chicken</t>
+          <t>subs/Extra Meat</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Extra Meat</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr"/>
       <c r="E118" s="10" t="n">
-        <v>10.99</v>
+        <v>3.95</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G118" s="10" t="n">
-        <v>13.99</v>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J118" s="10" t="inlineStr"/>
@@ -5072,7 +5020,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>burritos/Tequila-Lime Glazed Chicken</t>
+          <t>burritos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -5082,18 +5030,18 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr"/>
       <c r="E119" s="10" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="F119" s="10" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="G119" s="10" t="n">
         <v>10.99</v>
-      </c>
-      <c r="F119" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G119" s="10" t="n">
-        <v>13.99</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="inlineStr">
@@ -5106,7 +5054,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>burritos/Steak</t>
+          <t>burritos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -5116,18 +5064,18 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr"/>
       <c r="E120" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F120" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F120" s="10" t="n">
-        <v>11.99</v>
-      </c>
       <c r="G120" s="10" t="n">
-        <v>13.99</v>
+        <v>12.99</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="inlineStr">
@@ -5135,72 +5083,76 @@
           <t>Small / Medium / Large</t>
         </is>
       </c>
-      <c r="J120" s="10" t="inlineStr"/>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>burrito</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Beans &amp; Veggie</t>
+          <t>burritos/Ground Beef</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr"/>
       <c r="E121" s="10" t="n">
-        <v>10.49</v>
+        <v>9.99</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="G121" s="10" t="n"/>
+        <v>10.99</v>
+      </c>
+      <c r="G121" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J121" s="10" t="inlineStr">
-        <is>
-          <t>rice-bowl</t>
-        </is>
-      </c>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
+      <c r="J121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Spicy Chicken</t>
+          <t>burritos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr"/>
       <c r="E122" s="10" t="n">
-        <v>11.49</v>
+        <v>9.99</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="G122" s="10" t="n"/>
+        <v>10.99</v>
+      </c>
+      <c r="G122" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J122" s="10" t="inlineStr"/>
@@ -5208,31 +5160,33 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Ground Beef</t>
+          <t>burritos/Fish</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr"/>
       <c r="E123" s="10" t="n">
-        <v>11.49</v>
+        <v>9.99</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="G123" s="10" t="n"/>
+        <v>10.99</v>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J123" s="10" t="inlineStr"/>
@@ -5240,31 +5194,33 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Zesty Grilled Chicken</t>
+          <t>burritos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr"/>
       <c r="E124" s="10" t="n">
-        <v>11.49</v>
+        <v>10.99</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="G124" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J124" s="10" t="inlineStr"/>
@@ -5272,31 +5228,33 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Fish</t>
+          <t>burritos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr"/>
       <c r="E125" s="10" t="n">
-        <v>11.49</v>
+        <v>10.99</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="G125" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J125" s="10" t="inlineStr"/>
@@ -5304,31 +5262,33 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Shawarma Chicken</t>
+          <t>burritos/Steak</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr"/>
       <c r="E126" s="10" t="n">
-        <v>12.49</v>
+        <v>10.99</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="G126" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G126" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J126" s="10" t="inlineStr"/>
@@ -5336,7 +5296,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
+          <t>rice-bowls/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -5346,15 +5306,15 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr"/>
       <c r="E127" s="10" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="F127" s="10" t="n">
         <v>12.49</v>
-      </c>
-      <c r="F127" s="10" t="n">
-        <v>14.49</v>
       </c>
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="n"/>
@@ -5363,12 +5323,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J127" s="10" t="inlineStr"/>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>rice-bowl</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Steak</t>
+          <t>rice-bowls/Spicy Chicken</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -5378,15 +5342,15 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr"/>
       <c r="E128" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>14.49</v>
+        <v>13.49</v>
       </c>
       <c r="G128" s="10" t="n"/>
       <c r="H128" s="10" t="n"/>
@@ -5400,167 +5364,199 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Beans &amp; Veggie</t>
+          <t>rice-bowls/Ground Beef</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr"/>
       <c r="E129" s="10" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="F129" s="10" t="n"/>
+        <v>11.49</v>
+      </c>
+      <c r="F129" s="10" t="n">
+        <v>13.49</v>
+      </c>
       <c r="G129" s="10" t="n"/>
       <c r="H129" s="10" t="n"/>
-      <c r="I129" s="10" t="inlineStr"/>
-      <c r="J129" s="10" t="inlineStr">
-        <is>
-          <t>quesadilla</t>
-        </is>
-      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Spicy Chicken</t>
+          <t>rice-bowls/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr"/>
       <c r="E130" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F130" s="10" t="n"/>
+      <c r="F130" s="10" t="n">
+        <v>13.49</v>
+      </c>
       <c r="G130" s="10" t="n"/>
       <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="inlineStr"/>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Ground Beef</t>
+          <t>rice-bowls/Fish</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr"/>
       <c r="E131" s="10" t="n">
         <v>11.49</v>
       </c>
-      <c r="F131" s="10" t="n"/>
+      <c r="F131" s="10" t="n">
+        <v>13.49</v>
+      </c>
       <c r="G131" s="10" t="n"/>
       <c r="H131" s="10" t="n"/>
-      <c r="I131" s="10" t="inlineStr"/>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Zesty Grilled Chicken</t>
+          <t>rice-bowls/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr"/>
       <c r="E132" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F132" s="10" t="n"/>
+        <v>12.49</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>14.49</v>
+      </c>
       <c r="G132" s="10" t="n"/>
       <c r="H132" s="10" t="n"/>
-      <c r="I132" s="10" t="inlineStr"/>
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Fish</t>
+          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr"/>
       <c r="E133" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F133" s="10" t="n"/>
+        <v>12.49</v>
+      </c>
+      <c r="F133" s="10" t="n">
+        <v>14.49</v>
+      </c>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
-      <c r="I133" s="10" t="inlineStr"/>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Shawarma Chicken</t>
+          <t>rice-bowls/Steak</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr"/>
       <c r="E134" s="10" t="n">
         <v>12.49</v>
       </c>
-      <c r="F134" s="10" t="n"/>
+      <c r="F134" s="10" t="n">
+        <v>14.49</v>
+      </c>
       <c r="G134" s="10" t="n"/>
       <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="inlineStr"/>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
+          <t>quesadillas/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -5570,23 +5566,27 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr"/>
       <c r="E135" s="10" t="n">
-        <v>12.49</v>
+        <v>10.49</v>
       </c>
       <c r="F135" s="10" t="n"/>
       <c r="G135" s="10" t="n"/>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="inlineStr"/>
-      <c r="J135" s="10" t="inlineStr"/>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>quesadilla</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Steak</t>
+          <t>quesadillas/Spicy Chicken</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr"/>
       <c r="E136" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="10" t="n"/>
@@ -5612,52 +5612,48 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>tacos/Beans &amp; Veggie</t>
+          <t>quesadillas/Ground Beef</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr"/>
       <c r="E137" s="10" t="n">
-        <v>9.99</v>
+        <v>11.49</v>
       </c>
       <c r="F137" s="10" t="n"/>
       <c r="G137" s="10" t="n"/>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="inlineStr"/>
-      <c r="J137" s="10" t="inlineStr">
-        <is>
-          <t>tacos</t>
-        </is>
-      </c>
+      <c r="J137" s="10" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>tacos/Spicy Chicken</t>
+          <t>quesadillas/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr"/>
       <c r="E138" s="10" t="n">
-        <v>10.99</v>
+        <v>11.49</v>
       </c>
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="10" t="n"/>
@@ -5668,22 +5664,22 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>tacos/Ground Beef</t>
+          <t>quesadillas/Fish</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr"/>
       <c r="E139" s="10" t="n">
-        <v>10.99</v>
+        <v>11.49</v>
       </c>
       <c r="F139" s="10" t="n"/>
       <c r="G139" s="10" t="n"/>
@@ -5694,22 +5690,22 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>tacos/Zesty Grilled Chicken</t>
+          <t>quesadillas/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr"/>
       <c r="E140" s="10" t="n">
-        <v>10.99</v>
+        <v>12.49</v>
       </c>
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
@@ -5720,22 +5716,22 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>tacos/Fish</t>
+          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr"/>
       <c r="E141" s="10" t="n">
-        <v>10.99</v>
+        <v>12.49</v>
       </c>
       <c r="F141" s="10" t="n"/>
       <c r="G141" s="10" t="n"/>
@@ -5746,22 +5742,22 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>tacos/Shawarma Chicken</t>
+          <t>quesadillas/Steak</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr"/>
       <c r="E142" s="10" t="n">
-        <v>11.99</v>
+        <v>12.49</v>
       </c>
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="10" t="n"/>
@@ -5772,7 +5768,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>tacos/Tequila-Lime Glazed Chicken</t>
+          <t>tacos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -5782,23 +5778,27 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr"/>
       <c r="E143" s="10" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="F143" s="10" t="n"/>
       <c r="G143" s="10" t="n"/>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="inlineStr"/>
-      <c r="J143" s="10" t="inlineStr"/>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>tacos</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>tacos/Steak</t>
+          <t>tacos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr"/>
       <c r="E144" s="10" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
@@ -5824,22 +5824,22 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Salsa — Small</t>
+          <t>tacos/Ground Beef</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Salsa — Small</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr"/>
       <c r="E145" s="10" t="n">
-        <v>2.49</v>
+        <v>10.99</v>
       </c>
       <c r="F145" s="10" t="n"/>
       <c r="G145" s="10" t="n"/>
@@ -5850,22 +5850,22 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Salsa — Large</t>
+          <t>tacos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Salsa — Large</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr"/>
       <c r="E146" s="10" t="n">
-        <v>4.49</v>
+        <v>10.99</v>
       </c>
       <c r="F146" s="10" t="n"/>
       <c r="G146" s="10" t="n"/>
@@ -5876,22 +5876,22 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Queso — Small</t>
+          <t>tacos/Fish</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Queso — Small</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr"/>
       <c r="E147" s="10" t="n">
-        <v>3.49</v>
+        <v>10.99</v>
       </c>
       <c r="F147" s="10" t="n"/>
       <c r="G147" s="10" t="n"/>
@@ -5902,22 +5902,22 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Queso — Large</t>
+          <t>tacos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Queso — Large</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr"/>
       <c r="E148" s="10" t="n">
-        <v>6.49</v>
+        <v>11.99</v>
       </c>
       <c r="F148" s="10" t="n"/>
       <c r="G148" s="10" t="n"/>
@@ -5928,22 +5928,22 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Guac — Small</t>
+          <t>tacos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Guac — Small</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr"/>
       <c r="E149" s="10" t="n">
-        <v>3.99</v>
+        <v>11.99</v>
       </c>
       <c r="F149" s="10" t="n"/>
       <c r="G149" s="10" t="n"/>
@@ -5954,22 +5954,22 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Guac — Large</t>
+          <t>tacos/Steak</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Guac — Large</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr"/>
       <c r="E150" s="10" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
       <c r="F150" s="10" t="n"/>
       <c r="G150" s="10" t="n"/>
@@ -5980,7 +5980,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Fries Supreme</t>
+          <t>burrito-sides/Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Fries Supreme</t>
+          <t>Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr"/>
       <c r="E151" s="10" t="n">
-        <v>9.99</v>
+        <v>2.49</v>
       </c>
       <c r="F151" s="10" t="n"/>
       <c r="G151" s="10" t="n"/>
@@ -6006,7 +6006,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Spicy Fries</t>
+          <t>burrito-sides/Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Spicy Fries</t>
+          <t>Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr"/>
       <c r="E152" s="10" t="n">
-        <v>8.99</v>
+        <v>4.49</v>
       </c>
       <c r="F152" s="10" t="n"/>
       <c r="G152" s="10" t="n"/>
@@ -6032,7 +6032,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Deep Fried Pepperoni</t>
+          <t>burrito-sides/Chips &amp; Queso — Small</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -6042,16 +6042,12 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Deep Fried Pepperoni</t>
-        </is>
-      </c>
-      <c r="D153" s="10" t="inlineStr">
-        <is>
-          <t>With honey mustard sauce.</t>
-        </is>
-      </c>
+          <t>Chips &amp; Queso — Small</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr"/>
       <c r="E153" s="10" t="n">
-        <v>12.99</v>
+        <v>3.49</v>
       </c>
       <c r="F153" s="10" t="n"/>
       <c r="G153" s="10" t="n"/>
@@ -6062,7 +6058,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
+          <t>burrito-sides/Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -6072,12 +6068,12 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Add Chips &amp; Salsa + a Can of Pop</t>
+          <t>Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr"/>
       <c r="E154" s="10" t="n">
-        <v>3.49</v>
+        <v>6.49</v>
       </c>
       <c r="F154" s="10" t="n"/>
       <c r="G154" s="10" t="n"/>
@@ -6088,7 +6084,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Brownie</t>
+          <t>burrito-sides/Chips &amp; Guac — Small</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
@@ -6098,12 +6094,12 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Chips &amp; Guac — Small</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr"/>
       <c r="E155" s="10" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="F155" s="10" t="n"/>
       <c r="G155" s="10" t="n"/>
@@ -6111,12 +6107,172 @@
       <c r="I155" s="10" t="inlineStr"/>
       <c r="J155" s="10" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Chips &amp; Guac — Large</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Chips &amp; Guac — Large</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr"/>
+      <c r="E156" s="10" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F156" s="10" t="n"/>
+      <c r="G156" s="10" t="n"/>
+      <c r="H156" s="10" t="n"/>
+      <c r="I156" s="10" t="inlineStr"/>
+      <c r="J156" s="10" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Fries Supreme</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Fries Supreme</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr"/>
+      <c r="E157" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F157" s="10" t="n"/>
+      <c r="G157" s="10" t="n"/>
+      <c r="H157" s="10" t="n"/>
+      <c r="I157" s="10" t="inlineStr"/>
+      <c r="J157" s="10" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Spicy Fries</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Spicy Fries</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr"/>
+      <c r="E158" s="10" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F158" s="10" t="n"/>
+      <c r="G158" s="10" t="n"/>
+      <c r="H158" s="10" t="n"/>
+      <c r="I158" s="10" t="inlineStr"/>
+      <c r="J158" s="10" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Deep Fried Pepperoni</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>Deep Fried Pepperoni</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>With honey mustard sauce.</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="F159" s="10" t="n"/>
+      <c r="G159" s="10" t="n"/>
+      <c r="H159" s="10" t="n"/>
+      <c r="I159" s="10" t="inlineStr"/>
+      <c r="J159" s="10" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Add Chips &amp; Salsa + a Can of Pop</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr"/>
+      <c r="E160" s="10" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F160" s="10" t="n"/>
+      <c r="G160" s="10" t="n"/>
+      <c r="H160" s="10" t="n"/>
+      <c r="I160" s="10" t="inlineStr"/>
+      <c r="J160" s="10" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Brownie</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Brownie</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr"/>
+      <c r="E161" s="10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="F161" s="10" t="n"/>
+      <c r="G161" s="10" t="n"/>
+      <c r="H161" s="10" t="n"/>
+      <c r="I161" s="10" t="inlineStr"/>
+      <c r="J161" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J155" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
+    <dataValidation sqref="J5:J161" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
       <formula1>=Lists!$B$1:$B$41</formula1>
     </dataValidation>
   </dataValidations>
@@ -6580,7 +6736,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>

--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Cold cut, pizza or real turkey.</t>
+          <t>Two large subs: cold cut, pizza or real turkey.</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
@@ -1228,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2250,7 +2250,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>donair-plates/Small Donair Plate</t>
+          <t>donair-plates/Donair Plate</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Small Donair Plate</t>
+          <t>Donair Plate</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -2271,10 +2271,16 @@
       <c r="E28" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="F28" s="10" t="n"/>
+      <c r="F28" s="10" t="n">
+        <v>17.45</v>
+      </c>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
           <t>donair-plate</t>
@@ -2284,37 +2290,47 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>donair-plates/Large Donair Plate</t>
+          <t>donair-fried/Donair Egg Rolls</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Donair Plates</t>
+          <t>Donair, Deep Fried</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Large Donair Plate</t>
+          <t>Donair Egg Rolls</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Fries and donair meat, topped with mozzarella, onions, tomatoes and donair sauce.</t>
+          <t>Donair, rolled and fried. Order more than one.</t>
         </is>
       </c>
       <c r="E29" s="10" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="F29" s="10" t="n"/>
+        <v>2.95</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>32.95</v>
+      </c>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Each / Dozen</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>donair-egg-roll</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Egg Roll</t>
+          <t>donair-fried/Donair Pogos</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -2324,195 +2340,237 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Donair Egg Roll</t>
+          <t>Donair Pogos</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Donair, rolled and fried. Order more than one.</t>
+          <t>Donair on a stick in batter. Yes, really.</t>
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="F30" s="10" t="n"/>
+        <v>3.95</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>43.95</v>
+      </c>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="inlineStr"/>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Each / Dozen</t>
+        </is>
+      </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>donair-egg-roll</t>
+          <t>donair-pogo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Egg Rolls — Dozen</t>
+          <t>poutine/Classic Poutine</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Donair, Deep Fried</t>
+          <t>Poutine</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Donair Egg Rolls — Dozen</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>Classic Poutine</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Curds, gravy, fries. Done right.</t>
+        </is>
+      </c>
       <c r="E31" s="10" t="n">
-        <v>32.95</v>
-      </c>
-      <c r="F31" s="10" t="n"/>
+        <v>9.449999999999999</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>13.25</v>
+      </c>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>poutine</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Pogo</t>
+          <t>poutine/Donair Poutine</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Donair, Deep Fried</t>
+          <t>Poutine</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Donair Pogo</t>
+          <t>Donair Poutine</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Donair on a stick in batter. Yes, really.</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="F32" s="10" t="n"/>
+          <t>With donair meat and a line of donair sauce.</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n">
+        <v>15.25</v>
+      </c>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>donair-pogo</t>
-        </is>
-      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>donair-fried/Donair Pogos — Dozen</t>
+          <t>poutine/Chicken Poutine</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Donair, Deep Fried</t>
+          <t>Poutine</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Donair Pogos — Dozen</t>
+          <t>Chicken Poutine</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
-      <c r="E33" s="10" t="n">
-        <v>43.95</v>
-      </c>
-      <c r="F33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n">
+        <v>14.95</v>
+      </c>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>donair-sauce/Small Donair Sauce</t>
+          <t>poutine/Hamburger Poutine</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Donair Sauce</t>
+          <t>Poutine</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Small Donair Sauce</t>
+          <t>Hamburger Poutine</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
-      <c r="E34" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n">
+        <v>14.95</v>
+      </c>
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>donair-sauce/Large Donair Sauce</t>
+          <t>poutine/Greek Poutine</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Donair Sauce</t>
+          <t>Poutine</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Large Donair Sauce</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F35" s="10" t="n"/>
+          <t>Greek Poutine</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Feta, tomato, red onion, olives.</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n">
+        <v>14.95</v>
+      </c>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>donair-sauce/Extra Large Donair Sauce</t>
+          <t>poutine/Extra Cheese</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Donair Sauce</t>
+          <t>Poutine</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Extra Large Donair Sauce</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr"/>
       <c r="E36" s="10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F36" s="10" t="n"/>
+        <v>2.95</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>3.45</v>
+      </c>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>poutine/Classic Poutine</t>
+          <t>poutine/Extra Gravy</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -2522,19 +2580,15 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Classic Poutine</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Curds, gravy, fries. Done right.</t>
-        </is>
-      </c>
+          <t>Extra Gravy</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>13.25</v>
+        <v>3.45</v>
       </c>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
@@ -2543,66 +2597,74 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>poutine</t>
-        </is>
-      </c>
+      <c r="J37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>poutine/Donair Poutine</t>
+          <t>wings/Chicken Wings</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Poutine</t>
+          <t>Chicken Wings</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Donair Poutine</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>With donair meat and a line of donair sauce.</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="n"/>
+          <t>Chicken Wings</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr"/>
+      <c r="E38" s="10" t="n">
+        <v>13.95</v>
+      </c>
       <c r="F38" s="10" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
+        <v>20.95</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>39.95</v>
+      </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr"/>
+          <t>10 wings / 15 wings / 20 wings / 30 wings</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>chicken-wings</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>poutine/Chicken Poutine</t>
+          <t>nachos/Nachos</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Poutine</t>
+          <t>Nachos</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Chicken Poutine</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr"/>
-      <c r="E39" s="10" t="n"/>
+          <t>Nachos</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Green onion, tomato, black olives, jalapeño, mozzarella and cheddar. Salsa and sour cream on the side.</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>12.95</v>
+      </c>
       <c r="F39" s="10" t="n">
-        <v>14.95</v>
+        <v>16.95</v>
       </c>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
@@ -2611,29 +2673,33 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>nachos</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>poutine/Hamburger Poutine</t>
+          <t>nachos/Extra Cheese</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Poutine</t>
+          <t>Nachos</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Hamburger Poutine</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n">
-        <v>14.95</v>
-      </c>
+      <c r="E40" s="10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F40" s="10" t="n"/>
       <c r="G40" s="10" t="n"/>
       <c r="H40" s="10" t="n"/>
       <c r="I40" s="10" t="inlineStr">
@@ -2646,97 +2712,103 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>poutine/Greek Poutine</t>
+          <t>burgers/Hamburger</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Poutine</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Greek Poutine</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Feta, tomato, red onion, olives.</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="n"/>
+          <t>Hamburger</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr"/>
+      <c r="E41" s="10" t="n">
+        <v>7.75</v>
+      </c>
       <c r="F41" s="10" t="n">
-        <v>14.95</v>
+        <v>12.95</v>
       </c>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr"/>
+          <t>Burger / Platter</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>hamburger</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>poutine/Extra Cheese</t>
+          <t>burgers/Cheeseburger</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Poutine</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
+          <t>Cheeseburger</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr"/>
       <c r="E42" s="10" t="n">
-        <v>2.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>3.45</v>
+        <v>13.25</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr"/>
+          <t>Burger / Platter</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>cheeseburger</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>poutine/Extra Gravy</t>
+          <t>burgers/Chicken Burger</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Poutine</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Extra Gravy</t>
+          <t>Chicken Burger</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr"/>
       <c r="E43" s="10" t="n">
-        <v>2.25</v>
+        <v>8.25</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>3.45</v>
+        <v>12.95</v>
       </c>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Burger / Platter</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr"/>
@@ -2744,142 +2816,162 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>wings/10 Wings</t>
+          <t>burgers/Donair Burger</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Chicken Wings</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>10 Wings</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr"/>
+          <t>Donair Burger</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Donair meat and sauce on a burger. A Dartmouth idea.</t>
+        </is>
+      </c>
       <c r="E44" s="10" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="F44" s="10" t="n">
         <v>13.95</v>
       </c>
-      <c r="F44" s="10" t="n"/>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>chicken-wings</t>
-        </is>
-      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Burger / Platter</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>wings/15 Wings</t>
+          <t>burgers/Pizza Burger</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Chicken Wings</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>15 Wings</t>
+          <t>Pizza Burger</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr"/>
       <c r="E45" s="10" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F45" s="10" t="n"/>
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>13.45</v>
+      </c>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="inlineStr"/>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Burger / Platter</t>
+        </is>
+      </c>
       <c r="J45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>wings/20 Wings</t>
+          <t>burgers/Add Bacon</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Chicken Wings</t>
+          <t>Burgers</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>20 Wings</t>
+          <t>Add Bacon</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr"/>
       <c r="E46" s="10" t="n">
-        <v>26.95</v>
-      </c>
-      <c r="F46" s="10" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="inlineStr"/>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Burger / Platter</t>
+        </is>
+      </c>
       <c r="J46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>wings/30 Wings</t>
+          <t>sides/Club House Sandwich with Fries</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Chicken Wings</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>30 Wings</t>
+          <t>Club House Sandwich with Fries</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>For the room.</t>
+          <t>Real turkey.</t>
         </is>
       </c>
       <c r="E47" s="10" t="n">
-        <v>39.95</v>
+        <v>15.95</v>
       </c>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>club-sandwich</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>nachos/Nachos</t>
+          <t>sides/Hot Hamburger with Gravy &amp; Fries</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Nachos</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Nachos</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Green onion, tomato, black olives, jalapeño, mozzarella and cheddar. Salsa and sour cream on the side.</t>
-        </is>
-      </c>
+          <t>Hot Hamburger with Gravy &amp; Fries</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr"/>
       <c r="E48" s="10" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="F48" s="10" t="n">
-        <v>16.95</v>
-      </c>
+        <v>13.95</v>
+      </c>
+      <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
       <c r="H48" s="10" t="n"/>
       <c r="I48" s="10" t="inlineStr">
@@ -2887,31 +2979,27 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>nachos</t>
-        </is>
-      </c>
+      <c r="J48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>nachos/Add Chicken, Hamburger or Bacon</t>
+          <t>sides/Hot Turkey with Gravy &amp; Fries</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Nachos</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Add Chicken, Hamburger or Bacon</t>
+          <t>Hot Turkey with Gravy &amp; Fries</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="10" t="n">
-        <v>3.95</v>
+        <v>13.95</v>
       </c>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
@@ -2926,24 +3014,26 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>nachos/Extra Cheese</t>
+          <t>sides/Fries</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Nachos</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
+          <t>Fries</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr"/>
       <c r="E50" s="10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F50" s="10" t="n"/>
+        <v>4.95</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>6.95</v>
+      </c>
       <c r="G50" s="10" t="n"/>
       <c r="H50" s="10" t="n"/>
       <c r="I50" s="10" t="inlineStr">
@@ -2951,144 +3041,136 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr"/>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>fries</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>burgers/Hamburger</t>
+          <t>sides/Large Onion Rings</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Hamburger</t>
+          <t>Large Onion Rings</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr"/>
       <c r="E51" s="10" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="F51" s="10" t="n">
-        <v>12.95</v>
-      </c>
+        <v>6.95</v>
+      </c>
+      <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>Burger / Platter</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>hamburger</t>
+          <t>onion-rings</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>burgers/Cheeseburger</t>
+          <t>sides/9 Chicken Fries</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Cheeseburger</t>
+          <t>9 Chicken Fries</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr"/>
       <c r="E52" s="10" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="F52" s="10" t="n">
-        <v>13.25</v>
-      </c>
+        <v>9.949999999999999</v>
+      </c>
+      <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>Burger / Platter</t>
-        </is>
-      </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t>cheeseburger</t>
-        </is>
-      </c>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>burgers/Chicken Burger</t>
+          <t>sides/9 Mozza Sticks</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Chicken Burger</t>
+          <t>9 Mozza Sticks</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr"/>
       <c r="E53" s="10" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="F53" s="10" t="n">
         <v>12.95</v>
       </c>
+      <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>Burger / Platter</t>
-        </is>
-      </c>
-      <c r="J53" s="10" t="inlineStr"/>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>mozza-sticks</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>burgers/Donair Burger</t>
+          <t>sides/Spicy Fries</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Donair Burger</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>Donair meat and sauce on a burger. A Dartmouth idea.</t>
-        </is>
-      </c>
+          <t>Spicy Fries</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr"/>
       <c r="E54" s="10" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="F54" s="10" t="n">
-        <v>13.95</v>
-      </c>
+        <v>8.99</v>
+      </c>
+      <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
       <c r="H54" s="10" t="n"/>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>Burger / Platter</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr"/>
@@ -3096,31 +3178,29 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>burgers/Pizza Burger</t>
+          <t>sides/Brownie</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Pizza Burger</t>
+          <t>Brownie</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr"/>
       <c r="E55" s="10" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="F55" s="10" t="n">
-        <v>13.45</v>
-      </c>
+        <v>2.99</v>
+      </c>
+      <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>Burger / Platter</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr"/>
@@ -3128,31 +3208,29 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>burgers/Add Bacon</t>
+          <t>sides/Chips &amp; Salsa</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Burgers</t>
+          <t>Sides &amp; Plates</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Add Bacon</t>
+          <t>Chips &amp; Salsa</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr"/>
       <c r="E56" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>1.25</v>
-      </c>
+        <v>2.95</v>
+      </c>
+      <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
       <c r="H56" s="10" t="n"/>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>Burger / Platter</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr"/>
@@ -3160,28 +3238,30 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>sides/Club House Sandwich with Fries</t>
+          <t>bread-sticks/Yum Yums</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Bread Sticks ("Yum Yums")</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Club House Sandwich with Fries</t>
+          <t>Yum Yums</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Real turkey.</t>
+          <t>Tossed in parmesan, with donair dipping sauce.</t>
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="F57" s="10" t="n"/>
+        <v>14.45</v>
+      </c>
+      <c r="F57" s="10" t="n">
+        <v>18.95</v>
+      </c>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n"/>
       <c r="I57" s="10" t="inlineStr">
@@ -3191,230 +3271,230 @@
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>club-sandwich</t>
+          <t>bread-sticks</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>sides/Hot Hamburger with Gravy &amp; Fries</t>
+          <t>wraps-pockets/Pita Wrap</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Wraps &amp; Pockets</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Hot Hamburger with Gravy &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr"/>
+          <t>Pita Wrap</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Your pick of filling, rolled in a warm pita.</t>
+        </is>
+      </c>
       <c r="E58" s="10" t="n">
-        <v>13.95</v>
+        <v>11.95</v>
       </c>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
       <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr"/>
+      <c r="I58" s="10" t="inlineStr"/>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>pita-wrap</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>sides/Hot Turkey with Gravy &amp; Fries</t>
+          <t>wraps-pockets/Pocket</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Wraps &amp; Pockets</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Hot Turkey with Gravy &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr"/>
+          <t>Pocket</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Folded, stuffed and cooked the way you like it.</t>
+        </is>
+      </c>
       <c r="E59" s="10" t="n">
-        <v>13.95</v>
+        <v>17.45</v>
       </c>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J59" s="10" t="inlineStr"/>
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>pocket</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>sides/Fries</t>
+          <t>chicken/Chicken &amp; Chips</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Fries</t>
+          <t>Chicken &amp; Chips</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr"/>
       <c r="E60" s="10" t="n">
-        <v>4.95</v>
+        <v>10.95</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="G60" s="10" t="n"/>
+        <v>13.95</v>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>16.95</v>
+      </c>
       <c r="H60" s="10" t="n"/>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>1 piece / 2 pieces / 3 pieces</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>fries</t>
+          <t>fried-chicken</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>sides/Large Onion Rings</t>
+          <t>chicken/Extra Piece of Chicken</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Large Onion Rings</t>
+          <t>Extra Piece of Chicken</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr"/>
       <c r="E61" s="10" t="n">
-        <v>6.95</v>
+        <v>4.25</v>
       </c>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J61" s="10" t="inlineStr">
-        <is>
-          <t>onion-rings</t>
-        </is>
-      </c>
+      <c r="I61" s="10" t="inlineStr"/>
+      <c r="J61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>sides/9 Chicken Fries</t>
+          <t>chicken/2 Chicken Legs &amp; Chips</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>9 Chicken Fries</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr"/>
+          <t>2 Chicken Legs &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Everyday special.</t>
+        </is>
+      </c>
       <c r="E62" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>11.95</v>
       </c>
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="10" t="n"/>
       <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I62" s="10" t="inlineStr"/>
       <c r="J62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>sides/9 Mozza Sticks</t>
+          <t>chicken/Chicken Family Pack</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>9 Mozza Sticks</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr"/>
+          <t>Chicken Family Pack</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>10 pieces, 2 large fries, gravy and coleslaw.</t>
+        </is>
+      </c>
       <c r="E63" s="10" t="n">
-        <v>12.95</v>
+        <v>45.95</v>
       </c>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J63" s="10" t="inlineStr">
-        <is>
-          <t>mozza-sticks</t>
-        </is>
-      </c>
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>sides/Cup of Gravy — Small</t>
+          <t>chicken/Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Cup of Gravy — Small</t>
+          <t>Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr"/>
       <c r="E64" s="10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="F64" s="10" t="n"/>
+        <v>9.949999999999999</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>17.95</v>
+      </c>
       <c r="G64" s="10" t="n"/>
       <c r="H64" s="10" t="n"/>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>6 pieces / 12 pieces</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr"/>
@@ -3422,244 +3502,240 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>sides/Cup of Gravy — Large</t>
+          <t>chicken/Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Cup of Gravy — Large</t>
+          <t>Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr"/>
       <c r="E65" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F65" s="10" t="n"/>
+        <v>16.95</v>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>29.95</v>
+      </c>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J65" s="10" t="inlineStr"/>
+          <t>5 pieces / 10 pieces</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>chicken-fingers</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>sides/Spicy Fries</t>
+          <t>salads-pasta/Caesar or Garden Salad</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Spicy Fries</t>
+          <t>Caesar or Garden Salad</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr"/>
       <c r="E66" s="10" t="n">
-        <v>8.99</v>
+        <v>11.45</v>
       </c>
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
       <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr"/>
+      <c r="I66" s="10" t="inlineStr"/>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>salad</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>sides/Brownie</t>
+          <t>salads-pasta/Greek Salad</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Greek Salad</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr"/>
       <c r="E67" s="10" t="n">
-        <v>2.99</v>
+        <v>12.45</v>
       </c>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I67" s="10" t="inlineStr"/>
       <c r="J67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>sides/Chips &amp; Salsa</t>
+          <t>salads-pasta/Lasagna with Garlic Bread</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Sides &amp; Plates</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Salsa</t>
+          <t>Lasagna with Garlic Bread</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr"/>
       <c r="E68" s="10" t="n">
-        <v>2.95</v>
+        <v>13.45</v>
       </c>
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr"/>
+      <c r="I68" s="10" t="inlineStr"/>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>lasagna</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>bread-sticks/Small Yum Yums</t>
+          <t>salads-pasta/Ravioli with Garlic Bread</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Bread Sticks ("Yum Yums")</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Small Yum Yums</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Tossed in parmesan, with donair dipping sauce.</t>
-        </is>
-      </c>
+          <t>Ravioli with Garlic Bread</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr"/>
       <c r="E69" s="10" t="n">
-        <v>14.45</v>
+        <v>13.45</v>
       </c>
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="inlineStr"/>
-      <c r="J69" s="10" t="inlineStr">
-        <is>
-          <t>bread-sticks</t>
-        </is>
-      </c>
+      <c r="J69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>bread-sticks/Large Yum Yums</t>
+          <t>sauces/Donair Sauce</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Bread Sticks ("Yum Yums")</t>
+          <t>Sauces</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Large Yum Yums</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>Tossed in parmesan, with donair dipping sauce.</t>
-        </is>
-      </c>
+          <t>Donair Sauce</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr"/>
       <c r="E70" s="10" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
+        <v>2.5</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>5.25</v>
+      </c>
       <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="inlineStr"/>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large / Extra Large</t>
+        </is>
+      </c>
       <c r="J70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>wraps-pockets/Pita Wrap</t>
+          <t>sauces/Gravy</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Wraps &amp; Pockets</t>
+          <t>Sauces</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Pita Wrap</t>
+          <t>Gravy</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Pizza, donair, cold cut, club, vegetarian, chicken, turkey or chicken Caesar.</t>
+          <t>Homemade.</t>
         </is>
       </c>
       <c r="E71" s="10" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="F71" s="10" t="n"/>
+        <v>1.95</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>3.15</v>
+      </c>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="inlineStr"/>
-      <c r="J71" s="10" t="inlineStr">
-        <is>
-          <t>pita-wrap</t>
-        </is>
-      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>wraps-pockets/Pocket — Pizza, Chicken, Meats or Vegetarian</t>
+          <t>dips/Cheddar Chipotle Dip</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Wraps &amp; Pockets</t>
+          <t>Dips</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Pocket — Pizza, Chicken, Meats or Vegetarian</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Oven baked or deep fried.</t>
-        </is>
-      </c>
+          <t>Cheddar Chipotle Dip</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr"/>
       <c r="E72" s="10" t="n">
-        <v>17.45</v>
+        <v>1.75</v>
       </c>
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="10" t="n"/>
@@ -3670,86 +3746,74 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>wraps-pockets/Pocket — Donair or Steak</t>
+          <t>dips/Creamy Ranch Dip</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Wraps &amp; Pockets</t>
+          <t>Dips</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Pocket — Donair or Steak</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>Oven baked or deep fried.</t>
-        </is>
-      </c>
+          <t>Creamy Ranch Dip</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr"/>
       <c r="E73" s="10" t="n">
-        <v>18.45</v>
+        <v>1.75</v>
       </c>
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="inlineStr"/>
-      <c r="J73" s="10" t="inlineStr">
-        <is>
-          <t>pocket</t>
-        </is>
-      </c>
+      <c r="J73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken &amp; Chips — 1 pc</t>
+          <t>dips/Creamy Garlic Dip</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Dips</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Chicken &amp; Chips — 1 pc</t>
+          <t>Creamy Garlic Dip</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr"/>
       <c r="E74" s="10" t="n">
-        <v>10.95</v>
+        <v>1.75</v>
       </c>
       <c r="F74" s="10" t="n"/>
       <c r="G74" s="10" t="n"/>
       <c r="H74" s="10" t="n"/>
       <c r="I74" s="10" t="inlineStr"/>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>fried-chicken</t>
-        </is>
-      </c>
+      <c r="J74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken &amp; Chips — 2 pc</t>
+          <t>beverages/Any 519ml Pop</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Chicken &amp; Chips — 2 pc</t>
+          <t>Any 519ml Pop</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr"/>
       <c r="E75" s="10" t="n">
-        <v>13.95</v>
+        <v>2.59</v>
       </c>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
@@ -3760,22 +3824,22 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken &amp; Chips — 3 pc</t>
+          <t>beverages/Any Juice, Gatorade, G2 or Energy Drink</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Chicken &amp; Chips — 3 pc</t>
+          <t>Any Juice, Gatorade, G2 or Energy Drink</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr"/>
       <c r="E76" s="10" t="n">
-        <v>16.95</v>
+        <v>3.39</v>
       </c>
       <c r="F76" s="10" t="n"/>
       <c r="G76" s="10" t="n"/>
@@ -3786,22 +3850,22 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>chicken/Extra Piece of Chicken</t>
+          <t>beverages/Chocolate Milk</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Extra Piece of Chicken</t>
+          <t>Chocolate Milk</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr"/>
       <c r="E77" s="10" t="n">
-        <v>4.25</v>
+        <v>2.79</v>
       </c>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
@@ -3812,26 +3876,22 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>chicken/2 Chicken Legs &amp; Chips</t>
+          <t>beverages/Any 355ml Pop</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>2 Chicken Legs &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>Everyday special.</t>
-        </is>
-      </c>
+          <t>Any 355ml Pop</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr"/>
       <c r="E78" s="10" t="n">
-        <v>11.95</v>
+        <v>1.59</v>
       </c>
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="10" t="n"/>
@@ -3842,26 +3902,22 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken Family Pack</t>
+          <t>beverages/Any 2L Pop</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Chicken Family Pack</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>10 pieces, 2 large fries, gravy and coleslaw.</t>
-        </is>
-      </c>
+          <t>Any 2L Pop</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr"/>
       <c r="E79" s="10" t="n">
-        <v>45.95</v>
+        <v>4.19</v>
       </c>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
@@ -3872,22 +3928,22 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>chicken/6 Chicken Nuggets &amp; Fries</t>
+          <t>beverages/Aquafina Water 591ml</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>6 Chicken Nuggets &amp; Fries</t>
+          <t>Aquafina Water 591ml</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr"/>
       <c r="E80" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="F80" s="10" t="n"/>
       <c r="G80" s="10" t="n"/>
@@ -3898,78 +3954,94 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>chicken/12 Chicken Nuggets &amp; Fries</t>
+          <t>fish/Fish &amp; Chips</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>12 Chicken Nuggets &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr"/>
+          <t>Fish &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Fresh haddock and fries.</t>
+        </is>
+      </c>
       <c r="E81" s="10" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="G81" s="10" t="n">
         <v>17.95</v>
       </c>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="inlineStr"/>
-      <c r="J81" s="10" t="inlineStr"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>1 piece / 2 pieces / 3 pieces</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>fish-and-chips</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>chicken/5 Chicken Fingers &amp; Fries</t>
+          <t>fish/Extra Piece of Fish</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>5 Chicken Fingers &amp; Fries</t>
+          <t>Extra Piece of Fish</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr"/>
       <c r="E82" s="10" t="n">
-        <v>16.95</v>
+        <v>4.95</v>
       </c>
       <c r="F82" s="10" t="n"/>
       <c r="G82" s="10" t="n"/>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="inlineStr"/>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>chicken-fingers</t>
-        </is>
-      </c>
+      <c r="J82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>chicken/10 Chicken Fingers &amp; Fries</t>
+          <t>fish/Fish Family Pack</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>10 Chicken Fingers &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr"/>
+          <t>Fish Family Pack</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
+        </is>
+      </c>
       <c r="E83" s="10" t="n">
-        <v>29.95</v>
+        <v>46.95</v>
       </c>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
@@ -3980,22 +4052,26 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Caesar or Garden Salad</t>
+          <t>seafood/Scallops &amp; Chips</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Caesar or Garden Salad</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr"/>
+          <t>Scallops &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>10 scallops.</t>
+        </is>
+      </c>
       <c r="E84" s="10" t="n">
-        <v>11.45</v>
+        <v>14.95</v>
       </c>
       <c r="F84" s="10" t="n"/>
       <c r="G84" s="10" t="n"/>
@@ -4003,29 +4079,33 @@
       <c r="I84" s="10" t="inlineStr"/>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>scallops</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Greek Salad</t>
+          <t>seafood/Clams &amp; Chips</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Greek Salad</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr"/>
+          <t>Clams &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Two cups of clams.</t>
+        </is>
+      </c>
       <c r="E85" s="10" t="n">
-        <v>12.45</v>
+        <v>14.95</v>
       </c>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
@@ -4036,623 +4116,731 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Add Chicken — Crispy or Grilled</t>
+          <t>seafood/Shrimp &amp; Chips</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Add Chicken — Crispy or Grilled</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr"/>
+          <t>Shrimp &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>12 shrimp.</t>
+        </is>
+      </c>
       <c r="E86" s="10" t="n">
-        <v>2.95</v>
+        <v>14.95</v>
       </c>
       <c r="F86" s="10" t="n"/>
       <c r="G86" s="10" t="n"/>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="inlineStr"/>
-      <c r="J86" s="10" t="inlineStr"/>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>shrimp</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Lasagna with Garlic Bread</t>
+          <t>seafood/Seafood Platter</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Lasagna with Garlic Bread</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr"/>
+          <t>Seafood Platter</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
+        </is>
+      </c>
       <c r="E87" s="10" t="n">
-        <v>13.45</v>
+        <v>23.95</v>
       </c>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="inlineStr"/>
-      <c r="J87" s="10" t="inlineStr">
-        <is>
-          <t>lasagna</t>
-        </is>
-      </c>
+      <c r="J87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Ravioli with Garlic Bread</t>
+          <t>seafood/Extra Coleslaw</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Ravioli with Garlic Bread</t>
+          <t>Extra Coleslaw</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr"/>
       <c r="E88" s="10" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="F88" s="10" t="n"/>
+        <v>2.25</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>3.45</v>
+      </c>
       <c r="G88" s="10" t="n"/>
       <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="inlineStr"/>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any 519ml Pop</t>
+          <t>subs/Cold Cut</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Cold Drinks</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Any 519ml Pop</t>
+          <t>Cold Cut</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr"/>
       <c r="E89" s="10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="F89" s="10" t="n"/>
+        <v>10.95</v>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>13.25</v>
+      </c>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
-      <c r="I89" s="10" t="inlineStr"/>
-      <c r="J89" s="10" t="inlineStr"/>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>cold-cut-sub</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any Juice, Gatorade, G2 or Energy Drink</t>
+          <t>subs/Salami &amp; Ham</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Cold Drinks</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Any Juice, Gatorade, G2 or Energy Drink</t>
+          <t>Salami &amp; Ham</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr"/>
       <c r="E90" s="10" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="F90" s="10" t="n"/>
+        <v>10.95</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>13.25</v>
+      </c>
       <c r="G90" s="10" t="n"/>
       <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="inlineStr"/>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>beverages/Chocolate Milk</t>
+          <t>subs/Pizza Sub</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Cold Drinks</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Chocolate Milk</t>
+          <t>Pizza Sub</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr"/>
       <c r="E91" s="10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F91" s="10" t="n"/>
+        <v>10.95</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>13.25</v>
+      </c>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="inlineStr"/>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any 355ml Pop</t>
+          <t>subs/Vegetarian</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Cold Drinks</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Any 355ml Pop</t>
+          <t>Vegetarian</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr"/>
       <c r="E92" s="10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="F92" s="10" t="n"/>
+        <v>10.95</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>13.25</v>
+      </c>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="inlineStr"/>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any 2L Pop</t>
+          <t>subs/Real Turkey</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Cold Drinks</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Any 2L Pop</t>
+          <t>Real Turkey</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr"/>
       <c r="E93" s="10" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="F93" s="10" t="n"/>
+        <v>11.45</v>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>13.25</v>
+      </c>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="inlineStr"/>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>beverages/Aquafina Water 591ml</t>
+          <t>subs/Bubba</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Cold Drinks</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Aquafina Water 591ml</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr"/>
+          <t>Bubba</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>The one people ask for by name.</t>
+        </is>
+      </c>
       <c r="E94" s="10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="F94" s="10" t="n"/>
+        <v>11.95</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>14.25</v>
+      </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="inlineStr"/>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 1 pc</t>
+          <t>subs/Club</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 1 pc</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr"/>
       <c r="E95" s="10" t="n">
         <v>11.95</v>
       </c>
-      <c r="F95" s="10" t="n"/>
+      <c r="F95" s="10" t="n">
+        <v>14.25</v>
+      </c>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
-      <c r="I95" s="10" t="inlineStr"/>
-      <c r="J95" s="10" t="inlineStr">
-        <is>
-          <t>fish-and-chips</t>
-        </is>
-      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 2 pc</t>
+          <t>subs/Steak</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 2 pc</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr"/>
       <c r="E96" s="10" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="F96" s="10" t="n"/>
+        <v>11.95</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>14.95</v>
+      </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="inlineStr"/>
-      <c r="J96" s="10" t="inlineStr"/>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>steak-sub</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips — 3 pc</t>
+          <t>subs/Donair Sub</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips — 3 pc</t>
+          <t>Donair Sub</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr"/>
       <c r="E97" s="10" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F97" s="10" t="n"/>
+        <v>11.95</v>
+      </c>
+      <c r="F97" s="10" t="n">
+        <v>14.95</v>
+      </c>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="inlineStr"/>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>fish/Extra Piece of Fish</t>
+          <t>subs/Super Sub</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Extra Piece of Fish</t>
+          <t>Super Sub</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr"/>
       <c r="E98" s="10" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="F98" s="10" t="n"/>
+        <v>12.45</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>16.25</v>
+      </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
-      <c r="I98" s="10" t="inlineStr"/>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish Family Pack</t>
+          <t>subs/Garlic Bread</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Fish Family Pack</t>
-        </is>
-      </c>
-      <c r="D99" s="10" t="inlineStr">
-        <is>
-          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
-        </is>
-      </c>
+          <t>Garlic Bread</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr"/>
       <c r="E99" s="10" t="n">
-        <v>46.95</v>
-      </c>
-      <c r="F99" s="10" t="n"/>
+        <v>6.25</v>
+      </c>
+      <c r="F99" s="10" t="n">
+        <v>7.45</v>
+      </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="inlineStr"/>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>seafood/Scallops &amp; Chips</t>
+          <t>subs/Extra Cheese</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Scallops &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>10 scallops.</t>
-        </is>
-      </c>
+          <t>Extra Cheese</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr"/>
       <c r="E100" s="10" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="F100" s="10" t="n"/>
+        <v>2.75</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>3.95</v>
+      </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="inlineStr"/>
-      <c r="J100" s="10" t="inlineStr">
-        <is>
-          <t>scallops</t>
-        </is>
-      </c>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>seafood/Clams &amp; Chips</t>
+          <t>subs/Extra Meat</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Clams &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t>Two cups of clams.</t>
-        </is>
-      </c>
+          <t>Extra Meat</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr"/>
       <c r="E101" s="10" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="F101" s="10" t="n"/>
+        <v>3.95</v>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>4.75</v>
+      </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="inlineStr"/>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>seafood/Shrimp &amp; Chips</t>
+          <t>burritos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Shrimp &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="inlineStr">
-        <is>
-          <t>12 shrimp.</t>
-        </is>
-      </c>
+          <t>Beans &amp; Veggie</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr"/>
       <c r="E102" s="10" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
+        <v>7.99</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>10.99</v>
+      </c>
       <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="inlineStr"/>
-      <c r="J102" s="10" t="inlineStr">
-        <is>
-          <t>shrimp</t>
-        </is>
-      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
+      <c r="J102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>seafood/Seafood Platter</t>
+          <t>burritos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Seafood Platter</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
-        </is>
-      </c>
+          <t>Spicy Chicken</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr"/>
       <c r="E103" s="10" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
+        <v>9.99</v>
+      </c>
+      <c r="F103" s="10" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="inlineStr"/>
-      <c r="J103" s="10" t="inlineStr"/>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>burrito</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>seafood/Extra Coleslaw — Small</t>
+          <t>burritos/Ground Beef</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Extra Coleslaw — Small</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr"/>
       <c r="E104" s="10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
+        <v>9.99</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="inlineStr"/>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
       <c r="J104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>seafood/Extra Coleslaw — Large</t>
+          <t>burritos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Extra Coleslaw — Large</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr"/>
       <c r="E105" s="10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
+        <v>9.99</v>
+      </c>
+      <c r="F105" s="10" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="inlineStr"/>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
       <c r="J105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>subs/Cold Cut</t>
+          <t>burritos/Fish</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Cold Cut</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr"/>
       <c r="E106" s="10" t="n">
-        <v>10.95</v>
+        <v>9.99</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="G106" s="10" t="n"/>
+        <v>10.99</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>12.99</v>
+      </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J106" s="10" t="inlineStr">
-        <is>
-          <t>cold-cut-sub</t>
-        </is>
-      </c>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
+      <c r="J106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>subs/Salami &amp; Ham</t>
+          <t>burritos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Salami &amp; Ham</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr"/>
       <c r="E107" s="10" t="n">
-        <v>10.95</v>
+        <v>10.99</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="G107" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J107" s="10" t="inlineStr"/>
@@ -4660,31 +4848,33 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>subs/Pizza Sub</t>
+          <t>burritos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Pizza Sub</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr"/>
       <c r="E108" s="10" t="n">
-        <v>10.95</v>
+        <v>10.99</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="G108" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J108" s="10" t="inlineStr"/>
@@ -4692,31 +4882,33 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>subs/Vegetarian</t>
+          <t>burritos/Steak</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr"/>
       <c r="E109" s="10" t="n">
-        <v>10.95</v>
+        <v>10.99</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="G109" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Medium / Large</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr"/>
@@ -4724,25 +4916,25 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>subs/Real Turkey</t>
+          <t>rice-bowls/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Real Turkey</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr"/>
       <c r="E110" s="10" t="n">
-        <v>11.45</v>
+        <v>10.49</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>13.25</v>
+        <v>12.49</v>
       </c>
       <c r="G110" s="10" t="n"/>
       <c r="H110" s="10" t="n"/>
@@ -4751,34 +4943,34 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J110" s="10" t="inlineStr"/>
+      <c r="J110" s="10" t="inlineStr">
+        <is>
+          <t>rice-bowl</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>subs/Bubba</t>
+          <t>rice-bowls/Spicy Chicken</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Bubba</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>The one people ask for by name.</t>
-        </is>
-      </c>
+          <t>Spicy Chicken</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr"/>
       <c r="E111" s="10" t="n">
-        <v>11.95</v>
+        <v>11.49</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>14.25</v>
+        <v>13.49</v>
       </c>
       <c r="G111" s="10" t="n"/>
       <c r="H111" s="10" t="n"/>
@@ -4792,25 +4984,25 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>subs/Club</t>
+          <t>rice-bowls/Ground Beef</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr"/>
       <c r="E112" s="10" t="n">
-        <v>11.95</v>
+        <v>11.49</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>14.25</v>
+        <v>13.49</v>
       </c>
       <c r="G112" s="10" t="n"/>
       <c r="H112" s="10" t="n"/>
@@ -4824,25 +5016,25 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>subs/Steak</t>
+          <t>rice-bowls/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr"/>
       <c r="E113" s="10" t="n">
-        <v>11.95</v>
+        <v>11.49</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>14.95</v>
+        <v>13.49</v>
       </c>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
@@ -4851,34 +5043,30 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J113" s="10" t="inlineStr">
-        <is>
-          <t>steak-sub</t>
-        </is>
-      </c>
+      <c r="J113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>subs/Donair Sub</t>
+          <t>rice-bowls/Fish</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Donair Sub</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr"/>
       <c r="E114" s="10" t="n">
-        <v>11.95</v>
+        <v>11.49</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>14.95</v>
+        <v>13.49</v>
       </c>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
@@ -4892,25 +5080,25 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>subs/Super Sub</t>
+          <t>rice-bowls/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Super Sub</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr"/>
       <c r="E115" s="10" t="n">
-        <v>12.45</v>
+        <v>12.49</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>16.25</v>
+        <v>14.49</v>
       </c>
       <c r="G115" s="10" t="n"/>
       <c r="H115" s="10" t="n"/>
@@ -4924,25 +5112,25 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>subs/Garlic Bread</t>
+          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Garlic Bread</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr"/>
       <c r="E116" s="10" t="n">
-        <v>6.25</v>
+        <v>12.49</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>7.45</v>
+        <v>14.49</v>
       </c>
       <c r="G116" s="10" t="n"/>
       <c r="H116" s="10" t="n"/>
@@ -4956,25 +5144,25 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Cheese</t>
+          <t>rice-bowls/Steak</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr"/>
       <c r="E117" s="10" t="n">
-        <v>2.75</v>
+        <v>12.49</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>3.95</v>
+        <v>14.49</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
@@ -4988,620 +5176,498 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Meat</t>
+          <t>quesadillas/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Extra Meat</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr"/>
       <c r="E118" s="10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="F118" s="10" t="n">
-        <v>4.75</v>
-      </c>
+        <v>10.49</v>
+      </c>
+      <c r="F118" s="10" t="n"/>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J118" s="10" t="inlineStr"/>
+      <c r="I118" s="10" t="inlineStr"/>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>quesadilla</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>burritos/Beans &amp; Veggie</t>
+          <t>quesadillas/Spicy Chicken</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr"/>
       <c r="E119" s="10" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="F119" s="10" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="G119" s="10" t="n">
-        <v>10.99</v>
-      </c>
+        <v>11.49</v>
+      </c>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
-      <c r="I119" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
+      <c r="I119" s="10" t="inlineStr"/>
       <c r="J119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>burritos/Spicy Chicken</t>
+          <t>quesadillas/Ground Beef</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr"/>
       <c r="E120" s="10" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F120" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G120" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>11.49</v>
+      </c>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
-      <c r="J120" s="10" t="inlineStr">
-        <is>
-          <t>burrito</t>
-        </is>
-      </c>
+      <c r="I120" s="10" t="inlineStr"/>
+      <c r="J120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>burritos/Ground Beef</t>
+          <t>quesadillas/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr"/>
       <c r="E121" s="10" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F121" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G121" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>11.49</v>
+      </c>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
       <c r="H121" s="10" t="n"/>
-      <c r="I121" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
+      <c r="I121" s="10" t="inlineStr"/>
       <c r="J121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>burritos/Zesty Grilled Chicken</t>
+          <t>quesadillas/Fish</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr"/>
       <c r="E122" s="10" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F122" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G122" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>11.49</v>
+      </c>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
       <c r="H122" s="10" t="n"/>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
+      <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>burritos/Fish</t>
+          <t>quesadillas/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr"/>
       <c r="E123" s="10" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F123" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G123" s="10" t="n">
-        <v>12.99</v>
-      </c>
+        <v>12.49</v>
+      </c>
+      <c r="F123" s="10" t="n"/>
+      <c r="G123" s="10" t="n"/>
       <c r="H123" s="10" t="n"/>
-      <c r="I123" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
+      <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>burritos/Shawarma Chicken</t>
+          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr"/>
       <c r="E124" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F124" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G124" s="10" t="n">
-        <v>13.99</v>
-      </c>
+        <v>12.49</v>
+      </c>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
       <c r="H124" s="10" t="n"/>
-      <c r="I124" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
+      <c r="I124" s="10" t="inlineStr"/>
       <c r="J124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>burritos/Tequila-Lime Glazed Chicken</t>
+          <t>quesadillas/Steak</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr"/>
       <c r="E125" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F125" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G125" s="10" t="n">
-        <v>13.99</v>
-      </c>
+        <v>12.49</v>
+      </c>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
       <c r="H125" s="10" t="n"/>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
+      <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>burritos/Steak</t>
+          <t>tacos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr"/>
       <c r="E126" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F126" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G126" s="10" t="n">
-        <v>13.99</v>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
       <c r="H126" s="10" t="n"/>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>Small / Medium / Large</t>
-        </is>
-      </c>
-      <c r="J126" s="10" t="inlineStr"/>
+      <c r="I126" s="10" t="inlineStr"/>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>tacos</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Beans &amp; Veggie</t>
+          <t>tacos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr"/>
       <c r="E127" s="10" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="F127" s="10" t="n">
-        <v>12.49</v>
-      </c>
+        <v>10.99</v>
+      </c>
+      <c r="F127" s="10" t="n"/>
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="n"/>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J127" s="10" t="inlineStr">
-        <is>
-          <t>rice-bowl</t>
-        </is>
-      </c>
+      <c r="I127" s="10" t="inlineStr"/>
+      <c r="J127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Spicy Chicken</t>
+          <t>tacos/Ground Beef</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr"/>
       <c r="E128" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F128" s="10" t="n">
-        <v>13.49</v>
-      </c>
+        <v>10.99</v>
+      </c>
+      <c r="F128" s="10" t="n"/>
       <c r="G128" s="10" t="n"/>
       <c r="H128" s="10" t="n"/>
-      <c r="I128" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Ground Beef</t>
+          <t>tacos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr"/>
       <c r="E129" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F129" s="10" t="n">
-        <v>13.49</v>
-      </c>
+        <v>10.99</v>
+      </c>
+      <c r="F129" s="10" t="n"/>
       <c r="G129" s="10" t="n"/>
       <c r="H129" s="10" t="n"/>
-      <c r="I129" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I129" s="10" t="inlineStr"/>
       <c r="J129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Zesty Grilled Chicken</t>
+          <t>tacos/Fish</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr"/>
       <c r="E130" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F130" s="10" t="n">
-        <v>13.49</v>
-      </c>
+        <v>10.99</v>
+      </c>
+      <c r="F130" s="10" t="n"/>
       <c r="G130" s="10" t="n"/>
       <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Fish</t>
+          <t>tacos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr"/>
       <c r="E131" s="10" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="F131" s="10" t="n">
-        <v>13.49</v>
-      </c>
+        <v>11.99</v>
+      </c>
+      <c r="F131" s="10" t="n"/>
       <c r="G131" s="10" t="n"/>
       <c r="H131" s="10" t="n"/>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Shawarma Chicken</t>
+          <t>tacos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr"/>
       <c r="E132" s="10" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="F132" s="10" t="n">
-        <v>14.49</v>
-      </c>
+        <v>11.99</v>
+      </c>
+      <c r="F132" s="10" t="n"/>
       <c r="G132" s="10" t="n"/>
       <c r="H132" s="10" t="n"/>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
+          <t>tacos/Steak</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr"/>
       <c r="E133" s="10" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="F133" s="10" t="n">
-        <v>14.49</v>
-      </c>
+        <v>11.99</v>
+      </c>
+      <c r="F133" s="10" t="n"/>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Steak</t>
+          <t>burrito-sides/Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr"/>
       <c r="E134" s="10" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="F134" s="10" t="n">
-        <v>14.49</v>
-      </c>
+        <v>2.49</v>
+      </c>
+      <c r="F134" s="10" t="n"/>
       <c r="G134" s="10" t="n"/>
       <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I134" s="10" t="inlineStr"/>
       <c r="J134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Beans &amp; Veggie</t>
+          <t>burrito-sides/Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr"/>
       <c r="E135" s="10" t="n">
-        <v>10.49</v>
+        <v>4.49</v>
       </c>
       <c r="F135" s="10" t="n"/>
       <c r="G135" s="10" t="n"/>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="inlineStr"/>
-      <c r="J135" s="10" t="inlineStr">
-        <is>
-          <t>quesadilla</t>
-        </is>
-      </c>
+      <c r="J135" s="10" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Spicy Chicken</t>
+          <t>burrito-sides/Chips &amp; Queso — Small</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Chips &amp; Queso — Small</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr"/>
       <c r="E136" s="10" t="n">
-        <v>11.49</v>
+        <v>3.49</v>
       </c>
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="10" t="n"/>
@@ -5612,22 +5678,22 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Ground Beef</t>
+          <t>burrito-sides/Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr"/>
       <c r="E137" s="10" t="n">
-        <v>11.49</v>
+        <v>6.49</v>
       </c>
       <c r="F137" s="10" t="n"/>
       <c r="G137" s="10" t="n"/>
@@ -5638,22 +5704,22 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Zesty Grilled Chicken</t>
+          <t>burrito-sides/Chips &amp; Guac — Small</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Chips &amp; Guac — Small</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr"/>
       <c r="E138" s="10" t="n">
-        <v>11.49</v>
+        <v>3.99</v>
       </c>
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="10" t="n"/>
@@ -5664,22 +5730,22 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Fish</t>
+          <t>burrito-sides/Chips &amp; Guac — Large</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Chips &amp; Guac — Large</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr"/>
       <c r="E139" s="10" t="n">
-        <v>11.49</v>
+        <v>6.99</v>
       </c>
       <c r="F139" s="10" t="n"/>
       <c r="G139" s="10" t="n"/>
@@ -5690,22 +5756,22 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Shawarma Chicken</t>
+          <t>burrito-sides/Fries Supreme</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Fries Supreme</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr"/>
       <c r="E140" s="10" t="n">
-        <v>12.49</v>
+        <v>9.99</v>
       </c>
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
@@ -5716,22 +5782,22 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
+          <t>burrito-sides/Spicy Fries</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Spicy Fries</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr"/>
       <c r="E141" s="10" t="n">
-        <v>12.49</v>
+        <v>8.99</v>
       </c>
       <c r="F141" s="10" t="n"/>
       <c r="G141" s="10" t="n"/>
@@ -5742,22 +5808,26 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Steak</t>
+          <t>burrito-sides/Deep Fried Pepperoni</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="inlineStr"/>
+          <t>Deep Fried Pepperoni</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>With honey mustard sauce.</t>
+        </is>
+      </c>
       <c r="E142" s="10" t="n">
-        <v>12.49</v>
+        <v>12.99</v>
       </c>
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="10" t="n"/>
@@ -5768,52 +5838,48 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>tacos/Beans &amp; Veggie</t>
+          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Add Chips &amp; Salsa + a Can of Pop</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr"/>
       <c r="E143" s="10" t="n">
-        <v>9.99</v>
+        <v>3.49</v>
       </c>
       <c r="F143" s="10" t="n"/>
       <c r="G143" s="10" t="n"/>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="inlineStr"/>
-      <c r="J143" s="10" t="inlineStr">
-        <is>
-          <t>tacos</t>
-        </is>
-      </c>
+      <c r="J143" s="10" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>tacos/Spicy Chicken</t>
+          <t>burrito-sides/Brownie</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Sides</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Brownie</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr"/>
       <c r="E144" s="10" t="n">
-        <v>10.99</v>
+        <v>2.99</v>
       </c>
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
@@ -5821,458 +5887,12 @@
       <c r="I144" s="10" t="inlineStr"/>
       <c r="J144" s="10" t="inlineStr"/>
     </row>
-    <row r="145">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>tacos/Ground Beef</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>Tacos</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>Ground Beef</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr"/>
-      <c r="E145" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F145" s="10" t="n"/>
-      <c r="G145" s="10" t="n"/>
-      <c r="H145" s="10" t="n"/>
-      <c r="I145" s="10" t="inlineStr"/>
-      <c r="J145" s="10" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>tacos/Zesty Grilled Chicken</t>
-        </is>
-      </c>
-      <c r="B146" s="10" t="inlineStr">
-        <is>
-          <t>Tacos</t>
-        </is>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
-        <is>
-          <t>Zesty Grilled Chicken</t>
-        </is>
-      </c>
-      <c r="D146" s="10" t="inlineStr"/>
-      <c r="E146" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F146" s="10" t="n"/>
-      <c r="G146" s="10" t="n"/>
-      <c r="H146" s="10" t="n"/>
-      <c r="I146" s="10" t="inlineStr"/>
-      <c r="J146" s="10" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>tacos/Fish</t>
-        </is>
-      </c>
-      <c r="B147" s="10" t="inlineStr">
-        <is>
-          <t>Tacos</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>Fish</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="inlineStr"/>
-      <c r="E147" s="10" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F147" s="10" t="n"/>
-      <c r="G147" s="10" t="n"/>
-      <c r="H147" s="10" t="n"/>
-      <c r="I147" s="10" t="inlineStr"/>
-      <c r="J147" s="10" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>tacos/Shawarma Chicken</t>
-        </is>
-      </c>
-      <c r="B148" s="10" t="inlineStr">
-        <is>
-          <t>Tacos</t>
-        </is>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>Shawarma Chicken</t>
-        </is>
-      </c>
-      <c r="D148" s="10" t="inlineStr"/>
-      <c r="E148" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F148" s="10" t="n"/>
-      <c r="G148" s="10" t="n"/>
-      <c r="H148" s="10" t="n"/>
-      <c r="I148" s="10" t="inlineStr"/>
-      <c r="J148" s="10" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>tacos/Tequila-Lime Glazed Chicken</t>
-        </is>
-      </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t>Tacos</t>
-        </is>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>Tequila-Lime Glazed Chicken</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="inlineStr"/>
-      <c r="E149" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F149" s="10" t="n"/>
-      <c r="G149" s="10" t="n"/>
-      <c r="H149" s="10" t="n"/>
-      <c r="I149" s="10" t="inlineStr"/>
-      <c r="J149" s="10" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="9" t="inlineStr">
-        <is>
-          <t>tacos/Steak</t>
-        </is>
-      </c>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t>Tacos</t>
-        </is>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>Steak</t>
-        </is>
-      </c>
-      <c r="D150" s="10" t="inlineStr"/>
-      <c r="E150" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="F150" s="10" t="n"/>
-      <c r="G150" s="10" t="n"/>
-      <c r="H150" s="10" t="n"/>
-      <c r="I150" s="10" t="inlineStr"/>
-      <c r="J150" s="10" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Chips &amp; Salsa — Small</t>
-        </is>
-      </c>
-      <c r="B151" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C151" s="10" t="inlineStr">
-        <is>
-          <t>Chips &amp; Salsa — Small</t>
-        </is>
-      </c>
-      <c r="D151" s="10" t="inlineStr"/>
-      <c r="E151" s="10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="F151" s="10" t="n"/>
-      <c r="G151" s="10" t="n"/>
-      <c r="H151" s="10" t="n"/>
-      <c r="I151" s="10" t="inlineStr"/>
-      <c r="J151" s="10" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Chips &amp; Salsa — Large</t>
-        </is>
-      </c>
-      <c r="B152" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
-        <is>
-          <t>Chips &amp; Salsa — Large</t>
-        </is>
-      </c>
-      <c r="D152" s="10" t="inlineStr"/>
-      <c r="E152" s="10" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="F152" s="10" t="n"/>
-      <c r="G152" s="10" t="n"/>
-      <c r="H152" s="10" t="n"/>
-      <c r="I152" s="10" t="inlineStr"/>
-      <c r="J152" s="10" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Chips &amp; Queso — Small</t>
-        </is>
-      </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>Chips &amp; Queso — Small</t>
-        </is>
-      </c>
-      <c r="D153" s="10" t="inlineStr"/>
-      <c r="E153" s="10" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="F153" s="10" t="n"/>
-      <c r="G153" s="10" t="n"/>
-      <c r="H153" s="10" t="n"/>
-      <c r="I153" s="10" t="inlineStr"/>
-      <c r="J153" s="10" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Chips &amp; Queso — Large</t>
-        </is>
-      </c>
-      <c r="B154" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C154" s="10" t="inlineStr">
-        <is>
-          <t>Chips &amp; Queso — Large</t>
-        </is>
-      </c>
-      <c r="D154" s="10" t="inlineStr"/>
-      <c r="E154" s="10" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="F154" s="10" t="n"/>
-      <c r="G154" s="10" t="n"/>
-      <c r="H154" s="10" t="n"/>
-      <c r="I154" s="10" t="inlineStr"/>
-      <c r="J154" s="10" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Chips &amp; Guac — Small</t>
-        </is>
-      </c>
-      <c r="B155" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
-        <is>
-          <t>Chips &amp; Guac — Small</t>
-        </is>
-      </c>
-      <c r="D155" s="10" t="inlineStr"/>
-      <c r="E155" s="10" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F155" s="10" t="n"/>
-      <c r="G155" s="10" t="n"/>
-      <c r="H155" s="10" t="n"/>
-      <c r="I155" s="10" t="inlineStr"/>
-      <c r="J155" s="10" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Chips &amp; Guac — Large</t>
-        </is>
-      </c>
-      <c r="B156" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C156" s="10" t="inlineStr">
-        <is>
-          <t>Chips &amp; Guac — Large</t>
-        </is>
-      </c>
-      <c r="D156" s="10" t="inlineStr"/>
-      <c r="E156" s="10" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="F156" s="10" t="n"/>
-      <c r="G156" s="10" t="n"/>
-      <c r="H156" s="10" t="n"/>
-      <c r="I156" s="10" t="inlineStr"/>
-      <c r="J156" s="10" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Fries Supreme</t>
-        </is>
-      </c>
-      <c r="B157" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
-        <is>
-          <t>Fries Supreme</t>
-        </is>
-      </c>
-      <c r="D157" s="10" t="inlineStr"/>
-      <c r="E157" s="10" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F157" s="10" t="n"/>
-      <c r="G157" s="10" t="n"/>
-      <c r="H157" s="10" t="n"/>
-      <c r="I157" s="10" t="inlineStr"/>
-      <c r="J157" s="10" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Spicy Fries</t>
-        </is>
-      </c>
-      <c r="B158" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C158" s="10" t="inlineStr">
-        <is>
-          <t>Spicy Fries</t>
-        </is>
-      </c>
-      <c r="D158" s="10" t="inlineStr"/>
-      <c r="E158" s="10" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="F158" s="10" t="n"/>
-      <c r="G158" s="10" t="n"/>
-      <c r="H158" s="10" t="n"/>
-      <c r="I158" s="10" t="inlineStr"/>
-      <c r="J158" s="10" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Deep Fried Pepperoni</t>
-        </is>
-      </c>
-      <c r="B159" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
-        <is>
-          <t>Deep Fried Pepperoni</t>
-        </is>
-      </c>
-      <c r="D159" s="10" t="inlineStr">
-        <is>
-          <t>With honey mustard sauce.</t>
-        </is>
-      </c>
-      <c r="E159" s="10" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="F159" s="10" t="n"/>
-      <c r="G159" s="10" t="n"/>
-      <c r="H159" s="10" t="n"/>
-      <c r="I159" s="10" t="inlineStr"/>
-      <c r="J159" s="10" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
-        </is>
-      </c>
-      <c r="B160" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C160" s="10" t="inlineStr">
-        <is>
-          <t>Add Chips &amp; Salsa + a Can of Pop</t>
-        </is>
-      </c>
-      <c r="D160" s="10" t="inlineStr"/>
-      <c r="E160" s="10" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="F160" s="10" t="n"/>
-      <c r="G160" s="10" t="n"/>
-      <c r="H160" s="10" t="n"/>
-      <c r="I160" s="10" t="inlineStr"/>
-      <c r="J160" s="10" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="9" t="inlineStr">
-        <is>
-          <t>burrito-sides/Brownie</t>
-        </is>
-      </c>
-      <c r="B161" s="10" t="inlineStr">
-        <is>
-          <t>Sides</t>
-        </is>
-      </c>
-      <c r="C161" s="10" t="inlineStr">
-        <is>
-          <t>Brownie</t>
-        </is>
-      </c>
-      <c r="D161" s="10" t="inlineStr"/>
-      <c r="E161" s="10" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="F161" s="10" t="n"/>
-      <c r="G161" s="10" t="n"/>
-      <c r="H161" s="10" t="n"/>
-      <c r="I161" s="10" t="inlineStr"/>
-      <c r="J161" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J161" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
+    <dataValidation sqref="J5:J144" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
       <formula1>=Lists!$B$1:$B$41</formula1>
     </dataValidation>
   </dataValidations>

--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -834,27 +834,12 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>$2.00 | delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>home.facts</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
           <t>Free | parking</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="C16" s="11" t="inlineStr">
+    <row r="15">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Facts are written as  bold part | the rest  — e.g.  Free | parking</t>
         </is>
@@ -1228,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2141,7 +2126,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Spiced beef off the spit, sweet sauce, warm pita. The one we're known for.</t>
+          <t>Spiced beef off the spit with onions, tomatoes and sweet donair sauce on a warm pita. The one we're known for.</t>
         </is>
       </c>
       <c r="E25" s="10" t="n">
@@ -2425,7 +2410,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>With donair meat and a line of donair sauce.</t>
+          <t>With donair meat.</t>
         </is>
       </c>
       <c r="E32" s="10" t="n"/>
@@ -3346,45 +3331,33 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken &amp; Chips</t>
+          <t>wraps-pockets/Extra Cheese</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Wraps &amp; Pockets</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Chicken &amp; Chips</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr"/>
       <c r="E60" s="10" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="F60" s="10" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="G60" s="10" t="n">
-        <v>16.95</v>
-      </c>
+        <v>4.05</v>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>1 piece / 2 pieces / 3 pieces</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>fried-chicken</t>
-        </is>
-      </c>
+      <c r="I60" s="10" t="inlineStr"/>
+      <c r="J60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>chicken/Extra Piece of Chicken</t>
+          <t>chicken/Chicken &amp; Chips</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -3394,23 +3367,35 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Extra Piece of Chicken</t>
+          <t>Chicken &amp; Chips</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr"/>
       <c r="E61" s="10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
+        <v>10.95</v>
+      </c>
+      <c r="F61" s="10" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>16.95</v>
+      </c>
       <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="inlineStr"/>
-      <c r="J61" s="10" t="inlineStr"/>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>1 piece / 2 pieces / 3 pieces</t>
+        </is>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>fried-chicken</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>chicken/2 Chicken Legs &amp; Chips</t>
+          <t>chicken/Extra Piece of Chicken</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3420,16 +3405,12 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>2 Chicken Legs &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>Everyday special.</t>
-        </is>
-      </c>
+          <t>Extra Piece of Chicken</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr"/>
       <c r="E62" s="10" t="n">
-        <v>11.95</v>
+        <v>4.25</v>
       </c>
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="10" t="n"/>
@@ -3440,7 +3421,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken Family Pack</t>
+          <t>chicken/2 Chicken Legs &amp; Chips</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -3450,16 +3431,16 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Chicken Family Pack</t>
+          <t>2 Chicken Legs &amp; Chips</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>10 pieces, 2 large fries, gravy and coleslaw.</t>
+          <t>Everyday special.</t>
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>45.95</v>
+        <v>11.95</v>
       </c>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
@@ -3470,7 +3451,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken Nuggets &amp; Fries</t>
+          <t>chicken/Chicken Family Pack</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -3480,29 +3461,27 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Chicken Nuggets &amp; Fries</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr"/>
+          <t>Chicken Family Pack</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>10 pieces, 2 large fries, gravy and coleslaw.</t>
+        </is>
+      </c>
       <c r="E64" s="10" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>17.95</v>
-      </c>
+        <v>45.95</v>
+      </c>
+      <c r="F64" s="10" t="n"/>
       <c r="G64" s="10" t="n"/>
       <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>6 pieces / 12 pieces</t>
-        </is>
-      </c>
+      <c r="I64" s="10" t="inlineStr"/>
       <c r="J64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>chicken/Chicken Fingers &amp; Fries</t>
+          <t>chicken/Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -3512,63 +3491,65 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Chicken Fingers &amp; Fries</t>
+          <t>Chicken Nuggets &amp; Fries</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr"/>
       <c r="E65" s="10" t="n">
-        <v>16.95</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>29.95</v>
+        <v>17.95</v>
       </c>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>5 pieces / 10 pieces</t>
-        </is>
-      </c>
-      <c r="J65" s="10" t="inlineStr">
-        <is>
-          <t>chicken-fingers</t>
-        </is>
-      </c>
+          <t>6 pieces / 12 pieces</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Caesar or Garden Salad</t>
+          <t>chicken/Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Salads &amp; Pasta</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Caesar or Garden Salad</t>
+          <t>Chicken Fingers &amp; Fries</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr"/>
       <c r="E66" s="10" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="F66" s="10" t="n"/>
+        <v>16.95</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>29.95</v>
+      </c>
       <c r="G66" s="10" t="n"/>
       <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="inlineStr"/>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>5 pieces / 10 pieces</t>
+        </is>
+      </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>chicken-fingers</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Greek Salad</t>
+          <t>salads-pasta/Caesar or Garden Salad</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -3578,23 +3559,27 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Greek Salad</t>
+          <t>Caesar or Garden Salad</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr"/>
       <c r="E67" s="10" t="n">
-        <v>12.45</v>
+        <v>11.45</v>
       </c>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
       <c r="I67" s="10" t="inlineStr"/>
-      <c r="J67" s="10" t="inlineStr"/>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>salad</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Lasagna with Garlic Bread</t>
+          <t>salads-pasta/Greek Salad</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -3604,27 +3589,23 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Lasagna with Garlic Bread</t>
+          <t>Greek Salad</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr"/>
       <c r="E68" s="10" t="n">
-        <v>13.45</v>
+        <v>12.45</v>
       </c>
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n"/>
       <c r="I68" s="10" t="inlineStr"/>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>lasagna</t>
-        </is>
-      </c>
+      <c r="J68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>salads-pasta/Ravioli with Garlic Bread</t>
+          <t>salads-pasta/Lasagna with Garlic Bread</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -3634,7 +3615,7 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Ravioli with Garlic Bread</t>
+          <t>Lasagna with Garlic Bread</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr"/>
@@ -3645,46 +3626,42 @@
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="inlineStr"/>
-      <c r="J69" s="10" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>lasagna</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>sauces/Donair Sauce</t>
+          <t>salads-pasta/Ravioli with Garlic Bread</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Sauces</t>
+          <t>Salads &amp; Pasta</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Donair Sauce</t>
+          <t>Ravioli with Garlic Bread</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr"/>
       <c r="E70" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F70" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G70" s="10" t="n">
-        <v>5.25</v>
-      </c>
+        <v>13.45</v>
+      </c>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
       <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large / Extra Large</t>
-        </is>
-      </c>
+      <c r="I70" s="10" t="inlineStr"/>
       <c r="J70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>sauces/Gravy</t>
+          <t>sauces/Donair Sauce</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -3694,25 +3671,23 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Gravy</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>Homemade.</t>
-        </is>
-      </c>
+          <t>Donair Sauce</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr"/>
       <c r="E71" s="10" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G71" s="10" t="n"/>
+        <v>3.5</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>5.25</v>
+      </c>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
+          <t>Small / Large / Extra Large</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr"/>
@@ -3720,33 +3695,43 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>dips/Cheddar Chipotle Dip</t>
+          <t>sauces/Gravy</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Dips</t>
+          <t>Sauces</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Cheddar Chipotle Dip</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr"/>
+          <t>Gravy</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Homemade.</t>
+        </is>
+      </c>
       <c r="E72" s="10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F72" s="10" t="n"/>
+        <v>1.95</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>3.15</v>
+      </c>
       <c r="G72" s="10" t="n"/>
       <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="inlineStr"/>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
       <c r="J72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>dips/Creamy Ranch Dip</t>
+          <t>dips/Cheddar Chipotle Dip</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -3756,7 +3741,7 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Creamy Ranch Dip</t>
+          <t>Cheddar Chipotle Dip</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr"/>
@@ -3772,7 +3757,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>dips/Creamy Garlic Dip</t>
+          <t>dips/Creamy Ranch Dip</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -3782,7 +3767,7 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Creamy Garlic Dip</t>
+          <t>Creamy Ranch Dip</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr"/>
@@ -3798,22 +3783,22 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any 519ml Pop</t>
+          <t>dips/Creamy Garlic Dip</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Cold Drinks</t>
+          <t>Dips</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Any 519ml Pop</t>
+          <t>Creamy Garlic Dip</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr"/>
       <c r="E75" s="10" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
@@ -3824,7 +3809,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any Juice, Gatorade, G2 or Energy Drink</t>
+          <t>beverages/Any 519ml Pop</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -3834,12 +3819,12 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Any Juice, Gatorade, G2 or Energy Drink</t>
+          <t>Any 519ml Pop</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr"/>
       <c r="E76" s="10" t="n">
-        <v>3.39</v>
+        <v>2.59</v>
       </c>
       <c r="F76" s="10" t="n"/>
       <c r="G76" s="10" t="n"/>
@@ -3850,7 +3835,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>beverages/Chocolate Milk</t>
+          <t>beverages/Any Juice, Gatorade, G2 or Energy Drink</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -3860,12 +3845,12 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Chocolate Milk</t>
+          <t>Any Juice, Gatorade, G2 or Energy Drink</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr"/>
       <c r="E77" s="10" t="n">
-        <v>2.79</v>
+        <v>3.39</v>
       </c>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
@@ -3876,7 +3861,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any 355ml Pop</t>
+          <t>beverages/Chocolate Milk</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -3886,12 +3871,12 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Any 355ml Pop</t>
+          <t>Chocolate Milk</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr"/>
       <c r="E78" s="10" t="n">
-        <v>1.59</v>
+        <v>2.79</v>
       </c>
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="10" t="n"/>
@@ -3902,7 +3887,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any 2L Pop</t>
+          <t>beverages/Any 355ml Pop</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -3912,12 +3897,12 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Any 2L Pop</t>
+          <t>Any 355ml Pop</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr"/>
       <c r="E79" s="10" t="n">
-        <v>4.19</v>
+        <v>1.59</v>
       </c>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
@@ -3928,7 +3913,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>beverages/Aquafina Water 591ml</t>
+          <t>beverages/Any 2L Pop</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -3938,12 +3923,12 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Aquafina Water 591ml</t>
+          <t>Any 2L Pop</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr"/>
       <c r="E80" s="10" t="n">
-        <v>1.69</v>
+        <v>4.19</v>
       </c>
       <c r="F80" s="10" t="n"/>
       <c r="G80" s="10" t="n"/>
@@ -3954,49 +3939,33 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish &amp; Chips</t>
+          <t>beverages/Aquafina Water 591ml</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
+          <t>Cold Drinks</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Fish &amp; Chips</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>Fresh haddock and fries.</t>
-        </is>
-      </c>
+          <t>Aquafina Water 591ml</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr"/>
       <c r="E81" s="10" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="F81" s="10" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="G81" s="10" t="n">
-        <v>17.95</v>
-      </c>
+        <v>1.69</v>
+      </c>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>1 piece / 2 pieces / 3 pieces</t>
-        </is>
-      </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>fish-and-chips</t>
-        </is>
-      </c>
+      <c r="I81" s="10" t="inlineStr"/>
+      <c r="J81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>fish/Extra Piece of Fish</t>
+          <t>fish/Fish &amp; Chips</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -4006,23 +3975,39 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Extra Piece of Fish</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="inlineStr"/>
+          <t>Fish &amp; Chips</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Fresh haddock and fries.</t>
+        </is>
+      </c>
       <c r="E82" s="10" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
+        <v>11.95</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>17.95</v>
+      </c>
       <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="inlineStr"/>
-      <c r="J82" s="10" t="inlineStr"/>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>1 piece / 2 pieces / 3 pieces</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>fish-and-chips</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>fish/Fish Family Pack</t>
+          <t>fish/Extra Piece of Fish</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -4032,16 +4017,12 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Fish Family Pack</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
-        </is>
-      </c>
+          <t>Extra Piece of Fish</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr"/>
       <c r="E83" s="10" t="n">
-        <v>46.95</v>
+        <v>4.95</v>
       </c>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
@@ -4052,41 +4033,37 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>seafood/Scallops &amp; Chips</t>
+          <t>fish/Fish Family Pack</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>More Seafood</t>
+          <t>Fish &amp; Chips</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Scallops &amp; Chips</t>
+          <t>Fish Family Pack</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>10 scallops.</t>
+          <t>10 pieces of fish, 2 large fries, large gravy, coleslaw and tartar sauce.</t>
         </is>
       </c>
       <c r="E84" s="10" t="n">
-        <v>14.95</v>
+        <v>46.95</v>
       </c>
       <c r="F84" s="10" t="n"/>
       <c r="G84" s="10" t="n"/>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="inlineStr"/>
-      <c r="J84" s="10" t="inlineStr">
-        <is>
-          <t>scallops</t>
-        </is>
-      </c>
+      <c r="J84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>seafood/Clams &amp; Chips</t>
+          <t>seafood/Scallops &amp; Chips</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -4096,12 +4073,12 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Clams &amp; Chips</t>
+          <t>Scallops &amp; Chips</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Two cups of clams.</t>
+          <t>10 scallops.</t>
         </is>
       </c>
       <c r="E85" s="10" t="n">
@@ -4111,12 +4088,16 @@
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="inlineStr"/>
-      <c r="J85" s="10" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>scallops</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>seafood/Shrimp &amp; Chips</t>
+          <t>seafood/Clams &amp; Chips</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -4126,12 +4107,12 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Shrimp &amp; Chips</t>
+          <t>Clams &amp; Chips</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>12 shrimp.</t>
+          <t>Two cups of clams.</t>
         </is>
       </c>
       <c r="E86" s="10" t="n">
@@ -4141,16 +4122,12 @@
       <c r="G86" s="10" t="n"/>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="inlineStr"/>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>shrimp</t>
-        </is>
-      </c>
+      <c r="J86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>seafood/Seafood Platter</t>
+          <t>seafood/Shrimp &amp; Chips</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -4160,27 +4137,31 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Seafood Platter</t>
+          <t>Shrimp &amp; Chips</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
+          <t>12 shrimp.</t>
         </is>
       </c>
       <c r="E87" s="10" t="n">
-        <v>23.95</v>
+        <v>14.95</v>
       </c>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="inlineStr"/>
-      <c r="J87" s="10" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>shrimp</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>seafood/Extra Coleslaw</t>
+          <t>seafood/Seafood Platter</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -4190,47 +4171,45 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Extra Coleslaw</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr"/>
+          <t>Seafood Platter</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>A piece of fish, fries, 5 scallops, 5 shrimp and clams.</t>
+        </is>
+      </c>
       <c r="E88" s="10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F88" s="10" t="n">
-        <v>3.45</v>
-      </c>
+        <v>23.95</v>
+      </c>
+      <c r="F88" s="10" t="n"/>
       <c r="G88" s="10" t="n"/>
       <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
+      <c r="I88" s="10" t="inlineStr"/>
       <c r="J88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>subs/Cold Cut</t>
+          <t>seafood/Extra Coleslaw</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Subs</t>
+          <t>More Seafood</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Cold Cut</t>
+          <t>Extra Coleslaw</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr"/>
       <c r="E89" s="10" t="n">
-        <v>10.95</v>
+        <v>2.25</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>13.25</v>
+        <v>3.45</v>
       </c>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
@@ -4239,16 +4218,12 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J89" s="10" t="inlineStr">
-        <is>
-          <t>cold-cut-sub</t>
-        </is>
-      </c>
+      <c r="J89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>subs/Salami &amp; Ham</t>
+          <t>subs/Cold Cut</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -4258,7 +4233,7 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Salami &amp; Ham</t>
+          <t>Cold Cut</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr"/>
@@ -4275,12 +4250,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J90" s="10" t="inlineStr"/>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>cold-cut-sub</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>subs/Pizza Sub</t>
+          <t>subs/Salami &amp; Ham</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -4290,7 +4269,7 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Pizza Sub</t>
+          <t>Salami &amp; Ham</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr"/>
@@ -4312,7 +4291,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>subs/Vegetarian</t>
+          <t>subs/Pizza Sub</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -4322,7 +4301,7 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Pizza Sub</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr"/>
@@ -4344,7 +4323,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>subs/Real Turkey</t>
+          <t>subs/Vegetarian</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -4354,12 +4333,12 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Real Turkey</t>
+          <t>Vegetarian</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr"/>
       <c r="E93" s="10" t="n">
-        <v>11.45</v>
+        <v>10.95</v>
       </c>
       <c r="F93" s="10" t="n">
         <v>13.25</v>
@@ -4376,7 +4355,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>subs/Bubba</t>
+          <t>subs/Real Turkey</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -4386,19 +4365,15 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Bubba</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>The one people ask for by name.</t>
-        </is>
-      </c>
+          <t>Real Turkey</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr"/>
       <c r="E94" s="10" t="n">
-        <v>11.95</v>
+        <v>11.45</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>14.25</v>
+        <v>13.25</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -4412,7 +4387,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>subs/Club</t>
+          <t>subs/Bubba</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -4422,10 +4397,14 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Club</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr"/>
+          <t>Bubba</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>The one people ask for by name.</t>
+        </is>
+      </c>
       <c r="E95" s="10" t="n">
         <v>11.95</v>
       </c>
@@ -4444,7 +4423,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>subs/Steak</t>
+          <t>subs/Club</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -4454,7 +4433,7 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr"/>
@@ -4462,7 +4441,7 @@
         <v>11.95</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>14.95</v>
+        <v>14.25</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -4471,16 +4450,12 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J96" s="10" t="inlineStr">
-        <is>
-          <t>steak-sub</t>
-        </is>
-      </c>
+      <c r="J96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>subs/Donair Sub</t>
+          <t>subs/Steak</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -4490,7 +4465,7 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Donair Sub</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr"/>
@@ -4507,12 +4482,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J97" s="10" t="inlineStr"/>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>steak-sub</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>subs/Super Sub</t>
+          <t>subs/Donair Sub</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -4522,15 +4501,15 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Super Sub</t>
+          <t>Donair Sub</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr"/>
       <c r="E98" s="10" t="n">
-        <v>12.45</v>
+        <v>11.95</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>16.25</v>
+        <v>14.95</v>
       </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
@@ -4544,7 +4523,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>subs/Garlic Bread</t>
+          <t>subs/Super Sub</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -4554,15 +4533,15 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Garlic Bread</t>
+          <t>Super Sub</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr"/>
       <c r="E99" s="10" t="n">
-        <v>6.25</v>
+        <v>12.45</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>7.45</v>
+        <v>16.25</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -4576,7 +4555,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Cheese</t>
+          <t>subs/Garlic Bread</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -4586,15 +4565,15 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Extra Cheese</t>
+          <t>Garlic Bread</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr"/>
       <c r="E100" s="10" t="n">
-        <v>2.75</v>
+        <v>6.25</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>3.95</v>
+        <v>7.45</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -4608,7 +4587,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>subs/Extra Meat</t>
+          <t>subs/Extra Cheese</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -4618,15 +4597,15 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Extra Meat</t>
+          <t>Extra Cheese</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr"/>
       <c r="E101" s="10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F101" s="10" t="n">
         <v>3.95</v>
-      </c>
-      <c r="F101" s="10" t="n">
-        <v>4.75</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -4640,33 +4619,31 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>burritos/Beans &amp; Veggie</t>
+          <t>subs/Extra Meat</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Burritos</t>
+          <t>Subs</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Extra Meat</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr"/>
       <c r="E102" s="10" t="n">
-        <v>7.99</v>
+        <v>3.95</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="G102" s="10" t="n">
-        <v>10.99</v>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="inlineStr">
         <is>
-          <t>Small / Medium / Large</t>
+          <t>Small / Large</t>
         </is>
       </c>
       <c r="J102" s="10" t="inlineStr"/>
@@ -4674,7 +4651,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>burritos/Spicy Chicken</t>
+          <t>burritos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -4684,18 +4661,18 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr"/>
       <c r="E103" s="10" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="F103" s="10" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="G103" s="10" t="n">
         <v>10.99</v>
-      </c>
-      <c r="G103" s="10" t="n">
-        <v>12.99</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="inlineStr">
@@ -4703,16 +4680,12 @@
           <t>Small / Medium / Large</t>
         </is>
       </c>
-      <c r="J103" s="10" t="inlineStr">
-        <is>
-          <t>burrito</t>
-        </is>
-      </c>
+      <c r="J103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>burritos/Ground Beef</t>
+          <t>burritos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -4722,7 +4695,7 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr"/>
@@ -4741,12 +4714,16 @@
           <t>Small / Medium / Large</t>
         </is>
       </c>
-      <c r="J104" s="10" t="inlineStr"/>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>burrito</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>burritos/Zesty Grilled Chicken</t>
+          <t>burritos/Ground Beef</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -4756,7 +4733,7 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr"/>
@@ -4780,7 +4757,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>burritos/Fish</t>
+          <t>burritos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -4790,7 +4767,7 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr"/>
@@ -4814,7 +4791,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>burritos/Shawarma Chicken</t>
+          <t>burritos/Fish</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -4824,18 +4801,18 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr"/>
       <c r="E107" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F107" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="F107" s="10" t="n">
-        <v>11.99</v>
-      </c>
       <c r="G107" s="10" t="n">
-        <v>13.99</v>
+        <v>12.99</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="inlineStr">
@@ -4848,7 +4825,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>burritos/Tequila-Lime Glazed Chicken</t>
+          <t>burritos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -4858,7 +4835,7 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr"/>
@@ -4882,7 +4859,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>burritos/Steak</t>
+          <t>burritos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -4892,7 +4869,7 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr"/>
@@ -4916,43 +4893,41 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Beans &amp; Veggie</t>
+          <t>burritos/Steak</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Rice Bowls</t>
+          <t>Burritos</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr"/>
       <c r="E110" s="10" t="n">
-        <v>10.49</v>
+        <v>10.99</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="G110" s="10" t="n"/>
+        <v>11.99</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>13.99</v>
+      </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>Small / Large</t>
-        </is>
-      </c>
-      <c r="J110" s="10" t="inlineStr">
-        <is>
-          <t>rice-bowl</t>
-        </is>
-      </c>
+          <t>Small / Medium / Large</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Spicy Chicken</t>
+          <t>rice-bowls/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -4962,15 +4937,15 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr"/>
       <c r="E111" s="10" t="n">
-        <v>11.49</v>
+        <v>10.49</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>13.49</v>
+        <v>12.49</v>
       </c>
       <c r="G111" s="10" t="n"/>
       <c r="H111" s="10" t="n"/>
@@ -4979,12 +4954,16 @@
           <t>Small / Large</t>
         </is>
       </c>
-      <c r="J111" s="10" t="inlineStr"/>
+      <c r="J111" s="10" t="inlineStr">
+        <is>
+          <t>rice-bowl</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Ground Beef</t>
+          <t>rice-bowls/Spicy Chicken</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -4994,7 +4973,7 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr"/>
@@ -5016,7 +4995,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Zesty Grilled Chicken</t>
+          <t>rice-bowls/Ground Beef</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -5026,7 +5005,7 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr"/>
@@ -5048,7 +5027,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Fish</t>
+          <t>rice-bowls/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -5058,7 +5037,7 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr"/>
@@ -5080,7 +5059,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Shawarma Chicken</t>
+          <t>rice-bowls/Fish</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -5090,15 +5069,15 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr"/>
       <c r="E115" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>14.49</v>
+        <v>13.49</v>
       </c>
       <c r="G115" s="10" t="n"/>
       <c r="H115" s="10" t="n"/>
@@ -5112,7 +5091,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
+          <t>rice-bowls/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -5122,7 +5101,7 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr"/>
@@ -5144,7 +5123,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>rice-bowls/Steak</t>
+          <t>rice-bowls/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -5154,7 +5133,7 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr"/>
@@ -5176,37 +5155,39 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Beans &amp; Veggie</t>
+          <t>rice-bowls/Steak</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Quesadillas</t>
+          <t>Rice Bowls</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr"/>
       <c r="E118" s="10" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="F118" s="10" t="n"/>
+        <v>12.49</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>14.49</v>
+      </c>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
-      <c r="I118" s="10" t="inlineStr"/>
-      <c r="J118" s="10" t="inlineStr">
-        <is>
-          <t>quesadilla</t>
-        </is>
-      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>Small / Large</t>
+        </is>
+      </c>
+      <c r="J118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Spicy Chicken</t>
+          <t>quesadillas/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -5216,23 +5197,27 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr"/>
       <c r="E119" s="10" t="n">
-        <v>11.49</v>
+        <v>10.49</v>
       </c>
       <c r="F119" s="10" t="n"/>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="inlineStr"/>
-      <c r="J119" s="10" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>quesadilla</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Ground Beef</t>
+          <t>quesadillas/Spicy Chicken</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -5242,7 +5227,7 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr"/>
@@ -5258,7 +5243,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Zesty Grilled Chicken</t>
+          <t>quesadillas/Ground Beef</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -5268,7 +5253,7 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr"/>
@@ -5284,7 +5269,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Fish</t>
+          <t>quesadillas/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -5294,7 +5279,7 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr"/>
@@ -5310,7 +5295,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Shawarma Chicken</t>
+          <t>quesadillas/Fish</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -5320,12 +5305,12 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr"/>
       <c r="E123" s="10" t="n">
-        <v>12.49</v>
+        <v>11.49</v>
       </c>
       <c r="F123" s="10" t="n"/>
       <c r="G123" s="10" t="n"/>
@@ -5336,7 +5321,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
+          <t>quesadillas/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -5346,7 +5331,7 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr"/>
@@ -5362,7 +5347,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>quesadillas/Steak</t>
+          <t>quesadillas/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -5372,7 +5357,7 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr"/>
@@ -5388,37 +5373,33 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>tacos/Beans &amp; Veggie</t>
+          <t>quesadillas/Steak</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Tacos</t>
+          <t>Quesadillas</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Beans &amp; Veggie</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr"/>
       <c r="E126" s="10" t="n">
-        <v>9.99</v>
+        <v>12.49</v>
       </c>
       <c r="F126" s="10" t="n"/>
       <c r="G126" s="10" t="n"/>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="inlineStr"/>
-      <c r="J126" s="10" t="inlineStr">
-        <is>
-          <t>tacos</t>
-        </is>
-      </c>
+      <c r="J126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>tacos/Spicy Chicken</t>
+          <t>tacos/Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -5428,23 +5409,27 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Spicy Chicken</t>
+          <t>Beans &amp; Veggie</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr"/>
       <c r="E127" s="10" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="F127" s="10" t="n"/>
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="inlineStr"/>
-      <c r="J127" s="10" t="inlineStr"/>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>tacos</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>tacos/Ground Beef</t>
+          <t>tacos/Spicy Chicken</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -5454,7 +5439,7 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Ground Beef</t>
+          <t>Spicy Chicken</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr"/>
@@ -5470,7 +5455,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>tacos/Zesty Grilled Chicken</t>
+          <t>tacos/Ground Beef</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -5480,7 +5465,7 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Zesty Grilled Chicken</t>
+          <t>Ground Beef</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr"/>
@@ -5496,7 +5481,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>tacos/Fish</t>
+          <t>tacos/Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -5506,7 +5491,7 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Zesty Grilled Chicken</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr"/>
@@ -5522,7 +5507,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>tacos/Shawarma Chicken</t>
+          <t>tacos/Fish</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -5532,12 +5517,12 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Shawarma Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr"/>
       <c r="E131" s="10" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="F131" s="10" t="n"/>
       <c r="G131" s="10" t="n"/>
@@ -5548,7 +5533,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>tacos/Tequila-Lime Glazed Chicken</t>
+          <t>tacos/Shawarma Chicken</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -5558,7 +5543,7 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Tequila-Lime Glazed Chicken</t>
+          <t>Shawarma Chicken</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr"/>
@@ -5574,7 +5559,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>tacos/Steak</t>
+          <t>tacos/Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -5584,7 +5569,7 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Steak</t>
+          <t>Tequila-Lime Glazed Chicken</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr"/>
@@ -5600,22 +5585,22 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Salsa — Small</t>
+          <t>tacos/Steak</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Sides</t>
+          <t>Tacos</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Salsa — Small</t>
+          <t>Steak</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr"/>
       <c r="E134" s="10" t="n">
-        <v>2.49</v>
+        <v>11.99</v>
       </c>
       <c r="F134" s="10" t="n"/>
       <c r="G134" s="10" t="n"/>
@@ -5626,7 +5611,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Salsa — Large</t>
+          <t>burrito-sides/Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -5636,12 +5621,12 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Salsa — Large</t>
+          <t>Chips &amp; Salsa — Small</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr"/>
       <c r="E135" s="10" t="n">
-        <v>4.49</v>
+        <v>2.49</v>
       </c>
       <c r="F135" s="10" t="n"/>
       <c r="G135" s="10" t="n"/>
@@ -5652,7 +5637,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Queso — Small</t>
+          <t>burrito-sides/Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -5662,12 +5647,12 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Queso — Small</t>
+          <t>Chips &amp; Salsa — Large</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr"/>
       <c r="E136" s="10" t="n">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="10" t="n"/>
@@ -5678,7 +5663,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Queso — Large</t>
+          <t>burrito-sides/Chips &amp; Queso — Small</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -5688,12 +5673,12 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Queso — Large</t>
+          <t>Chips &amp; Queso — Small</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr"/>
       <c r="E137" s="10" t="n">
-        <v>6.49</v>
+        <v>3.49</v>
       </c>
       <c r="F137" s="10" t="n"/>
       <c r="G137" s="10" t="n"/>
@@ -5704,7 +5689,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Guac — Small</t>
+          <t>burrito-sides/Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -5714,12 +5699,12 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Guac — Small</t>
+          <t>Chips &amp; Queso — Large</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr"/>
       <c r="E138" s="10" t="n">
-        <v>3.99</v>
+        <v>6.49</v>
       </c>
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="10" t="n"/>
@@ -5730,7 +5715,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Chips &amp; Guac — Large</t>
+          <t>burrito-sides/Chips &amp; Guac — Small</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -5740,12 +5725,12 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Chips &amp; Guac — Large</t>
+          <t>Chips &amp; Guac — Small</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr"/>
       <c r="E139" s="10" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="F139" s="10" t="n"/>
       <c r="G139" s="10" t="n"/>
@@ -5756,7 +5741,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Fries Supreme</t>
+          <t>burrito-sides/Chips &amp; Guac — Large</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -5766,12 +5751,12 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Fries Supreme</t>
+          <t>Chips &amp; Guac — Large</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr"/>
       <c r="E140" s="10" t="n">
-        <v>9.99</v>
+        <v>6.99</v>
       </c>
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
@@ -5782,7 +5767,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Spicy Fries</t>
+          <t>burrito-sides/Fries Supreme</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -5792,12 +5777,12 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Spicy Fries</t>
+          <t>Fries Supreme</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr"/>
       <c r="E141" s="10" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="F141" s="10" t="n"/>
       <c r="G141" s="10" t="n"/>
@@ -5808,7 +5793,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Deep Fried Pepperoni</t>
+          <t>burrito-sides/Spicy Fries</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -5818,16 +5803,12 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Deep Fried Pepperoni</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>With honey mustard sauce.</t>
-        </is>
-      </c>
+          <t>Spicy Fries</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr"/>
       <c r="E142" s="10" t="n">
-        <v>12.99</v>
+        <v>8.99</v>
       </c>
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="10" t="n"/>
@@ -5838,7 +5819,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
+          <t>burrito-sides/Deep Fried Pepperoni</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -5848,12 +5829,16 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Add Chips &amp; Salsa + a Can of Pop</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr"/>
+          <t>Deep Fried Pepperoni</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>With honey mustard sauce.</t>
+        </is>
+      </c>
       <c r="E143" s="10" t="n">
-        <v>3.49</v>
+        <v>12.99</v>
       </c>
       <c r="F143" s="10" t="n"/>
       <c r="G143" s="10" t="n"/>
@@ -5864,7 +5849,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>burrito-sides/Brownie</t>
+          <t>burrito-sides/Add Chips &amp; Salsa + a Can of Pop</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -5874,12 +5859,12 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Add Chips &amp; Salsa + a Can of Pop</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr"/>
       <c r="E144" s="10" t="n">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
@@ -5887,12 +5872,38 @@
       <c r="I144" s="10" t="inlineStr"/>
       <c r="J144" s="10" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>burrito-sides/Brownie</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>Brownie</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr"/>
+      <c r="E145" s="10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="F145" s="10" t="n"/>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="10" t="inlineStr"/>
+      <c r="J145" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J144" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
+    <dataValidation sqref="J5:J145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Pick one from the dropdown, or leave it empty." type="list">
       <formula1>=Lists!$B$1:$B$41</formula1>
     </dataValidation>
   </dataValidations>

--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -2092,7 +2092,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Any size.</t>
+          <t>12" medium pizzas only.</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">

--- a/TastyPizza-Control.xlsx
+++ b/TastyPizza-Control.xlsx
@@ -3809,7 +3809,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>beverages/Any 519ml Pop</t>
+          <t>beverages/Any 591ml Pop</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Any 519ml Pop</t>
+          <t>Any 591ml Pop</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr"/>
